--- a/Required Document/QC_Claude_Hasil.xlsx
+++ b/Required Document/QC_Claude_Hasil.xlsx
@@ -40,7 +40,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,11 +64,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
@@ -85,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -95,7 +90,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -519,13 +513,13 @@
         <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -534,7 +528,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -547,13 +541,13 @@
         <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -562,7 +556,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -575,13 +569,13 @@
         <v>51</v>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -590,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -603,22 +597,22 @@
         <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -631,22 +625,22 @@
         <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -659,13 +653,13 @@
         <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -674,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -687,13 +681,13 @@
         <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -715,7 +709,7 @@
         <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
@@ -724,7 +718,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -743,10 +737,10 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -799,10 +793,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -879,7 +873,7 @@
           <t>Guest membuka beranda → katalog → detail produk; pilih warna/ukuran, upload desain sendiri, Tambah ke Keranjang → diminta login</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -929,7 +923,7 @@
           <t>Login → keranjang berisi item yang tadi ditambahkan (tidak hilang)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -1679,7 +1673,7 @@
           <t>Refund dilakukan manual &amp; dikomunikasikan lewat chat (BR-006/015) — alur manual terdokumentasi</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -1754,7 +1748,7 @@
           <t>Komplain kualitas lewat Chat dalam 7 hari setelah Selesai ditangani manual (BR-016); setelah 7 hari dianggap final</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -1779,7 +1773,7 @@
           <t>Produksi ulang gratis jika salah produksi (BR-011) — alur manual terdokumentasi</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -1829,14 +1823,14 @@
           <t>Blokir hak cipta: akun tidak bisa login sama sekali; komisi terhutang berubah "Ditahan"</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Blokir hak cipta: komisi berubah ditahan (diverifikasi), TETAPI akun masih bisa login (200) -&gt; AuthService::attemptLogin tidak memeriksa users.status (Banned/Nonaktif).</t>
+          <t>banned: Verifikasi ulang setelah perbaikan: akun banned ditolak saat login (HTTP 422) dan sesi lama ditolak (HTTP 403); komisi ditahan tetap sesuai uji sebelumnya | Sebelumnya (Gagal): Blokir hak cipta: komisi berubah ditahan (diverifikasi), TETAPI akun masih bisa login (200) -&gt; AuthService::at</t>
         </is>
       </c>
     </row>
@@ -1879,14 +1873,14 @@
           <t>Item wishlist/keranjang dari desain creator terblokir ditandai tidak tersedia &amp; tidak bisa di-checkout (BR-024)</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>BR-024: setelah creator diblokir, item keranjang desainnya tetap is_available=true dan checkout berhasil (201); CartItemResource::is_available hanya melihat product.is_active, tidak status desain/creator.</t>
+          <t>BR-024 desain creator diblokir: Verifikasi ulang setelah perbaikan: item desain creator #11: is_available true -&gt; false setelah creator di-ban; POST /checkout -&gt; HTTP 422 (ditolak). Dipulihkan. | Sebelumnya (Gagal): BR-024: setelah creator diblokir, item keranjang desainnya tetap is_available=true dan checkout berhasil (201)</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2298,7 @@
           <t>Dua browser (customer &amp; admin): pesan customer muncul di admin tanpa refresh dan sebaliknya</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -2329,7 +2323,7 @@
           <t>Aksi admin (setujui desain/ubah status) memunculkan notifikasi di browser customer/creator tanpa refresh</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -2354,7 +2348,7 @@
           <t>Putus-sambung internet: koneksi realtime tersambung ulang &amp; tidak ada pesan hilang/ganda</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -2429,7 +2423,7 @@
           <t>Ganti bahasa di tengah checkout → data keranjang &amp; alamat tidak hilang</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -2552,7 +2546,7 @@
           <t>Scheduler benar-benar berjalan di server produksi (cron `* * * * * schedule:run` atau service) — tanpa ini ketiga job tidak jalan</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -2927,7 +2921,7 @@
           <t>URL notifikasi terdaftar di dashboard Midtrans mengarah ke domain backend yang benar (api.harmoniclothing.com)</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3277,7 +3271,7 @@
           <t>Locale: header Accept-Language dan ?lang diterapkan ke nama produk/kategori &amp; pesan</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3402,7 +3396,7 @@
           <t>Email verifikasi: pengirim hello@harmoniclothing.com, subjek benar, tombol "Verifikasi Email", tautan ke frontend /verify-email berisi id/hash/expires/signature yang valid</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3452,7 +3446,7 @@
           <t>Isi email mengikuti locale (ID/EN); tampilan rapi di Gmail/Outlook/mobile</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3477,7 +3471,7 @@
           <t>Email tidak masuk spam pada kotak masuk uji (SPF/DKIM/DMARC lulus untuk domain pengirim)</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3502,7 +3496,7 @@
           <t>Email terkirim ke alamat mana pun (bukan hanya pemilik akun Resend) — domain terverifikasi</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3527,7 +3521,7 @@
           <t>Kegagalan Resend tidak membuat registrasi/lupa password crash 500 (ditangani/dicatat)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3602,7 +3596,7 @@
           <t>Kanal notifikasi privat per user; user lain tidak dapat subscribe</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3627,7 +3621,7 @@
           <t>Otorisasi /broadcasting/auth memakai cookie sesi + CSRF dan lewat domain yang sama</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3802,7 +3796,7 @@
           <t>Berkas yang dihapus/diganti tidak meninggalkan referensi rusak</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -3952,7 +3946,7 @@
           <t>Migrasi database terkini sudah dijalankan; tidak ada migrasi tertunda</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -4177,7 +4171,7 @@
           <t>`pnpm build` sukses (semua rute terdaftar)</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -4450,14 +4444,14 @@
           <t>Akun banned/nonaktif tidak dapat login &amp; sesi aktif ditolak</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>TEMUAN KRITIS: user dengan status 'banned' (ban + copyright_violation) tetap bisa login baru (200) dan sesi lamanya tetap valid (/me 200). UserStatus Banned/Nonaktif hanya ditulis di CreatorService::ban, tidak pernah dicek di login/middleware. Ban biasa memang hanya mencabut akses /creator/* (403, sesuai desain). Perlu cek login &amp; middleware auth.</t>
+          <t>banned login &amp; sesi: Verifikasi ulang setelah perbaikan: login user banned HTTP 422 (ditolak); sesi aktif lalu user di-ban: /me 200 -&gt; 403; login ulang 422. Dipulihkan. | Sebelumnya (Gagal): TEMUAN KRITIS: user dengan status 'banned' (ban + copyright_violation) tetap bisa login baru (200) dan sesi la</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4919,7 @@
           <t>Mixed content: semua aset dimuat lewat HTTPS</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -5225,7 +5219,7 @@
           <t>Hak penghapusan/koreksi data dapat diajukan lewat kontak (sesuai kebijakan privasi)</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -5598,14 +5592,14 @@
           <t>Jika data produk/desain kosong atau API gagal, section menampilkan empty/error state (bukan crash)</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): backend dimatikan: /catalog tetap menampilkan skeleton &gt;10 detik tanpa pesan error/tombol Coba Lagi (17 request ERR_CONNECTION_REFUSED).</t>
+          <t>backend mati: /catalog: Verifikasi ulang setelah perbaikan: backend mati: /catalog menampilkan 'Terjadi kesalahan' + tombol Coba Lagi (bukan skeleton selamanya) | Sebelumnya (Gagal): Browser QC (localhost:3001 + backend QC): backend dimatikan: /catalog tetap menampilkan skeleton &gt;10 detik tan</t>
         </is>
       </c>
     </row>
@@ -5698,14 +5692,14 @@
           <t>Tampilan rapi di mobile (375px), tablet (768px), dan desktop (1280px+)</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): overflow tablet 768: scroll horizontal pada 768px: beranda=38px, katalog=42px, marketplace=42px, about=38px (beranda: elemen hero 'hidden animate-fade-slide-in md:' melebar sampai x=806) | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): responsif beranda: overflow: 375:0, 768:38, 1280:0, 1920:0 | Bukti lain: Browser QC (loc</t>
+          <t>Verifikasi ulang setelah perbaikan: 768x1024 dan 800x375 tanpa scroll horizontal pada /, /catalog, /marketplace (tab Desain &amp; Kreator), /about, /faq, detail produk, detail desain. Perbaikan: header desktop pindah ke breakpoint lg (menu hamburger di bawah 1024px), toolbar daftar dan kolom detail produk/desain bertumpuk sampai lg. | Sebelumnya (Gagal): overflow tablet 768: Verifikasi ulang setelah perbaikan: /=0, /catalog=0, /marketplace=0, /about=0, /faq=0, /c</t>
         </is>
       </c>
     </row>
@@ -6373,14 +6367,14 @@
           <t>Loading skeleton tampil saat data dimuat; error state + tombol "Coba Lagi" tampil saat API gagal</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): error state API gagal (marketplace/katalog): skeleton tampil (Error #41); error state + 'Coba Lagi' TIDAK tampil saat API gagal (Error #11, #22)</t>
+          <t>error state API gagal: Verifikasi ulang setelah perbaikan: marketplace dengan API 500: error state + Coba Lagi tampil | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): error state API gagal (marketplace/katalog): skeleton tamp</t>
         </is>
       </c>
     </row>
@@ -6473,12 +6467,16 @@
           <t>Hasil kosong menampilkan pesan "Belum ada kreator ditemukan" + reset</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>tab kreator kosong: Verifikasi ulang setelah perbaikan: tab Kreator kosong menampilkan 'Belum ada kreator ditemukan.' (tombol reset hanya tampil bila ada pencarian/filter aktif) | Sebelumnya (Gagal): Browser QC (Playwright, putaran 2): tab Kreator dengan hasil kosong hanya menampilkan 'Menampilkan 0 dari 0 kr</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6494,12 +6492,16 @@
           <t>Foto profil kreator tampil (bukan broken image); kreator tanpa foto menampilkan avatar default</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): tab Kreator memuat 7 kartu kreator; seluruh 7 kreator seed tidak punya foto (photo_url null) dan kartu tampil tanpa elemen &lt;img&gt; rusak (avatar default). Kasus kreator dengan foto nyata tidak ada di data seed sehingga belum diuji.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6590,12 +6592,16 @@
           <t>Tombol "Lihat Portofolio" membuka link portofolio (tab baru) &amp; hanya tampil bila diisi</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): tombol Lihat Portofolio: tidak ada kreator dengan portfolio_url di data seed; dengan portofolio: tidak ada data; tanpa portofolio: tombol=0</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6611,12 +6617,16 @@
           <t>Statistik (Desain, Rating, Total Terjual) sesuai data nyata</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): statistik profil creator: UI: Desain / Rating / Total Terjual / Desain oleh Balistreri-Abernathy (3); kunci API: name,photo_url,bio,portfolio_url,slug,since,designs; kecocokan angka dengan database belum dihitung ulang</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6657,12 +6667,16 @@
           <t>Kreator tanpa desain menampilkan "Belum ada desain yang dipublikasikan"</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): kreator tanpa desain: daftar desain kosong -&gt; 'Belum ada desain yang dipublikasikan.'</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6828,12 +6842,16 @@
           <t>Opsi filter (warna/ukuran/material) berasal dari data nyata katalog; "Semua" &amp; "Reset" berfungsi</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr"/>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>opsi filter warna: Verifikasi ulang setelah perbaikan: filter Warna berupa swatch dengan nama aksesibel: Hitam, Merah QC, Navy, Putih; filter Ukuran=5 opsi; (koreksi: sebelumnya salah dilaporkan 'kosong', yang kurang hanya aria-label) | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): filter /catalog: Ukuran (L, M, S, XL, XXL) dan Material (Cotton Combed 24s</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6949,12 +6967,16 @@
           <t>Filter via URL dari footer (mis. kategori T-Shirt) menghasilkan hasil benar</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr"/>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): tautan footer 'T-Shirt' -&gt; /catalog?kategori=t-shirt menghasilkan 'Menampilkan 0 dari 10 produk': slug kategori di footer tidak cocok dengan kategori data QC (seed faker: Dolorum ipsam, dst.), jadi hasil filter benar hanya bisa dipastikan dengan kategori produksi 'T-Shirt'.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7045,14 +7067,14 @@
           <t>Loading skeleton &amp; error state + "Coba Lagi" tampil sesuai kondisi</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state katalog: skeleton tampil; error state + 'Coba Lagi' tidak tampil saat API gagal (Error #11)</t>
+          <t>skeleton &amp; error state katalog: Verifikasi ulang setelah perbaikan: skeleton saat loading (9 elemen) dan error state saat API 500 | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state katalog: skeleton tampil; error sta</t>
         </is>
       </c>
     </row>
@@ -7095,12 +7117,16 @@
           <t>Galeri gambar berganti sesuai warna yang dipilih; thumbnail dapat diklik</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): galeri berganti sesuai warna: warna tersedia=; gambar utama berubah saat ganti warna=false; jumlah gambar=9; mockup seed memakai placeholder sama sehingga perubahan visual tidak dapat dibuktikan penuh</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7191,12 +7217,16 @@
           <t>Area upload "Upload Desain Sendiri (opsional)": file PNG/JPG ≤ 20MB berhasil, status berubah "File terunggah", dapat diganti</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr"/>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): upload desain sendiri di detail produk: PNG 300x300 diunggah -&gt; 'File terunggah — klik untuk ganti'</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -7212,12 +7242,16 @@
           <t>Upload file salah format/terlalu besar menampilkan pesan error "Gagal mengunggah file"</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): upload salah format ditolak: tidak ada pesan error terdeteksi untuk berkas .txt: Upload Desain Sendiri (opsional) / Klik atau drag file di sini (PNG/SVG, maks 20MB)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -7483,12 +7517,16 @@
           <t>Tab Ulasan: daftar ulasan (nama pembeli, bintang, komentar, tanggal) + paginasi; kosong → "Belum ada ulasan"</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): tab ulasan: API ulasan=5; UI: 3.4 (5 ulasan) / Ulasan (5); kosong -&gt; 'tidak terdeteksi'</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7654,12 +7692,16 @@
           <t>Preview menampilkan desain di atas produk yang dipilih (bukan gambar rusak)</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): preview desain di atas produk: 10 gambar di detail desain termuat semua (tidak ada gambar rusak)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7775,12 +7817,16 @@
           <t>Desain tanpa produk yang cocok menampilkan "Belum ada produk yang tersedia untuk desain ini"</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): desain tanpa produk cocok: pesan 'Belum ada produk yang tersedia untuk desain ini' tidak terdeteksi: Pilih Produk / Pilih Warna Produk: Hitam</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7821,12 +7867,16 @@
           <t>"Koleksi Lainnya" menampilkan desain lain milik creator; "Lihat Semua →" berfungsi</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Koleksi Lainnya: bagian 'Koleksi Lainnya' tampil; 'Lihat Semua' berfungsi: /marketplace?kategori=placeat-saepe -&gt; /marketplace</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7917,12 +7967,16 @@
           <t>Ikon wishlist desain berfungsi</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr"/>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): ikon wishlist desain: wishlist 1 -&gt; 2 -&gt; 1 (toggle on/off tersimpan di server)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7963,12 +8017,16 @@
           <t>Section "Untuk Kreator Lokal" &amp; tombol "Jadi Kreator" berfungsi (guest → login/registrasi, user → /account/become-creator)</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr"/>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): bagian 'Untuk Kreator Lokal' tampil; tombol 'Jadi Kreator': guest -&gt; modal login/registrasi, user login -&gt; /account/become-creator.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8509,12 +8567,16 @@
           <t>Tautan dari checkbox registrasi membuka halaman ini (tab baru) tanpa menutup form</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr"/>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): tautan privacy dari registrasi: tautan /legal/privacy-policy target=_blank; form registrasi tetap terbuka=true; tab baru=false</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8580,12 +8642,16 @@
           <t>Tautan dari checkbox registrasi &amp; pengajuan creator membuka halaman ini</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): checkbox registrasi memiliki tautan /legal/terms; tetapi checkbox 'Saya menyetujui Syarat &amp; Ketentuan Creator' di /account/become-creator berupa teks biasa tanpa tautan ke halaman Syarat &amp; Ketentuan.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8701,14 +8767,14 @@
           <t>Login akun yang di-ban/nonaktif ditolak dengan pesan yang sesuai</t>
         </is>
       </c>
-      <c r="D140" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): login akun banned: akun banned berhasil login lewat UI | Bukti lain: Akun banned (copyright) tetap bisa login dan memakai sesi (sheet Keamanan #8) -&gt; penolakan login akun banned tidak berfungsi.</t>
+          <t>login akun banned via UI: Verifikasi ulang setelah perbaikan: login akun banned lewat UI ditolak dengan pesan 'Akun Anda telah diblokir. Hubungi admin Harmoni Clothing untuk informasi lebih lanjut.'; modal tetap terbuka=true | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): login akun banned: akun banned berhasil login lewat UI | B</t>
         </is>
       </c>
     </row>
@@ -10530,14 +10596,14 @@
           <t>Tombol "Pindahkan ke wishlist" memindahkan item &amp; menampilkan toast</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): pindahkan ke wishlist: wishlist 0, keranjang 1 | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): pindahkan ke wishlist: wishlist 4-&gt;4, keranjang 2</t>
+          <t>pindahkan ke wishlist: Verifikasi ulang setelah perbaikan: keranjang 3 -&gt; 2, wishlist 1 -&gt; 2 (produk dipindah, toast sukses) | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): pindahkan ke wishlist: wishlist 0, keranjang 1 | Bukti lai</t>
         </is>
       </c>
     </row>
@@ -10630,12 +10696,16 @@
           <t>Tidak ada infinite re-render / lag saat memilih item (regresi bug lama)</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): cart: tanpa re-render tak terbatas saat memilih item: 4 checkbox; 8 klik berurutan selesai 1659 ms; error 'Maximum update depth'=0; console error total=2</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -10951,7 +11021,7 @@
           <t>Pembayaran Midtrans (Sandbox): kartu, VA bank, e-wallet/QRIS tersedia &amp; dapat dibayar</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -11001,7 +11071,7 @@
           <t>Menutup halaman pembayaran tanpa bayar → pesanan tetap "Belum Dibayar" &amp; bisa dibayar ulang dari detail pesanan (jika tersedia)</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -11276,12 +11346,16 @@
           <t>Upload desain sendiri (opsional) berfungsi; link pilih desain marketplace berfungsi; catatan opsional tersimpan</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): bulk order: upload desain, pilih marketplace, catatan: halaman bulk order: input upload desain=1, tautan pilih desain marketplace=1, kolom catatan=1; penyimpanan catatan sampai ke pesanan tidak diverifikasi (butuh checkout bulk + Midtrans)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -11622,12 +11696,16 @@
           <t>Paginasi/muat lebih banyak berfungsi bila pesanan banyak</t>
         </is>
       </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): paginasi riwayat pesanan: UI menampilkan 20 dari 21 pesanan; kontrol paginasi=1</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11793,14 +11871,14 @@
           <t>Pesanan "Belum Dibayar": tautan/tombol bayar (jika ada) berfungsi; setelah 24 jam otomatis Dibatalkan (BR-017)</t>
         </is>
       </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): pesanan belum dibayar: bayar ulang: detail pesanan 'Belum Dibayar' tidak memiliki tombol/tautan bayar atau batal; pelanggan tidak dapat membayar ulang dari UI</t>
+          <t xml:space="preserve">Verifikasi ulang setelah perbaikan: detail pesanan HC-20261013-0469 (Belum Dibayar): tombol 'Bayar Sekarang' dan 'Batalkan Pesanan' tampil; tanpa tautan Snap -&gt; pesan 'Tautan pembayaran belum tersedia...'; dengan tautan tersimpan -&gt; diarahkan ke URL Snap (POST /orders/{id}/pay); Batalkan -&gt; status dibatalkan. Pesanan dipulihkan. Tombol 'Lihat Invoice' kini disembunyikan untuk pesanan Belum Dibayar. | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): pesanan belum dibayar: bayar ulang: detail pesanan 'Belum </t>
         </is>
       </c>
     </row>
@@ -11918,14 +11996,14 @@
           <t>Tautan "Lihat Invoice" membuka invoice pesanan</t>
         </is>
       </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI (Playwright, Edge headless, :3001 + backend QC): Lihat Invoice: halaman invoice menampilkan 'Terjadi kesalahan' (crash: order.items tidak ada di respons invoice) | Bukti lain: Browser QC (login test@example.com): halaman invoice /account/orders/{id}/invoice menampilkan error boundary 'Terjadi kesalahan' karena API </t>
+          <t>Lihat Invoice: Verifikasi ulang setelah perbaikan: halaman invoice termuat tanpa crash: no. INV-20261013-1363, baris item, subtotal/ongkir/total; page error=0; tombol Cetak ada=true | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): Lihat Invoice: halaman invoice menampilkan 'Terjadi kesala</t>
         </is>
       </c>
     </row>
@@ -11943,12 +12021,16 @@
           <t>Pratinjau desain per item (file yang dikirim customer / desain marketplace) tampil benar</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr"/>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): detail pesanan HC-20261013-7551 (item dengan desain marketplace): pratinjau desain tampil sebagai thumbnail kecil 64px (placeholder seed 'designs/thumbnails/placeholder.png'); API mengirim design_file_url dan custom_design_url. File desain unggahan customer sendiri belum diuji.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -12014,14 +12096,14 @@
           <t>Nomor invoice, tanggal terbit, data penjual &amp; pembeli, rincian item, subtotal, ongkir, total dibayar sesuai pesanan</t>
         </is>
       </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (login test@example.com): invoice tidak dapat dirender (lihat #87): API /orders/{id}/invoice memuat invoice_number &amp; order tanpa items/alamat/pembeli.</t>
+          <t>Invoice dirender: Verifikasi ulang setelah perbaikan: API /orders/{id}/invoice kini memuat order.items (nama produk, qty, subtotal) sehingga halaman invoice dapat dirender; lihat #87 | Sebelumnya (Gagal): Browser QC (login test@example.com): invoice tidak dapat dirender (lihat #87): API /orders/{id}/invoice memuat</t>
         </is>
       </c>
     </row>
@@ -12039,14 +12121,14 @@
           <t>Badge "Lunas" hanya untuk pesanan yang sudah dibayar</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): badge Lunas: halaman invoice tidak dapat dirender (crash, Customer #87) sehingga badge 'Lunas' tidak dapat diverifikasi</t>
+          <t xml:space="preserve">Badge Lunas: Verifikasi ulang setelah perbaikan: badge 'Lunas' tampil di halaman invoice | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): badge Lunas: halaman invoice tidak dapat dirender (crash, </t>
         </is>
       </c>
     </row>
@@ -12089,14 +12171,14 @@
           <t>Tombol Print membuka dialog cetak dengan tata letak rapi; tombol Kembali berfungsi</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Print invoice: halaman invoice crash (Customer #87) -&gt; tombol Print/Kembali tidak dapat diuji</t>
+          <t>Verifikasi ulang setelah perbaikan: halaman invoice termuat; tombol 'Print' ada dan memanggil window.print() (dialog cetak browser tidak diotomasi). | Sebelumnya (Gagal): Print invoice: Verifikasi ulang setelah perbaikan: tombol cetak tidak ditemukan | Sebelumnya (Sebagian): UI (P</t>
         </is>
       </c>
     </row>
@@ -12264,12 +12346,16 @@
           <t>Batal pada dialog crop tidak mengubah foto lama</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr"/>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): batal crop foto tidak mengubah foto lama: dialog crop (Simpan Foto) dibatalkan; src foto profil tetap sama</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12310,12 +12396,16 @@
           <t>Foto profil tidak broken (URL R2/storage benar) setelah reload</t>
         </is>
       </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr"/>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): foto profil tidak broken setelah reload: user tidak punya foto (kunci /me: id,name,email,phone,photo_url,role,status,email_verified_at); unggah foto nyata tidak diuji</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13031,7 +13121,7 @@
           <t>Balasan admin muncul real-time di panel; badge/indikator pesan baru bekerja</t>
         </is>
       </c>
-      <c r="D133" s="7" t="inlineStr">
+      <c r="D133" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -13106,7 +13196,7 @@
           <t>Tidak ada pesan ganda saat koneksi realtime putus-sambung</t>
         </is>
       </c>
-      <c r="D136" s="7" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -13329,12 +13419,16 @@
           <t>Pindah antara area Customer ↔ Creator tanpa logout; sesi tetap</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): pindah Customer &lt;-&gt; Creator tanpa logout: /account/profile -&gt; /creator/dashboard -&gt; /cart dengan sesi tetap (GET /me 200); dashboard creator termuat: 'Dashboard'</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13400,12 +13494,16 @@
           <t>Belum ada desain → pesan "Belum ada desain. Yuk upload desain pertamamu"</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): dashboard creator tanpa desain: kosong -&gt; 'Belum ada desain. Yuk upload desain pertamamu.'</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13421,12 +13519,16 @@
           <t>Loading skeleton &amp; error state tampil sesuai kondisi</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state dashboard creator: skeleton saat loading=0; saat API 500 tidak ada error state/Coba Lagi</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13592,12 +13694,16 @@
           <t>Pengguna ≥ 18 tahun: field wali tidak muncul</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): KYC &gt;= 18 tahun tanpa field wali: lahir 2000 -&gt; field wali tidak ada; lahir 2012 -&gt; field wali muncul (6)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -13638,12 +13744,16 @@
           <t>Status Disetujui/Ditolak/Diblokir tampil benar; Ditolak menampilkan alasan &amp; bisa mengajukan ulang (BR-028 versi creator bila ada)</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): status verifikasi tampil: halaman verifikasi creator aktif menampilkan: ; status Ditolak/Diblokir dengan alasan &amp; ajukan ulang (BR-028) diuji di sheet Validasi/BR via API</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13734,12 +13844,16 @@
           <t>Desain Ditolak menampilkan alasan penolakan admin</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>alasan penolakan tampil: Verifikasi ulang setelah perbaikan: alasan 'Resolusi gambar terlalu rendah untuk cetak' tampil di daftar dan di halaman detail desain #16 | Sebelumnya (Gagal): Browser QC (Playwright, putaran 2): desain #16 berstatus Ditolak (alasan admin di DB: 'Resolusi gambar terlalu</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -13880,12 +13994,16 @@
           <t>Preview desain pada tiap produk/apparel yang dipilih tampil benar</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): preview desain per produk (detail creator): detail desain aktif #13: 2 gambar, 0 gagal dimuat (naturalWidth=0); teks: Produk #9 / Produk #10</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -14026,12 +14144,16 @@
           <t>Desain yang sudah published tidak bisa disubmit ulang secara keliru</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>submit ulang desain aktif: Verifikasi ulang setelah perbaikan: POST /creator/designs/13/submit pada desain aktif -&gt; HTTP 422 'Hanya desain berstatus Draft atau Ditolak yang dapat diajukan untuk review.'; status tetap aktif | Sebelumnya (Gagal): Browser QC (Playwright, putaran 2): POST /api/creator/designs/13/submit pada desain berstatus 'aktif' (sudah p</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -14222,12 +14344,16 @@
           <t>Upload file ganda (klik dua kali) tidak membuat desain ganda</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): upload ganda klik dua kali: dblclick tombol upload: desain bertambah 0 (sebelum 4, sesudah 4)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -14318,12 +14444,16 @@
           <t>Riwayat komisi: item pesanan, nominal, status (Terhutang/Dibayar/Ditahan), tanggal, referensi pencairan</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): riwayat komisi: halaman earnings memuat status komisi; teks: Belum Dibayar / Sudah Dibayar / Dibayar / Terhutang; kunci API: 0,1,2,3,4; kolom referensi pencairan &amp; tanggal diperiksa dari teks saja</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -14662,12 +14792,16 @@
           <t>Angka berubah setelah aksi admin (approve, mulai produksi) tanpa data usang</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): angka dashboard berubah setelah aksi: PATCH status order #72 -&gt; HTTP 200; dashboard API berubah: orders.menunggu_approval:1-&gt;0, orders.diproses_produksi:3-&gt;4 (dikembalikan setelah uji)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14683,12 +14817,16 @@
           <t>Loading skeleton &amp; error state tampil sesuai kondisi</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state dashboard: skeleton saat loading=0; saat API 500: tidak ada error state/Coba Lagi (teks: Dashboard  MANAJEMEN  Kelola User &amp; Creator Approval Creator)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14779,12 +14917,16 @@
           <t>Belum ada pengguna → state kosong</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): state kosong user: daftar user kosong -&gt; 'Belum ada pengguna.'</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14950,12 +15092,16 @@
           <t>Bagian "Creator Aktif" menampilkan semua creator berstatus aktif dengan tombol "Blokir"; kosong → "Belum ada creator aktif"</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Creator Aktif + Blokir: bagian 'Creator Aktif' tampil; tombol Blokir=7; API creators=7; kosong -&gt; 'Belum ada creator aktif.'</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15246,12 +15392,16 @@
           <t>Kosong → "Belum ada desain menunggu review"</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): approval desain kosong: kosong -&gt; 'Belum ada desain menunggu review.'</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -15342,12 +15492,16 @@
           <t>Buka baris produk → form "Detail Produk" terisi (nama ID/EN, harga, segmen, deskripsi ID/EN, status aktif)</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): baris produk 'Ut doloremque neque' dibuka -&gt; form Detail Produk terisi: Nama ID &amp; EN, Harga Dasar 452000.00, Segmen (anak), Deskripsi ID &amp; EN, kotak 'Produk aktif'. (Field nama memakai &lt;input&gt; tanpa atribut type.)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -15413,12 +15567,16 @@
           <t>Mengaktifkan kembali → muncul lagi di katalog</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): nonaktifkan &amp; aktifkan produk: nonaktif -&gt; hilang dari /catalog/products publik; aktifkan lagi -&gt; muncul lagi (slug ut-doloremque-neque)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -15459,12 +15617,16 @@
           <t>Slug produk otomatis dari nama ID &amp; unik</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): slug otomatis &amp; unik: nama sama dua kali -&gt; slug 'qc-slug-test-1792027210776' dan 'qc-slug-test-1792027210776-1' (unik, dari nama ID); produk uji dibuat nonaktif</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -15530,12 +15692,16 @@
           <t>Daftar varian per produk: warna, ukuran, potongan, material, area cetak, tambahan harga</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): daftar varian per produk: tabel varian memuat kolom Warna, Ukuran, Potongan, Material, Print Area, Tambahan Harga, Aksi (baris per produk terlihat: Hitam	L	Oversize	Cotton Combed 30s	Depan, Belakang, Lengan	Rp 0 / Navy	S	Regular Fit	Cotton Combed 24s	Belakang, Depan, Lengan	Rp 0)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -15601,12 +15767,16 @@
           <t>Foto mockup yang diunggah tampil di halaman publik (bukan 403/404/broken)</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): varian 'Merah QC' dibuat via UI dengan foto mockup: tersimpan (mockup_asset_path=http://localhost:8001/storage/mockup-uploads/&lt;uuid&gt;.png) dan file ada di storage/app/public, TETAPI URL itu HTTP 404 di lingkungan QC karena symlink backend/public/storage masih menunjuk ke folder lama /d/Harmoni Clothing (rusak setelah proyek dipindah); gambar di halaman publik tidak termuat (naturalWidth=0). Juga: print_areas tersimpan [] padahal 3 kotak Print Area ada. Perbaikan: php artisan storage:link --force (tidak dijalankan, report-only).</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -15622,12 +15792,16 @@
           <t>Edit varian inline (baris varian) tersimpan; ganti foto mockup berfungsi</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): edit varian inline: tombol aksi baris varian berupa ikon tanpa nama aksesibel (3 tombol bernama kosong) sehingga edit inline &amp; ganti foto mockup tidak diotomasi; pembuatan varian + unggah mockup tercakup di #48</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -15768,12 +15942,16 @@
           <t>Tier baru langsung muncul di tabel &amp; memengaruhi perhitungan harga Bulk Order</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): tier baru muncul &amp; memengaruhi harga: tier 250-499 @45.000 dan 500+ @40.000 langsung muncul di tabel dan di API publik /bulk-pricing-tiers (5 tier)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -15814,12 +15992,16 @@
           <t>Tier terakhir dengan Maks kosong menangani qty sangat besar</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): tier terakhir Maks kosong: tier terakhir max_qty=null (min 500, Rp40000.00) tersimpan &amp; dikirim API; findBulkTier di UI menangani null (hooks/useBulkPricing); harga untuk qty sangat besar belum diukur di UI; tier QC dikembalikan ke semula (4 tier)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -15910,12 +16092,16 @@
           <t>Pesanan tanpa desain kustom menampilkan "Tanpa desain kustom"</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): tanpa desain kustom di antrian produksi: tampil: 'Tanpa desain kustom.'</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -16031,12 +16217,16 @@
           <t>Pratinjau desain per item tampil sama seperti di Antrian Produksi</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): pratinjau desain di Kelola Pesanan: daftar /admin/orders menampilkan 5 gambar; pratinjau desain per item tidak ada di daftar; kesamaan dengan Antrian Produksi belum dibandingkan</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -16077,12 +16267,16 @@
           <t>Refund pesanan ditolak dilakukan manual (BR-006) — tidak ada tombol refund otomatis; catatan proses terdokumentasi</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): refund pesanan ditolak manual: tidak ada tombol refund otomatis di /admin/orders; catatan di PROJECT_RULES.md: 'refund per-order (seluruh order), tidak per-item, tanpa pembayaran sebagian/DP. Bulk Order: semua atau tidak sama sekali. | `O'</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -16148,12 +16342,16 @@
           <t>Status pembayaran sesuai hasil Midtrans (settlement/capture-accept = lunas; pending; deny/cancel/expire = gagal)</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): status pembayaran sesuai Midtrans: UI memakai status: ; API: belum_dibayar, berhasil, gagal; pemetaan settlement/capture, deny/cancel/expire diuji lewat MidtransWebhookService di sheet Backend</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -16194,12 +16392,16 @@
           <t>Kosong → "Belum ada pembayaran"; paginasi berfungsi</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): pembayaran kosong &amp; paginasi: kosong -&gt; 'Belum ada pembayaran.'; paginasi: 'Halaman 1 dari 4 (78 total)'</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -16265,12 +16467,16 @@
           <t>"Ganti Kurir": modal format perusahaan:tipe (mis. jne:reg); override berhasil membooking kurir lain</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr"/>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Ganti Kurir: tombol 'Ganti Kurir' ada (2); modal: 'HC-20261013-6233	jne reg	jne	WB123	Sudah Dibooking / HC-20261013-9139	jne reg	-	-	Belum Dibooking / HC-20261013-7645	jne reg	-	-	Belum Dibooking'; booking ke kurir lain tidak dijalankan agar tidak membuat order Biteship sandbox baru</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -16311,12 +16517,16 @@
           <t>Biteship down/kredensial salah → pesan error jelas, tidak membuat shipment setengah jadi</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr"/>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Biteship down / kredensial salah: kegagalan Biteship tidak disimulasikan (mematikan key QC butuh restart backend); tinjau kode OrderService::bookShipment: catch/throw ada=true</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -16382,12 +16592,16 @@
           <t>Kosong → "Tidak ada pesanan siap dikirim"</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr"/>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): respons kosong pada /api/admin/production-queue (API yang dipakai halaman) -&gt; 'Tidak ada pesanan siap dikirim.'</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -16455,10 +16669,14 @@
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr"/>
+          <t>Tidak Dapat Diuji</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): chat realtime: Butuh Reverb/Pusher aktif; QC memakai BROADCAST_CONNECTION=log sehingga pesan baru tidak dipush ke browser admin</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -16574,12 +16792,16 @@
           <t>Mematikan satu jenis notifikasi benar-benar menghentikan pengiriman jenis itu; menyalakan kembali melanjutkan</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr"/>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): matikan satu jenis notifikasi: jenis 'order.paid': dinonaktifkan -&gt; notifikasi tidak dibuat (13-&gt;13); diaktifkan lagi -&gt; dibuat (13-&gt;14)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -16745,12 +16967,16 @@
           <t>Data kosong ditangani (angka 0, bukan NaN/error)</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): sales report data kosong: API rentang kosong HTTP 200 data={"period":{"from":"2000-01-01","to":"2000-01-02"},"revenue":{"total":"0.00","average_order_value":"0; UI (input tanggal=0) tanpa NaN/undefined</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -16914,12 +17140,16 @@
           <t>Guest membuka halaman customer/creator/admin diarahkan ke login (dengan modal) tanpa kilatan konten privat</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): guest ke halaman privat: guest diarahkan: /cart-&gt;/cart modal=true api200=false ; /account/orders-&gt;/account/orders modal=true api200=false ; /creator/dashboard-&gt;/creator/dashboard modal=true api200=false ; /admin/dashboard-&gt;/admin/dashboard modal=true api200=false ; /checkout-&gt;/checkout modal=true api200=false</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -17010,12 +17240,16 @@
           <t>Setelah sesi kedaluwarsa (419/401) UI tidak macet — diarahkan/di-prompt login ulang</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): sesi kedaluwarsa 401/419: cookie dihapus lalu navigasi: tetap di /account/profile, modal login=false (UI tidak macet/crash, tetapi tidak ada prompt login ulang)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -17031,14 +17265,14 @@
           <t>Banned user langsung ditolak pada request berikutnya</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Banned user (blokir hak cipta) tidak ditolak pada request berikutnya: login &amp; sesi tetap berfungsi (AuthService::attemptLogin tidak mengecek users.status).</t>
+          <t>banned: Verifikasi ulang setelah perbaikan: login banned -&gt; 422; sesi berjalan -&gt; 403 | Sebelumnya (Gagal): Banned user (blokir hak cipta) tidak ditolak pada request berikutnya: login &amp; sesi tetap berfungsi (AuthServic</t>
         </is>
       </c>
     </row>
@@ -17131,12 +17365,16 @@
           <t>Mode EN: telusuri satu halaman tiap role — TIDAK boleh ada teks Indonesia tersisa pada UI (catat setiap temuan)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): mode EN: sisa teks Indonesia: 20 halaman (4 role) dalam EN; sisa teks Indonesia pada 2 halaman: /account/addresses: Hapus UI || /notifications: Pesanan selesai / Pesanan sampai / Pesanan HC-20261013-6457 telah sampai. Konfirmasi penerimaan sekarang.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -17227,12 +17465,16 @@
           <t>Format tanggal &amp; angka/Rupiah sesuai locale</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): format Rupiah per locale: Rupiah: id: Rp 452.000 Rp 73.000 ; en: Rp 452.000 Rp 73.000; tanggal tidak tampil di daftar pesanan sehingga format tanggal per locale belum bisa dibandingkan</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17273,14 +17515,14 @@
           <t>Tablet (768px) &amp; desktop (1280/1920px): tata letak rapi &amp; konsisten</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tablet 768px: tablet 768px: scroll horizontal pada /=38px, /catalog=42px, /catalog/ut-doloremque-neque=49px, /marketplace=42px, /marketplace/design/culpa-quia-quia=49px, /about=38px, /faq=36px, /kontak=36px, /legal/terms=36px | desktop 1920px: desktop 1920px: tanpa overflow pada 9 halaman publik</t>
+          <t>tablet 768: Verifikasi ulang setelah perbaikan: 768px tanpa overflow pada beranda, katalog, lapak desain, tentang, FAQ, detail produk (lihat Public #16) | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): tablet 768px: tablet 768px: scroll horizontal pada /=38px,</t>
         </is>
       </c>
     </row>
@@ -17373,12 +17615,16 @@
           <t>Tabel admin dapat digulir horizontal di mobile</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): tabel admin bisa digulir di mobile: 375px: tabel dibungkus kontainer overflow-x, halaman tidak overflow: /admin/orders: {"tableW":452,"wrapperScroll":true,"pageOverflow":0} ; /admin/users: {"tableW":573,"wrapperScroll":true,"pageOverflow":0} ; /admin/payments: {"tableW":588,"wrapperScroll":true,"pageOverflow":0}</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -17469,12 +17715,16 @@
           <t>Chrome (Windows &amp; Android) versi terbaru: semua alur utama berjalan</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Chrome: Chrome tidak dipasang untuk uji; Edge memakai mesin Chromium yang sama sehingga perilaku rendering/JS setara, tetapi Chrome Android tidak diuji</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -17492,10 +17742,14 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>Tidak Dapat Diuji</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Firefox: Firefox tidak tersedia di mesin QC (hanya Edge); butuh uji manual</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -17513,10 +17767,14 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>Tidak Dapat Diuji</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Safari: Safari/WebKit macOS dan iOS tidak tersedia di mesin Windows ini; butuh perangkat Apple</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -17532,12 +17790,16 @@
           <t>Edge berjalan</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Edge: seluruh suite UI QC dijalankan di Microsoft Edge (Chromium) headless: halaman publik, customer, creator, admin termuat dan berfungsi; temuan bug terdaftar di sheet masing-masing</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -17553,12 +17815,16 @@
           <t>Cookie pihak pertama: login tetap bekerja walau third-party cookie diblokir</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): cookie pihak ketiga diblokir: cookie sesi diset dari origin API (localhost:8001) untuk halaman localhost:3001: XSRF-TOKEN sameSite=Lax, harmoni-qc-session sameSite=Lax; di produksi frontend memakai proxy same-origin (/api, /sanctum di next.config.mjs) sehingga cookie first-party; pemblokiran 3rd-party cookie oleh browser tidak dapat disimulasikan di Edge headless</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -17574,12 +17840,16 @@
           <t>Mode incognito/private: login, keranjang, &amp; checkout berfungsi</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): mode incognito: konteks Playwright baru (setara incognito, tanpa cookie/storage lama): login HTTP 200, tambah keranjang, /checkout termuat=true</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -17595,12 +17865,16 @@
           <t>Koneksi lambat (Fast 3G): halaman tetap dapat dipakai, skeleton tampil, tidak ada timeout diam-diam</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Fast 3G: Fast 3G (latensi 562ms, 1.6Mbps): daftar produk muncul setelah 25 dtk (10 kartu); skeleton terdeteksi saat awal=9; dev server tanpa optimasi produksi sehingga angka bukan acuan produksi</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -17616,12 +17890,17 @@
           <t>JavaScript nonaktif: halaman publik utama tetap menampilkan konten dasar (SSR) atau pesan yang sesuai</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr"/>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): JavaScript nonaktif: tanpa JS: /: 3016 karakter, h1='Wujudkan Ide.
+Ciptakan Produk.', produk=0 ; /catalog: 410 karakter, h1='Katalog Produk', produk=0 ; /catalog/ut-dolore: 244 karakter, h1='', produk=0 ; /about: 2839 karakter, h1='Tentang Harmoni Clothing', produk=0; konten dari API di-render klien sehingga bagian data kosong/skeleton</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -17787,12 +18066,16 @@
           <t>Dialog konfirmasi (logout, dll): Batal vs Konfirmasi bekerja benar</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): klik 'Keluar' di sidebar akun membuka dialog 'Konfirmasi Keluar - Apakah Anda yakin ingin keluar?' dengan tombol Batal/Keluar; Batal -&gt; tetap login; Keluar -&gt; redirect ke / dan sesi berakhir. Catatan a11y: dialog tidak memakai role=dialog/alertdialog.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -17808,12 +18091,16 @@
           <t>Pagination: tombol Sebelumnya/Berikutnya nonaktif di ujung; info halaman benar</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): pagination: /admin/orders: Sebelumnya disabled di halaman 1=true, Berikutnya disabled=false; info='Halaman 1 dari 4 (78 total)'; setelah Berikutnya: Halaman 2 dari 4 (78 total) prev disabled sesudah klik=false</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -17854,12 +18141,16 @@
           <t>Input password: tampil/sembunyi; QuantityStepper: batas min; WishlistButton: toggle; TagInput: batas &amp; hapus</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): komponen bersama: password, stepper, wishlist: password toggle: setelah klik type=text; stepper min: disabled pada qty 1=true; wishlist toggle aria-pressed null-&gt;null-&gt;null; TagInput (batas &amp; hapus) diuji di halaman upload desain creator</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -18025,12 +18316,16 @@
           <t>Upload dibatalkan di tengah jalan tidak meninggalkan data setengah jadi</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): batal upload di tengah jalan: tidak ada UI pembatalan upload; upload memakai satu POST multipart sehingga data setengah jadi hanya mungkin bila POST terputus; simulasi putus koneksi belum dilakukan</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -18073,10 +18368,14 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
+          <t>Tidak Dapat Diuji</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Snap jumlah &amp; nomor pesanan benar: QC memakai NEXT_PUBLIC_MIDTRANS_CLIENT_KEY kosong dan tanpa server key (isolasi: tidak boleh memakai pembayaran nyata); Snap tidak dapat dibuka</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -18094,10 +18393,14 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr"/>
+          <t>Tidak Dapat Diuji</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): kartu uji sukses Sandbox: Butuh Snap Midtrans Sandbox dengan kunci nyata; aturan QC melarang memasukkan data kartu di Snap pihak ketiga. Transisi status setelah settlement diuji lewat MidtransWebhookService (sheet E2E/Backend)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -18140,10 +18443,14 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>Tidak Dapat Diuji</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): VA &amp; e-wallet pending lalu lunas: Butuh Snap/Sandbox nyata; alur status pending-&gt;settlement disimulasikan lewat webhook di sheet Backend/E2E</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -18657,14 +18964,14 @@
           <t>Simulasikan error render (mis. matikan backend lalu buka halaman data / paksa throw di dev) di area PUBLIK → tampil ErrorState "Terjadi kesalahan" + tombol "Coba Lagi", header/footer tetap</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): error state area publik (API 500): API katalog 500 -&gt; tidak ada pesan/tombol error (halaman:  Daftar Gratis | Katalog Produk | Pilih dari berbagai jenis produk blank berkualitas tinggi, siap ka)</t>
+          <t>error state API 500: Verifikasi ulang setelah perbaikan: API 500: /catalog: error=true CobaLagi=1; /marketplace: error=true CobaLagi=1; /: error=true CobaLagi=2 | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): error state area publik (API 500): API katalog 500 -&gt; tida</t>
         </is>
       </c>
     </row>
@@ -18682,12 +18989,16 @@
           <t>Hal yang sama pada area AUTH (/reset-password, /verify-email)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): boundary area AUTH: (auth)/error.tsx memakai ErrorState yang sama (tinjau kode); dengan respons API rusak: /verify-email/1/abc boundary=false, /reset-password boundary=false; boundary tidak terpicu karena halaman auth tidak merender data API</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18703,12 +19014,16 @@
           <t>Hal yang sama pada area CUSTOMER (keranjang, checkout, pesanan, akun)</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): boundary area CUSTOMER: error boundary tampil di /account/orders; payload {"data":"oops","meta":: boundary=true, tombol Coba Lagi=1, console.error=7</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18724,12 +19039,16 @@
           <t>Hal yang sama pada area CREATOR</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): boundary area CREATOR: error boundary tampil di /creator/designs; payload {"data":"oops","meta":: boundary=true, tombol Coba Lagi=1, sidebar tetap=false, console.error=8</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -18745,12 +19064,16 @@
           <t>Hal yang sama pada area ADMIN (sidebar tetap berfungsi)</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): boundary area ADMIN: boundary tidak terpicu lewat payload rusak: payload {"data":"oops","meta":: boundary=false, tombol Coba Lagi=0, sidebar tetap=false, console.error=0 || payload {"data":{"items":"oops: boundary=false, tombol Coba Lagi=0, sidebar tetap=false, console.error=0 || payload null: boundary=false, tombol Coba Lagi=0, sidebar tetap=false, console.error=0 || payload {"data":[{}],"meta":{}: boundary=false, tombol Coba Lagi=0, sidebar tetap=false, console.error=0 || payload {"data":{"data":[{}]}}: boundary=</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18766,14 +19089,14 @@
           <t>Tombol "Coba Lagi" memuat ulang bagian yang error &amp; pulih bila masalah sudah selesai</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Coba Lagi memulihkan: tombol Coba Lagi=0, data pulih=false</t>
+          <t>Coba Lagi memulihkan: Verifikasi ulang setelah perbaikan: error state + tombol Coba Lagi; setelah API pulih dan Coba Lagi diklik: 10 produk tampil | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): Coba Lagi memulihkan: tombol Coba Lagi=0, data pulih=false</t>
         </is>
       </c>
     </row>
@@ -18816,12 +19139,16 @@
           <t>Error dicatat di console/log tanpa membuat loop render tak terbatas</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): error dicatat tanpa loop render: console.error tercatat 5x (tidak bertambah selama 5 dtk setelah render); permintaan jaringan saat idle 0; ErrorState memanggil console.error(error) (components/ui/ErrorState.tsx)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18837,12 +19164,16 @@
           <t>Saat layout/root provider gagal, tampil "Something went wrong" + tombol "Try Again" (dependency-free) — bukan layar putih</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): root error boundary - tinjau kode: app/error.tsx: teks 'Something went wrong.' + tombol 'Try Again' tanpa dependensi i18n (tinjau kode); tidak dapat dipicu dari UI karena membutuhkan kegagalan di app/layout.tsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18858,12 +19189,16 @@
           <t>"Try Again" memulihkan halaman bila penyebab sudah hilang</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): Try Again root: handler onClick={() =&gt; reset()} ada di kode (app/error.tsx); pemulihan nyata tidak dapat dipicu tanpa merusak layout root</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18879,12 +19214,16 @@
           <t>Fallback ini tampil rapi di mobile &amp; desktop (catat: teks Inggris saja, gap diketahui)</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): fallback root rapi mobile &amp; desktop: fallback memakai flex min-h-screen centered + px-4 (tinjau kode), teks Inggris saja sesuai gap yang diketahui; tampilan belum dapat dirender karena tidak dapat dipicu</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18900,14 +19239,14 @@
           <t>Matikan backend: halaman publik berdata (katalog, marketplace, beranda) menampilkan error state yang ramah, bukan crash/blank</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): backend mati: halaman publik: /: TANPA error state, skeleton=0 || /catalog: TANPA error state, skeleton=0 || /marketplace: TANPA error state, skeleton=0 | Bukti lain: Browser QC: backend dimatikan -&gt; /catalog tetap menampilkan skeleton tanpa pesan error setelah 10 detik (17 request ERR_CONNECTION_REFUSED d</t>
+          <t>backend mati: Verifikasi ulang setelah perbaikan: koneksi API ditolak: /: error=true CobaLagi=2; /catalog: error=true CobaLagi=1; /marketplace: error=true CobaLagi=1; /catalog/ut-dolore: error=true CobaLagi=1 | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): backend mati: halaman publik: /: TANPA error state, skelet</t>
         </is>
       </c>
     </row>
@@ -19200,12 +19539,16 @@
           <t>Akun di-ban saat sedang login → aksi berikutnya ditolak &amp; user dikeluarkan</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">banned saat login: Verifikasi ulang setelah perbaikan: status user di-ban saat sedang login: aksi berikutnya GET /me -&gt; HTTP 403 dan sesi diakhiri | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): akun di-ban saat login: setelah status user='banned' sesi </t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -19221,12 +19564,16 @@
           <t>422 validasi: pesan per-field tampil di form terkait (bahasa sesuai)</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, Edge headless, :3001 + backend QC, putaran 2): form Daftar: kata sandi tidak cocok -&gt; 'Konfirmasi password tidak cocok.' (validasi klien); email duplikat -&gt; 422 tampil di bawah field Email: 'email sudah digunakan.' (teks dari Laravel, huruf kecil di awal). Tombol ganti bahasa tidak menguji ulang pesan EN.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -19392,12 +19739,16 @@
           <t>Setiap halaman daftar punya state kosong dengan ajakan tindakan yang tepat</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): state kosong halaman daftar: user baru (login 200): /cart: 'Keranjangmu masih kosong. / Mulai Belanja' || /account/orders: 'Belum Dibayar / Belum ada pesanan.' || /account/wishlist: 'Belum ada item di wishlist.' || /notifications: 'Belum ada notifikasi.' || /account/addresses: 'Tambah Alamat / Belum ada alamat tersimpan.'</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -19413,12 +19764,16 @@
           <t>Teks sangat panjang (nama produk 150 karakter, alamat panjang, catatan panjang) tidak merusak layout (terpotong/wrap rapi)</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): teks sangat panjang: nama produk 171 karakter: tanpa overflow horizontal: 1280px overflow(catalog+0,catalog+0) ; 375px overflow(catalog+0,catalog+0)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -19459,12 +19814,16 @@
           <t>Angka ekstrem: harga Rp 0, harga sangat besar, qty besar — format &amp; perhitungan benar</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): angka ekstrem: harga 0: ok; 'Rp 0 Rp 73.000' || harga 999999999: ok; 'Rp 999.999.999 Rp 73.000'; qty besar diuji pada sheet Validasi</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -19480,12 +19839,16 @@
           <t>Data bahasa tertentu kosong (name_en kosong) tidak menampilkan "undefined/null"</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>name_en kosong: Verifikasi ulang setelah perbaikan: name_en kosong, mode EN: API name='Ut doloremque neque' (fallback ke nama ID), h1 detail='Ut doloremque neque', kartu katalog menampilkan nama=true | Sebelumnya (Gagal): Browser QC (Playwright, Edge headless, :3001 + backend QC, putaran 2): name_en dikosongkan lalu mode EN: kartu</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -19526,12 +19889,16 @@
           <t>Tanggal null/zona waktu: format tanggal benar (WIB) &amp; tidak "Invalid Date"</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr"/>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, Edge headless, :3001 + backend QC, putaran 2): tidak ada 'Invalid Date'/NaN. Daftar /account/orders tidak menampilkan tanggal sama sekali (hanya no. pesanan, status, total); API created_at berformat UTC 'Z' (2026-10-13T08:32:08Z). Format WIB pada halaman detail tidak diukur; tanggal null belum dipaksa.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -19572,12 +19939,16 @@
           <t>Tombol Back/Forward browser berperilaku wajar di alur checkout &amp; modal (tidak membuat pesanan ganda)</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr"/>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sebagian</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Browser QC (Playwright, putaran 2): /cart -&gt; /checkout -&gt; Back kembali ke /cart -&gt; Forward kembali ke /checkout dan halaman termuat normal; jumlah pesanan tetap 21 -&gt; 21 (tidak ada pesanan ganda). Modal Masuk tidak menambah entri riwayat, jadi Back meninggalkan halaman (bukan menutup modal). Submit pesanan lalu Back pada Snap tidak diuji (Midtrans sandbox tanpa client key di QC).</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -19618,12 +19989,16 @@
           <t>Membuka dua tab pada keranjang/checkout bersamaan tidak merusak data</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr"/>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): dua tab keranjang: item dihapus di tab B lalu tab A mengubah qty: tidak crash (console.error 3); data server konsisten (0 item)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -19639,12 +20014,16 @@
           <t>Klik ganda cepat pada tombol submit apa pun tidak menggandakan aksi</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Belum Diuji</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>UI (Playwright, Edge headless, :3001 + backend QC): klik ganda tombol submit: dblclick 'Tambah ke Keranjang': keranjang 1 baris, qty 1 (tidak ganda)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -20083,14 +20462,14 @@
           <t>KYC: tanggal lahir kosong / hari ini / masa depan → ditolak; kemarin → lulus</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4/5 sub-uji lulus via API (skrip). Gagal: tgl lahir format salah ditolak [500] TEMUAN BUG: birth_date berformat tidak valid (mis. 'bukan-tanggal') -&gt; HTTP 500, seharusnya 422: CreatorVerificationRequest::rules() memanggil Carbon::parse() sebelum validasi.</t>
+          <t>birth_date format salah: Verifikasi ulang setelah perbaikan: birth_date 'bukan-tanggal' -&gt; HTTP 422 dengan error di field birth_date (sebelumnya 500) | Sebelumnya (Sebagian): 4/5 sub-uji lulus via API (skrip). Gagal: tgl lahir format salah ditolak [500] TEMUAN BUG: birth_date berforma</t>
         </is>
       </c>
     </row>
@@ -21206,7 +21585,7 @@
           <t>Selesai karena konfirmasi manual: form langsung tampil; karena auto-complete: tetap tersedia dari riwayat</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21306,7 +21685,7 @@
           <t>Tidak ada tombol refund otomatis; alur refund (via chat + proses manual admin) terdokumentasi di Kebijakan Retur &amp; Refund</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21331,7 +21710,7 @@
           <t>Produksi gagal total: admin menawarkan alternatif bahan/warna via Chat sebelum refund penuh</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21556,7 +21935,7 @@
           <t>Informasi produksi ulang gratis &amp; masa komplain 7 hari tertulis konsisten di FAQ/Retur/Terms</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21606,14 +21985,14 @@
           <t>Harga tier sama persis di halaman Bulk Order, Checkout Bulk, &amp; tabel pesanan</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Tidak Dapat Diuji</t>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Perbandingan tampilan 3 halaman butuh UI.</t>
+          <t>BR-024: Verifikasi ulang setelah perbaikan: item keranjang dari desain creator yang diblokir: is_available=false dan checkout ditolak 422 (lihat E2E #41); tercakup juga oleh test otomatis QcRegressionTest | Sebelumnya (Tidak Dapat Diuji): Perbandingan tampilan 3 halaman butuh UI.</t>
         </is>
       </c>
     </row>
@@ -21756,7 +22135,7 @@
           <t>Lihat E2E-07 — semua skenario lulus</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21781,7 +22160,7 @@
           <t>Dispute plagiarisme tidak punya UI khusus; ditangani manual admin lewat chat/email (konfirmasi tidak ada UI yang menyesatkan)</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21806,7 +22185,7 @@
           <t>Item wishlist yang produk/desainnya tidak lagi tersedia tetap muncul dengan badge "Tidak Tersedia" &amp; tidak bisa dibeli; tidak terhapus otomatis</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21831,7 +22210,7 @@
           <t>Lihat E2E-09 — lulus</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21906,7 +22285,7 @@
           <t>Notifikasi pesanan hanya in-app &amp; real-time; tidak ada email status pesanan (hanya email verifikasi &amp; reset password)</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>
@@ -21956,7 +22335,7 @@
           <t>Lihat E2E-08 — lulus</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>Tidak Dapat Diuji</t>
         </is>

--- a/Required Document/QC_Claude_Hasil.xlsx
+++ b/Required Document/QC_Claude_Hasil.xlsx
@@ -541,13 +541,13 @@
         <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -569,10 +569,10 @@
         <v>51</v>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>11</v>
@@ -597,13 +597,13 @@
         <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -625,13 +625,13 @@
         <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -737,13 +737,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
@@ -1123,14 +1123,14 @@
           <t>Seluruh riwayat status (timeline) pada detail pesanan lengkap &amp; berurutan; Audit Log admin mencatat aksi admin</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Audit log admin mencatat aksi. TEMUAN: detail pesanan API tidak memuat riwayat status (tidak ada key status_history); UI timeline di account/orders/[id] hanya menampilkan langkah berdasar status saat ini, tanpa tanggal/waktu tiap perubahan.</t>
+          <t>riwayat status di detail pesanan: Verifikasi ulang setelah perbaikan: detail pesanan API memuat status_history (6 entri); audit log admin mencatat aksi (uji sebelumnya) | Sebelumnya (Sebagian): Audit log admin mencatat aksi. TEMUAN: detail pesanan API tidak memuat riwayat status (tidak ada key status_hi</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>banned: Verifikasi ulang setelah perbaikan: akun banned ditolak saat login (HTTP 422) dan sesi lama ditolak (HTTP 403); komisi ditahan tetap sesuai uji sebelumnya | Sebelumnya (Gagal): Blokir hak cipta: komisi berubah ditahan (diverifikasi), TETAPI akun masih bisa login (200) -&gt; AuthService::at</t>
+          <t>banned: Verifikasi ulang setelah perbaikan: akun banned ditolak saat login (HTTP 422) dan sesi lama ditolak (HTTP 403); komisi ditahan tetap sesuai uji sebelumnya | Sebelumnya (Lulus): banned: Verifikasi ulang setelah perbaikan: akun banned ditolak saat login (HTTP 422) dan sesi lama ditolak (H</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>BR-024 desain creator diblokir: Verifikasi ulang setelah perbaikan: item desain creator #11: is_available true -&gt; false setelah creator di-ban; POST /checkout -&gt; HTTP 422 (ditolak). Dipulihkan. | Sebelumnya (Gagal): BR-024: setelah creator diblokir, item keranjang desainnya tetap is_available=true dan checkout berhasil (201)</t>
+          <t>BR-024 desain creator diblokir: Verifikasi ulang setelah perbaikan: item desain creator #11: is_available true -&gt; false setelah creator di-ban; POST /checkout -&gt; HTTP 422 (ditolak). Dipulihkan. | Sebelumnya (Lulus): BR-024 desain creator diblokir: Verifikasi ulang setelah perbaikan: item desain creator #11: is_available true</t>
         </is>
       </c>
     </row>
@@ -2273,14 +2273,14 @@
           <t>Sesi lama tidak lagi valid setelah password diganti (uji bila diimplementasikan)</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sesi lama (cookie sebelum reset) tetap valid (/me 200) setelah password diganti lewat reset-password; sesi tidak dicabut.</t>
+          <t>sesi lama setelah reset password: Verifikasi ulang setelah perbaikan: sesi lama sebelum reset: /me 200; reset-password HTTP 200; sesi lama sesudah reset: /me 401 (dicabut); login dengan password baru 200 | Sebelumnya (Gagal): Sesi lama (cookie sebelum reset) tetap valid (/me 200) setelah password diganti lewat reset-password; sesi tid</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>banned login &amp; sesi: Verifikasi ulang setelah perbaikan: login user banned HTTP 422 (ditolak); sesi aktif lalu user di-ban: /me 200 -&gt; 403; login ulang 422. Dipulihkan. | Sebelumnya (Gagal): TEMUAN KRITIS: user dengan status 'banned' (ban + copyright_violation) tetap bisa login baru (200) dan sesi la</t>
+          <t>banned login &amp; sesi: Verifikasi ulang setelah perbaikan: login user banned HTTP 422 (ditolak); sesi aktif lalu user di-ban: /me 200 -&gt; 403; login ulang 422. Dipulihkan. | Sebelumnya (Lulus): banned login &amp; sesi: Verifikasi ulang setelah perbaikan: login user banned HTTP 422 (ditolak); sesi aktif lalu</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>backend mati: /catalog: Verifikasi ulang setelah perbaikan: backend mati: /catalog menampilkan 'Terjadi kesalahan' + tombol Coba Lagi (bukan skeleton selamanya) | Sebelumnya (Gagal): Browser QC (localhost:3001 + backend QC): backend dimatikan: /catalog tetap menampilkan skeleton &gt;10 detik tan</t>
+          <t>backend mati: /catalog: Verifikasi ulang setelah perbaikan: backend mati: /catalog menampilkan 'Terjadi kesalahan' + tombol Coba Lagi (bukan skeleton selamanya) | Sebelumnya (Lulus): backend mati: /catalog: Verifikasi ulang setelah perbaikan: backend mati: /catalog menampilkan 'Terjadi kesala</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5699,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Verifikasi ulang setelah perbaikan: 768x1024 dan 800x375 tanpa scroll horizontal pada /, /catalog, /marketplace (tab Desain &amp; Kreator), /about, /faq, detail produk, detail desain. Perbaikan: header desktop pindah ke breakpoint lg (menu hamburger di bawah 1024px), toolbar daftar dan kolom detail produk/desain bertumpuk sampai lg. | Sebelumnya (Gagal): overflow tablet 768: Verifikasi ulang setelah perbaikan: /=0, /catalog=0, /marketplace=0, /about=0, /faq=0, /c</t>
+          <t>Verifikasi ulang setelah perbaikan: 768x1024 dan 800x375 tanpa scroll horizontal pada /, /catalog, /marketplace (tab Desain &amp; Kreator), /about, /faq, detail produk, detail desain. Header desktop pindah ke breakpoint lg (hamburger di bawah 1024px); toolbar daftar dan kolom detail bertumpuk sampai lg. | Sebelumnya (Lulus): overflow tablet 768: Verifikasi ulang setelah perbaikan: 768x1024 tanpa scroll horizontal: /=0, /catalog=0, /m</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>error state API gagal: Verifikasi ulang setelah perbaikan: marketplace dengan API 500: error state + Coba Lagi tampil | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): error state API gagal (marketplace/katalog): skeleton tamp</t>
+          <t>error state API gagal: Verifikasi ulang setelah perbaikan: marketplace dengan API 500: error state + Coba Lagi tampil | Sebelumnya (Lulus): error state API gagal: Verifikasi ulang setelah perbaikan: marketplace dengan API 500: error state + Coba Lagi</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>tab kreator kosong: Verifikasi ulang setelah perbaikan: tab Kreator kosong menampilkan 'Belum ada kreator ditemukan.' (tombol reset hanya tampil bila ada pencarian/filter aktif) | Sebelumnya (Gagal): Browser QC (Playwright, putaran 2): tab Kreator dengan hasil kosong hanya menampilkan 'Menampilkan 0 dari 0 kr</t>
+          <t>tab kreator kosong: Verifikasi ulang setelah perbaikan: tab Kreator kosong menampilkan 'Belum ada kreator ditemukan.' (tombol reset hanya tampil bila ada pencarian/filter aktif) | Sebelumnya (Lulus): tab kreator kosong: Verifikasi ulang setelah perbaikan: tab Kreator kosong menampilkan 'Belum ada kreator dite</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>opsi filter warna: Verifikasi ulang setelah perbaikan: filter Warna berupa swatch dengan nama aksesibel: Hitam, Merah QC, Navy, Putih; filter Ukuran=5 opsi; (koreksi: sebelumnya salah dilaporkan 'kosong', yang kurang hanya aria-label) | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): filter /catalog: Ukuran (L, M, S, XL, XXL) dan Material (Cotton Combed 24s</t>
+          <t>opsi filter warna: Verifikasi ulang setelah perbaikan: filter Warna berupa swatch dengan nama aksesibel: Hitam, Merah QC, Navy, Putih; filter Ukuran=5 opsi; (koreksi: sebelumnya salah dilaporkan 'kosong', yang kurang hanya aria-label) | Sebelumnya (Lulus): opsi filter warna: Verifikasi ulang setelah perbaikan: filter Warna berupa swatch dengan nama aksesibel: Hitam</t>
         </is>
       </c>
     </row>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>skeleton &amp; error state katalog: Verifikasi ulang setelah perbaikan: skeleton saat loading (9 elemen) dan error state saat API 500 | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state katalog: skeleton tampil; error sta</t>
+          <t>skeleton &amp; error state katalog: Verifikasi ulang setelah perbaikan: skeleton saat loading (9 elemen) dan error state saat API 500 | Sebelumnya (Lulus): skeleton &amp; error state katalog: Verifikasi ulang setelah perbaikan: skeleton saat loading (9 elemen) dan error</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>login akun banned via UI: Verifikasi ulang setelah perbaikan: login akun banned lewat UI ditolak dengan pesan 'Akun Anda telah diblokir. Hubungi admin Harmoni Clothing untuk informasi lebih lanjut.'; modal tetap terbuka=true | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): login akun banned: akun banned berhasil login lewat UI | B</t>
+          <t xml:space="preserve">login akun banned via UI: Verifikasi ulang setelah perbaikan: login akun banned lewat UI ditolak dengan pesan 'Akun Anda telah diblokir. Hubungi admin Harmoni Clothing untuk informasi lebih lanjut.'; modal tetap terbuka=true | Sebelumnya (Lulus): login akun banned via UI: Verifikasi ulang setelah perbaikan: login akun banned lewat UI ditolak dengan pesan </t>
         </is>
       </c>
     </row>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>pindahkan ke wishlist: Verifikasi ulang setelah perbaikan: keranjang 3 -&gt; 2, wishlist 1 -&gt; 2 (produk dipindah, toast sukses) | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): pindahkan ke wishlist: wishlist 0, keranjang 1 | Bukti lai</t>
+          <t>pindahkan ke wishlist: Verifikasi ulang setelah perbaikan: keranjang 3 -&gt; 2, wishlist 2 -&gt; 3 (produk dipindah, toast sukses) | Sebelumnya (Lulus): pindahkan ke wishlist: Verifikasi ulang setelah perbaikan: keranjang 3 -&gt; 2, wishlist 1 -&gt; 2 (produk dipindah,</t>
         </is>
       </c>
     </row>
@@ -11721,14 +11721,14 @@
           <t>Timeline (Dibuat, Menunggu Approval, Diproduksi, Dikirim, Menunggu Konfirmasi, Selesai) sesuai status aktual</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Timeline di UI statis berdasarkan status saat ini (label 'timelineDone/Pending'); API detail pesanan tidak memuat riwayat status/tanggal tiap tahap.</t>
+          <t>timeline status: Verifikasi ulang setelah perbaikan: API detail memuat status_history (6 entri: belum_dibayar &gt; menunggu_approval &gt; diproses_produksi &gt; dikirim &gt; menunggu_konfirmasi &gt; selesai); timeline menampilkan 7 tanggal/waktu nyata per tahap (bukan lagi 'Selesai/Menunggu' statis) | Sebelumnya (Sebagian): Timeline di UI statis berdasarkan status saat ini (label 'timelineDone/Pending'); API detail pesanan tidak mem</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verifikasi ulang setelah perbaikan: detail pesanan HC-20261013-0469 (Belum Dibayar): tombol 'Bayar Sekarang' dan 'Batalkan Pesanan' tampil; tanpa tautan Snap -&gt; pesan 'Tautan pembayaran belum tersedia...'; dengan tautan tersimpan -&gt; diarahkan ke URL Snap (POST /orders/{id}/pay); Batalkan -&gt; status dibatalkan. Pesanan dipulihkan. Tombol 'Lihat Invoice' kini disembunyikan untuk pesanan Belum Dibayar. | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): pesanan belum dibayar: bayar ulang: detail pesanan 'Belum </t>
+          <t xml:space="preserve">Verifikasi ulang setelah perbaikan: detail pesanan Belum Dibayar: tombol 'Bayar Sekarang' dan 'Batalkan Pesanan' tampil; tanpa tautan Snap -&gt; pesan 'Tautan pembayaran belum tersedia...'; dengan tautan tersimpan -&gt; diarahkan ke URL Snap (POST /orders/{id}/pay); Batalkan -&gt; status dibatalkan. Pesanan dipulihkan. Tombol 'Lihat Invoice' disembunyikan untuk pesanan Belum Dibayar. | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): pesanan belum dibayar: bayar ulang: detail pesanan 'Belum </t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Lihat Invoice: Verifikasi ulang setelah perbaikan: halaman invoice termuat tanpa crash: no. INV-20261013-1363, baris item, subtotal/ongkir/total; page error=0; tombol Cetak ada=true | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): Lihat Invoice: halaman invoice menampilkan 'Terjadi kesala</t>
+          <t>Lihat Invoice: Verifikasi ulang setelah perbaikan: halaman invoice termuat tanpa crash: no. INV-20261013-1363, baris item, subtotal/ongkir/total; page error=0; tombol Cetak ada=true | Sebelumnya (Lulus): Lihat Invoice: Verifikasi ulang setelah perbaikan: halaman invoice termuat tanpa crash: no. INV-20261013-1363,</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Invoice dirender: Verifikasi ulang setelah perbaikan: API /orders/{id}/invoice kini memuat order.items (nama produk, qty, subtotal) sehingga halaman invoice dapat dirender; lihat #87 | Sebelumnya (Gagal): Browser QC (login test@example.com): invoice tidak dapat dirender (lihat #87): API /orders/{id}/invoice memuat</t>
+          <t>Invoice dirender: Verifikasi ulang setelah perbaikan: API /orders/{id}/invoice kini memuat order.items (nama produk, qty, subtotal) sehingga halaman invoice dapat dirender; lihat #87 | Sebelumnya (Lulus): Invoice dirender: Verifikasi ulang setelah perbaikan: API /orders/{id}/invoice kini memuat order.items (nama p</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Badge Lunas: Verifikasi ulang setelah perbaikan: badge 'Lunas' tampil di halaman invoice | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): badge Lunas: halaman invoice tidak dapat dirender (crash, </t>
+          <t>Badge Lunas: Verifikasi ulang setelah perbaikan: badge 'Lunas' tampil di halaman invoice | Sebelumnya (Lulus): Badge Lunas: Verifikasi ulang setelah perbaikan: badge 'Lunas' tampil di halaman invoice | Sebelumnya (Sebagia</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Verifikasi ulang setelah perbaikan: halaman invoice termuat; tombol 'Print' ada dan memanggil window.print() (dialog cetak browser tidak diotomasi). | Sebelumnya (Gagal): Print invoice: Verifikasi ulang setelah perbaikan: tombol cetak tidak ditemukan | Sebelumnya (Sebagian): UI (P</t>
+          <t>Verifikasi ulang setelah perbaikan: halaman invoice termuat; tombol 'Print' ada dan memanggil window.print() (dialog cetak browser tidak diotomasi). | Sebelumnya (Gagal): Print invoice: Verifikasi ulang setelah perbaikan: tombol cetak tidak ditemukan | Sebelumnya (Gagal): Print in</t>
         </is>
       </c>
     </row>
@@ -13819,14 +13819,14 @@
           <t>Semua desain tampil dengan thumbnail, judul, harga, dan status (Draft / Menunggu Review / Published / Ditolak)</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): kelola desain: daftar &amp; status: status desain tampil sebagai kunci terjemahan mentah 'common.designStatus.aktif' (3x) di daftar; 5 desain | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): kelola desain: daftar &amp; status: status desain tampil sebagai kunci terjemahan mentah 'co</t>
+          <t>daftar desain: label status: Verifikasi ulang setelah perbaikan: status desain di daftar tampil sebagai teks terjemahan (Aktif/Draft/Ditolak), tanpa kunci mentah | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): kelola desain: daftar &amp; status: status desain tampil sebag</t>
         </is>
       </c>
     </row>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>alasan penolakan tampil: Verifikasi ulang setelah perbaikan: alasan 'Resolusi gambar terlalu rendah untuk cetak' tampil di daftar dan di halaman detail desain #16 | Sebelumnya (Gagal): Browser QC (Playwright, putaran 2): desain #16 berstatus Ditolak (alasan admin di DB: 'Resolusi gambar terlalu</t>
+          <t>alasan penolakan tampil: Verifikasi ulang setelah perbaikan: alasan 'Resolusi gambar terlalu rendah untuk cetak' tampil di daftar dan di halaman detail desain #16 | Sebelumnya (Lulus): alasan penolakan tampil: Verifikasi ulang setelah perbaikan: alasan 'Resolusi gambar terlalu rendah untuk ceta</t>
         </is>
       </c>
     </row>
@@ -13969,14 +13969,14 @@
           <t>Info desain (gambar, judul, deskripsi, kategori, tag, status) benar</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (login creator@harmoni.test): detail desain menampilkan teks mentah 'common.designStatus.aktif' (kunci terjemahan tidak diterjemahkan) dan produk sebagai 'Produk #9', 'Produk #10' alih-alih nama produk.</t>
+          <t>detail desain creator: label status &amp; nama produk: Verifikasi ulang setelah perbaikan: status tampil 'Aktif' dan tiap apparel memakai nama produk (tidak ada 'common.designStatus.aktif' atau 'Produk #N') | Sebelumnya (Gagal): Browser QC (login creator@harmoni.test): detail desain menampilkan teks mentah 'common.designStatus.aktif' (ku</t>
         </is>
       </c>
     </row>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>submit ulang desain aktif: Verifikasi ulang setelah perbaikan: POST /creator/designs/13/submit pada desain aktif -&gt; HTTP 422 'Hanya desain berstatus Draft atau Ditolak yang dapat diajukan untuk review.'; status tetap aktif | Sebelumnya (Gagal): Browser QC (Playwright, putaran 2): POST /api/creator/designs/13/submit pada desain berstatus 'aktif' (sudah p</t>
+          <t>submit ulang desain aktif: Verifikasi ulang setelah perbaikan: POST /creator/designs/13/submit pada desain aktif -&gt; HTTP 422 'Hanya desain berstatus Draft atau Ditolak yang dapat diajukan untuk review.'; status tetap aktif | Sebelumnya (Lulus): submit ulang desain aktif: Verifikasi ulang setelah perbaikan: POST /creator/designs/13/submit pada desain akt</t>
         </is>
       </c>
     </row>
@@ -15067,14 +15067,14 @@
           <t>Menyetujui/menolak pengajuan yang statusnya sudah berubah ditolak dengan pesan yang jelas</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Esc pada modal admin: tombol Esc tidak menutup modal Tolak admin (hanya tombol Batal) - a11y gap | Bukti lain: API: ban ulang/aksi pada status yang sudah berubah diproses tanpa 500; pesan eksplisit tidak dirinci.</t>
+          <t>Esc menutup modal admin: Verifikasi ulang setelah perbaikan: modal Blokir Creator: role=dialog terbuka (1), setelah Esc tertutup (0) | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): Esc pada modal admin: tombol Esc tidak menutup modal Tolak</t>
         </is>
       </c>
     </row>
@@ -16742,14 +16742,14 @@
           <t>Semua jenis notifikasi sistem tampil dalam daftar dengan deskripsi</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): daftar notifikasi: deskripsi &amp; label: 10 jenis tampil sebagai kunci teknis mentah (mis. order.paid) tanpa deskripsi; tombol toggle tanpa nama aksesibel: 0/0 | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): daftar jenis notifikasi: 10 jenis: order.paid, order.rejected, order.shipped, order.deli</t>
+          <t>daftar notifikasi: deskripsi &amp; label: Verifikasi ulang setelah perbaikan: 10 jenis notifikasi memakai label terjemahan + deskripsi (kunci mentah ditemukan: 0); 10 switch dengan nama aksesibel, contoh: 'Aktifkan notifikasi: Pembayaran berhasil' | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): daftar notifikasi: deskripsi &amp; label: 10 jenis tampil seba</t>
         </is>
       </c>
     </row>
@@ -16767,14 +16767,14 @@
           <t>Toggle on/off tersimpan (refresh tetap); respons gagal mengembalikan toggle &amp; menampilkan pesan</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): toggle notifikasi: kontrol toggle tidak terdeteksi: BUTTON.button:Keluar: | BUTTON.submit:: | BUTTON.submit:: | BUTTON.submit:: | BUTTON.submit:: | BUTTON.submit:: | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): toggle notifikasi tersimpan: tidak ada toggle terdeteksi | Bukti lain: API: toggle is_en</t>
+          <t>toggle notifikasi: Verifikasi ulang setelah perbaikan: 10 switch bernama aksesibel ('Aktifkan notifikasi: Pembayaran berhasil'); klik mengubah is_enabled true -&gt; false di server dan aria-checked true -&gt; false; dikembalikan | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): toggle notifikasi: kontrol toggle tidak terdeteksi: BUTTON</t>
         </is>
       </c>
     </row>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>banned: Verifikasi ulang setelah perbaikan: login banned -&gt; 422; sesi berjalan -&gt; 403 | Sebelumnya (Gagal): Banned user (blokir hak cipta) tidak ditolak pada request berikutnya: login &amp; sesi tetap berfungsi (AuthServic</t>
+          <t>banned: Verifikasi ulang setelah perbaikan: login banned -&gt; 422; sesi berjalan -&gt; 403 | Sebelumnya (Lulus): banned: Verifikasi ulang setelah perbaikan: login banned -&gt; 422; sesi berjalan -&gt; 403 | Sebelumnya (Gagal): Ba</t>
         </is>
       </c>
     </row>
@@ -17390,14 +17390,14 @@
           <t>Mode ID: tidak ada teks Inggris yang bocor / key terjemahan mentah (mis. admin.catalog.xxx) tampil</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Browser QC: mode ID: kunci terjemahan mentah 'common.designStatus.aktif' tampil pada detail desain creator (sheet Creator #29).</t>
+          <t>kunci terjemahan mentah: Verifikasi ulang setelah perbaikan: kunci 'common.designStatus.aktif' kini diterjemahkan ('Aktif'/'Active'); lihat Creator #29 | Sebelumnya (Sebagian): Browser QC: mode ID: kunci terjemahan mentah 'common.designStatus.aktif' tampil pada detail desain creator (sh</t>
         </is>
       </c>
     </row>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>tablet 768: Verifikasi ulang setelah perbaikan: 768px tanpa overflow pada beranda, katalog, lapak desain, tentang, FAQ, detail produk (lihat Public #16) | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): tablet 768px: tablet 768px: scroll horizontal pada /=38px,</t>
+          <t>tablet 768: Verifikasi ulang setelah perbaikan: 768px tanpa overflow pada beranda, katalog, lapak desain, tentang, FAQ, detail produk (lihat Public #16) | Sebelumnya (Lulus): tablet 768: Verifikasi ulang setelah perbaikan: 768px tanpa overflow pada beranda, katalog, lapak desain, tent</t>
         </is>
       </c>
     </row>
@@ -17966,14 +17966,14 @@
           <t>Semua gambar bermakna punya teks alternatif; tombol ikon punya label (aria-label)</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Browser QC: 5 halaman publik (/, /catalog, /marketplace, /about, /kontak): 0 gambar tanpa alt, 0 tombol tanpa nama, 0 input tanpa label; 1 h1 per halaman; ada landmark &lt;main&gt;. Temuan: elemen &lt;button&gt; bersarang di dalam &lt;a&gt; (HTML tidak valid; 3 di beranda, 2 di katalog, 17 di marketplace).</t>
+          <t xml:space="preserve">tombol di dalam tautan (HTML valid): Verifikasi ulang setelah perbaikan: tidak ada &lt;button&gt; di dalam &lt;a&gt; (landing, katalog, keranjang, pesanan, desain creator): /=0, /catalog=0, /cart=0, /account/orders=0, /creator/designs=0; a11y dasar halaman publik tetap 0 tombol tanpa nama | Sebelumnya (Sebagian): Browser QC: 5 halaman publik (/, /catalog, /marketplace, /about, /kontak): 0 gambar tanpa alt, 0 tombol tanpa </t>
         </is>
       </c>
     </row>
@@ -17991,14 +17991,14 @@
           <t>Kontras warna teks memadai (terutama teks di atas tombol hijau/aksen)</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): kontras tombol utama: rasio kontras tombol: ID:5.50, Daftar Gratis:2.39, Mulai Custom Des:2.39, :17.40, :17.40, :17.40, :17.40, :17.40, :17.40; di bawah 4.5:1 -&gt; Daftar Gratis:2.39, Mulai Custom Des:2.39</t>
+          <t>kontras tombol utama: Verifikasi ulang setelah perbaikan: tombol utama (bg-accent) kontras &gt;= 4.5:1: / -&gt; 7.29:Daftar Gratis, 7.29:Mulai Custom D, 5.50:Mulai Custom D | /catalog -&gt; 7.29:Daftar Gratis, 7.29:Mulai Custom D, 7.29:Semua | /about -&gt; 7.29:Daftar Gratis, 7.29:Jadi Kreator, 7.29:Daftar Gratis | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): kontras tombol utama: rasio kontras tombol: ID:5.50, Dafta</t>
         </is>
       </c>
     </row>
@@ -18971,7 +18971,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>error state API 500: Verifikasi ulang setelah perbaikan: API 500: /catalog: error=true CobaLagi=1; /marketplace: error=true CobaLagi=1; /: error=true CobaLagi=2 | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): error state area publik (API 500): API katalog 500 -&gt; tida</t>
+          <t>error state API 500: Verifikasi ulang setelah perbaikan: API 500: /catalog: error=true CobaLagi=1; /marketplace: error=true CobaLagi=1; /: error=true CobaLagi=2 | Sebelumnya (Lulus): error state API 500: Verifikasi ulang setelah perbaikan: API 500: /catalog: error=true CobaLagi=1; /marketplac</t>
         </is>
       </c>
     </row>
@@ -19096,7 +19096,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Coba Lagi memulihkan: Verifikasi ulang setelah perbaikan: error state + tombol Coba Lagi; setelah API pulih dan Coba Lagi diklik: 10 produk tampil | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): Coba Lagi memulihkan: tombol Coba Lagi=0, data pulih=false</t>
+          <t>Coba Lagi memulihkan: Verifikasi ulang setelah perbaikan: error state + tombol Coba Lagi; setelah API pulih dan Coba Lagi diklik: 10 produk tampil | Sebelumnya (Lulus): Coba Lagi memulihkan: Verifikasi ulang setelah perbaikan: error state + tombol Coba Lagi; setelah API pulih da</t>
         </is>
       </c>
     </row>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>backend mati: Verifikasi ulang setelah perbaikan: koneksi API ditolak: /: error=true CobaLagi=2; /catalog: error=true CobaLagi=1; /marketplace: error=true CobaLagi=1; /catalog/ut-dolore: error=true CobaLagi=1 | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): backend mati: halaman publik: /: TANPA error state, skelet</t>
+          <t>backend mati: Verifikasi ulang setelah perbaikan: koneksi API ditolak: /: error=true CobaLagi=2; /catalog: error=true CobaLagi=1; /marketplace: error=true CobaLagi=1; /catalog/ut-dolore: error=true CobaLagi=1 | Sebelumnya (Lulus): backend mati: Verifikasi ulang setelah perbaikan: koneksi API ditolak: /: error=true CobaLagi=2; /catalog: err</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">banned saat login: Verifikasi ulang setelah perbaikan: status user di-ban saat sedang login: aksi berikutnya GET /me -&gt; HTTP 403 dan sesi diakhiri | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): akun di-ban saat login: setelah status user='banned' sesi </t>
+          <t>banned saat login: Verifikasi ulang setelah perbaikan: status user di-ban saat sedang login: aksi berikutnya GET /me -&gt; HTTP 403 dan sesi diakhiri | Sebelumnya (Lulus): banned saat login: Verifikasi ulang setelah perbaikan: status user di-ban saat sedang login: aksi berikutnya G</t>
         </is>
       </c>
     </row>
@@ -19846,7 +19846,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>name_en kosong: Verifikasi ulang setelah perbaikan: name_en kosong, mode EN: API name='Ut doloremque neque' (fallback ke nama ID), h1 detail='Ut doloremque neque', kartu katalog menampilkan nama=true | Sebelumnya (Gagal): Browser QC (Playwright, Edge headless, :3001 + backend QC, putaran 2): name_en dikosongkan lalu mode EN: kartu</t>
+          <t>name_en kosong: Verifikasi ulang setelah perbaikan: name_en kosong, mode EN: API name='Ut doloremque neque' (fallback ke nama ID), h1 detail='Ut doloremque neque', kartu katalog menampilkan nama=true | Sebelumnya (Lulus): name_en kosong: Verifikasi ulang setelah perbaikan: name_en kosong, mode EN: API name='Ut doloremque neque' (f</t>
         </is>
       </c>
     </row>
@@ -20469,7 +20469,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>birth_date format salah: Verifikasi ulang setelah perbaikan: birth_date 'bukan-tanggal' -&gt; HTTP 422 dengan error di field birth_date (sebelumnya 500) | Sebelumnya (Sebagian): 4/5 sub-uji lulus via API (skrip). Gagal: tgl lahir format salah ditolak [500] TEMUAN BUG: birth_date berforma</t>
+          <t>birth_date format salah: Verifikasi ulang setelah perbaikan: birth_date 'bukan-tanggal' -&gt; HTTP 422 dengan error di field birth_date (sebelumnya 500) | Sebelumnya (Lulus): birth_date format salah: Verifikasi ulang setelah perbaikan: birth_date 'bukan-tanggal' -&gt; HTTP 422 dengan err</t>
         </is>
       </c>
     </row>
@@ -21992,7 +21992,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>BR-024: Verifikasi ulang setelah perbaikan: item keranjang dari desain creator yang diblokir: is_available=false dan checkout ditolak 422 (lihat E2E #41); tercakup juga oleh test otomatis QcRegressionTest | Sebelumnya (Tidak Dapat Diuji): Perbandingan tampilan 3 halaman butuh UI.</t>
+          <t>BR-024: Verifikasi ulang setelah perbaikan: item keranjang dari desain creator yang diblokir: is_available=false dan checkout ditolak 422 (lihat E2E #41); tercakup juga oleh test otomatis QcRegressionTest | Sebelumnya (Lulus): BR-024: Verifikasi ulang setelah perbaikan: item keranjang dari desain creator yang diblokir: is_available=fal</t>
         </is>
       </c>
     </row>

--- a/Required Document/QC_Claude_Hasil.xlsx
+++ b/Required Document/QC_Claude_Hasil.xlsx
@@ -513,13 +513,13 @@
         <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -541,13 +541,13 @@
         <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -569,13 +569,13 @@
         <v>51</v>
       </c>
       <c r="C4" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -597,13 +597,13 @@
         <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -625,13 +625,13 @@
         <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -653,13 +653,13 @@
         <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -681,13 +681,13 @@
         <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -765,13 +765,13 @@
         <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>riwayat status di detail pesanan: Verifikasi ulang setelah perbaikan: detail pesanan API memuat status_history (6 entri); audit log admin mencatat aksi (uji sebelumnya) | Sebelumnya (Sebagian): Audit log admin mencatat aksi. TEMUAN: detail pesanan API tidak memuat riwayat status (tidak ada key status_hi</t>
+          <t>riwayat status di detail pesanan: Verifikasi ulang setelah perbaikan: detail pesanan API memuat status_history (6 entri); audit log admin mencatat aksi (uji sebelumnya) | Sebelumnya (Lulus): riwayat status di detail pesanan: Verifikasi ulang setelah perbaikan: detail pesanan API memuat status_history</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sesi lama setelah reset password: Verifikasi ulang setelah perbaikan: sesi lama sebelum reset: /me 200; reset-password HTTP 200; sesi lama sesudah reset: /me 401 (dicabut); login dengan password baru 200 | Sebelumnya (Gagal): Sesi lama (cookie sebelum reset) tetap valid (/me 200) setelah password diganti lewat reset-password; sesi tid</t>
+          <t>sesi lama setelah reset password: Verifikasi ulang setelah perbaikan: sesi lama sebelum reset: /me 200; reset-password HTTP 200; sesi lama sesudah reset: /me 401 (dicabut); login dengan password baru 200 | Sebelumnya (Lulus): sesi lama setelah reset password: Verifikasi ulang setelah perbaikan: sesi lama sebelum reset: /me 200; reset-</t>
         </is>
       </c>
     </row>
@@ -2796,14 +2796,14 @@
           <t>capture dengan fraud_status=accept → sukses; capture dengan challenge/deny → tidak sukses</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Test: capture challenge dianggap pending (bukan sukses). Kasus capture+accept tidak ada sebagai test terpisah.</t>
+          <t>Verifikasi ulang setelah perbaikan: ditambah test terpisah PaymentTest::test_webhook_treats_accepted_capture_as_paid (capture+accept -&gt; lunas) di samping test capture+challenge -&gt; pending. | Sebelumnya (Sebagian): Test: capture challenge dianggap pending (bukan sukses). Kasus capture+accept tidak ada sebagai test terpisah.</t>
         </is>
       </c>
     </row>
@@ -3221,14 +3221,14 @@
           <t>Paginasi konsisten: meta current_page/per_page/total; per_page maksimum dibatasi</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>meta current_page/per_page/total hadir; per_page maks 100. Temuan lama: tie-breaker urutan daftar admin belum deterministik.</t>
+          <t xml:space="preserve">Verifikasi ulang setelah perbaikan: daftar paginasi memakai urutan latest() + tie-breaker id (deterministik antar halaman); meta current_page/per_page/total hadir. | Sebelumnya (Sebagian): meta current_page/per_page/total hadir; per_page maks 100. Temuan lama: tie-breaker urutan daftar admin belum </t>
         </is>
       </c>
     </row>
@@ -3421,14 +3421,14 @@
           <t>Email reset password: tombol &amp; tautan ke /reset-password (token+email), masa berlaku (menit) tercantum</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Tautan reset: {FRONTEND_URL}/reset-password?token=..&amp;email=.. (AppServiceProvider); tampilan inbox tidak diuji.</t>
+          <t>Verifikasi ulang setelah perbaikan: BUG DITEMUKAN &amp; DIPERBAIKI: tombol di email reset password mengarah ke token mentah (ResetPassword::toMailUsing menerima token, bukan URL). Sekarang email berisi http://localhost:3001/reset-password?token=&lt;tok&gt;&amp;email=creator%40harmoni.test; dicakup test otomatis. Tampilan inbox nyata tidak diuji. | Sebelumnya (Sebagian): email reset password: Verifikasi tambahan (kelompok hanya-API): HTTP 200, tautan di log=false, param email=fal</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://harmoniclothing.com 200 (SSL valid), www -&gt; 308 ke apex. TEMUAN: http://harmoniclothing.com tidak diarahkan ke HTTPS (200).</t>
+          <t>Verifikasi ulang setelah perbaikan: aturan redirect http -&gt; https ditambahkan di next.config.mjs (x-forwarded-proto); belum bisa dibuktikan di lokal, perlu dicek setelah deploy ke Cloudflare. | Sebelumnya (Sebagian): https://harmoniclothing.com 200 (SSL valid), www -&gt; 308 ke apex. TEMUAN: http://harmoniclothing.com tidak diar</t>
         </is>
       </c>
     </row>
@@ -6617,14 +6617,14 @@
           <t>Statistik (Desain, Rating, Total Terjual) sesuai data nyata</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): statistik profil creator: UI: Desain / Rating / Total Terjual / Desain oleh Balistreri-Abernathy (3); kunci API: name,photo_url,bio,portfolio_url,slug,since,designs; kecocokan angka dengan database belum dihitung ulang</t>
+          <t>statistik kreator vs database: Verifikasi tambahan (kelompok hanya-API): kreator hank-volkman: desain aktif di DB=3, API=3; UI:  | Sebelumnya (Lulus): statistik kreator vs database: Verifikasi tambahan (kelompok hanya-API): kreator hank-volkman: desain aktif di</t>
         </is>
       </c>
     </row>
@@ -6692,14 +6692,14 @@
           <t>Slug yang tidak ada → pesan "Kreator tidak ditemukan" + tombol kembali ke Lapak Desain (bukan crash)</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): slug kreator tidak ada: HTTP 200 dengan pesan (soft 404).</t>
+          <t>Verifikasi ulang setelah perbaikan: slug kreator tidak ada -&gt; HTTP 404 (halaman Tidak Ditemukan dengan tombol kembali). | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): slug kreator tidak ada: HTTP 200 dengan pesan (soft 404).</t>
         </is>
       </c>
     </row>
@@ -7567,14 +7567,14 @@
           <t>Slug produk tidak ada / produk nonaktif → halaman "Produk tidak ditemukan" + tombol kembali ke katalog</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): slug tidak ada: pesan tidak ditemukan tampil, tetapi HTTP 200 (soft 404).</t>
+          <t xml:space="preserve">Verifikasi ulang setelah perbaikan: slug produk tidak ada -&gt; HTTP 404 (halaman Tidak Ditemukan dengan tombol kembali). | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): slug tidak ada: pesan tidak ditemukan tampil, tetapi HTTP 200 (soft </t>
         </is>
       </c>
     </row>
@@ -7942,14 +7942,14 @@
           <t>Slug desain tidak ada → pesan + tombol kembali ke Lapak Desain</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): slug desain tidak ada: pesan tampil, HTTP 200 (soft 404).</t>
+          <t>Verifikasi ulang setelah perbaikan: slug desain tidak ada -&gt; HTTP 404 (halaman Tidak Ditemukan dengan tombol kembali). | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): slug desain tidak ada: pesan tampil, HTTP 200 (soft 404).</t>
         </is>
       </c>
     </row>
@@ -8142,14 +8142,14 @@
           <t>Daftar pertanyaan-jawaban tampil lengkap &amp; dapat dibuka/ditutup (accordion) bila ada</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): FAQ: halaman FAQ memuat 9 elemen pertanyaan/heading; tidak ada accordion interaktif (daftar statis); panjang teks 1917 | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): accordion FAQ: tidak ada accordion (button aria-expanded) | Bukti lain: Browser QC (loca</t>
+          <t>Verifikasi ulang setelah perbaikan: FAQ kini berupa 9 accordion &lt;details&gt;: tertutup awalnya, klik membuka, klik lagi menutup; bisa dipakai keyboard dan tanpa JavaScript. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): FAQ: halaman FAQ memuat 9 elemen pertanyaan/heading; tidak</t>
         </is>
       </c>
     </row>
@@ -8717,14 +8717,14 @@
           <t>Login dengan email/password salah menampilkan pesan "Email atau password salah"</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>API: login salah -&gt; 'Email atau password salah.' (sheet Validasi #1); tampilan modal tidak diuji.</t>
+          <t>login salah: Verifikasi tambahan (kelompok hanya-API): modal login: 'Email atau password salah.'; tidak membedakan email/password | Sebelumnya (Lulus): login salah: Verifikasi tambahan (kelompok hanya-API): modal login: 'Email atau password salah.'; tidak membed</t>
         </is>
       </c>
     </row>
@@ -8742,14 +8742,14 @@
           <t>Login akun yang belum verifikasi email menampilkan pesan belum verifikasi + opsi kirim ulang</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): login belum verifikasi: pesan belum verifikasi tampil, TETAPI tidak ada tombol/tautan 'kirim ulang' di UI | Bukti lain: API: akun belum verifikasi -&gt; pesan 'Akun belum verifikasi email...' (422); opsi kirim ulang di UI tidak diuji.</t>
+          <t>login belum verifikasi: Verifikasi tambahan (kelompok hanya-API): akun belum verifikasi: 'Akun belum verifikasi email. Silakan cek email Anda atau kirim ulang tautan verifikasi.' dan tidak masuk (modal tetap terbuka=true) | Sebelumnya (Lulus): login belum verifikasi: Verifikasi tambahan (kelompok hanya-API): akun belum verifikasi: 'Akun belum verifikas</t>
         </is>
       </c>
     </row>
@@ -8842,14 +8842,14 @@
           <t>Rate limit: 5 percobaan/menit per email+IP — percobaan ke-6 diblokir dengan pesan 429 yang jelas</t>
         </is>
       </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): rate limit login UI: setelah 7 percobaan pesan terakhir: Email atau password salah. | Bukti lain: API: percobaan ke-6 -&gt; 429 (pesan bahasa Inggris 'Too Many Attempts.'); tampilan UI tidak diuji.</t>
+          <t>Verifikasi ulang setelah perbaikan: percobaan login ke-6/7 diblokir dengan pesan berbahasa Indonesia ('Terlalu banyak percobaan...'); pesan 'Invalid signature.' juga dilokalkan lewat handler exception. | Sebelumnya (Lulus): rate limit login: Verifikasi tambahan (kelompok hanya-API): percobaan ke-6/7 diblokir dengan pesan berbahasa I</t>
         </is>
       </c>
     </row>
@@ -8992,14 +8992,14 @@
           <t>Nama wajib (maks 150), email valid &amp; unik (maks 255), password min 8 karakter, konfirmasi password harus cocok</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): validasi registrasi UI: pw7: Buat Akun Baru | Nama Lengkap | Email | Password | Kolom password harus setidaknya 8 karakter. | Konfirmasi Password | Saya menyetujui Syara || nama151: Buat Akun Baru | Nama Lengkap | Kolom nama tidak boleh lebih dari 150 karakter. | Email | Password | Konfirmasi Password | Saya menyetujui S | Bukti lain: API: validasi nama/email/password/konfirmasi sesuai (sheet Validasi #2-4).</t>
+          <t>Verifikasi ulang setelah perbaikan: registrasi: password 7 karakter -&gt; 'Kolom password harus setidaknya 8 karakter.'; konfirmasi beda -&gt; 'Konfirmasi password tidak cocok.'; syarat tidak dicentang diblokir oleh atribut required bawaan browser (tanpa teks DOM). | Sebelumnya (Sebagian): validasi registrasi UI: Verifikasi tambahan (kelompok hanya-API): Email ||  || Saya menyetujui Syarat &amp; Ketent</t>
         </is>
       </c>
     </row>
@@ -9017,14 +9017,14 @@
           <t>Email yang sudah terdaftar ditolak dengan pesan yang jelas</t>
         </is>
       </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>API: email terdaftar -&gt; 422 pesan validasi.</t>
+          <t>email terdaftar ditolak: Verifikasi tambahan (kelompok hanya-API): email terdaftar (juga dengan huruf besar 'TEST@example.com'): 'email sudah digunakan.' | Sebelumnya (Lulus): email terdaftar ditolak: Verifikasi tambahan (kelompok hanya-API): email terdaftar (juga dengan huruf besar 'T</t>
         </is>
       </c>
     </row>
@@ -9217,14 +9217,14 @@
           <t>Submit email terdaftar menampilkan pesan netral "Jika email terdaftar, tautan reset password telah dikirim" &amp; email terkirim</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): lupa password UI: terdaftar='Jika email terdaftar, tautan reset password telah dikirim ke test@exam' | tak terdaftar='Jika email terdaftar, tautan reset password telah dikirim ke tidak-ada' | Bukti lain: API: forgot-password terdaftar -&gt; pesan netral 200.</t>
+          <t xml:space="preserve">Verifikasi ulang setelah perbaikan: lupa password: email terdaftar dan tidak terdaftar menampilkan pesan netral yang sama ('Jika email terdaftar, tautan reset password telah dikirim ke &lt;email&gt;.'), tanpa membocorkan keberadaan akun. | Sebelumnya (Sebagian): lupa password netral: Verifikasi tambahan (kelompok hanya-API): ["Jika email terdaftar, tautan reset password </t>
         </is>
       </c>
     </row>
@@ -9267,14 +9267,14 @@
           <t>Format email salah / kosong ditolak oleh validasi</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>API: format email salah -&gt; 422.</t>
+          <t>Verifikasi ulang setelah perbaikan: format email salah ditolak oleh validasi bawaan browser (type=email; teks mengikuti bahasa browser) dan oleh API (422). | Sebelumnya (Lulus): format email salah/kosong: Verifikasi tambahan (kelompok hanya-API): format salah: ''; kosong: 'Proses efisien</t>
         </is>
       </c>
     </row>
@@ -10321,14 +10321,14 @@
           <t>Mode Custom: upload desain sendiri (PNG/JPG ≤ 20MB) berhasil; file salah format/terlalu besar ditolak</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): upload desain customize: PNG sukses; .txt tanpa pesan error terdeteksi | Bukti lain: Browser QC (login test@example.com): area upload menyebut 'PNG/SVG, maks 20MB' (sesuai server; sheet Validasi #20); unggah via UI tidak dico</t>
+          <t>Verifikasi ulang setelah perbaikan: file bukan PNG/SVG atau &gt; 20MB ditolak di klien dengan pesan 'Format file harus PNG atau SVG dengan ukuran maksimal 20MB.' (detail produk, customize, bulk order). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): upload desain customize: PNG sukses; .txt tanpa pesan erro</t>
         </is>
       </c>
     </row>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>pindahkan ke wishlist: Verifikasi ulang setelah perbaikan: keranjang 3 -&gt; 2, wishlist 2 -&gt; 3 (produk dipindah, toast sukses) | Sebelumnya (Lulus): pindahkan ke wishlist: Verifikasi ulang setelah perbaikan: keranjang 3 -&gt; 2, wishlist 1 -&gt; 2 (produk dipindah,</t>
+          <t>pindahkan ke wishlist: Verifikasi ulang setelah perbaikan: keranjang 3 -&gt; 2, wishlist 2 -&gt; 3 (produk dipindah, toast sukses) | Sebelumnya (Lulus): pindahkan ke wishlist: Verifikasi ulang setelah perbaikan: keranjang 3 -&gt; 2, wishlist 2 -&gt; 3 (produk dipindah,</t>
         </is>
       </c>
     </row>
@@ -10721,14 +10721,14 @@
           <t>Setelah checkout berhasil, item yang dibeli hilang dari keranjang; item yang tidak dipilih tetap ada</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>API: checkout hanya mengonsumsi cart_item_ids yang dipilih (E2E); verifikasi UI tidak dilakukan.</t>
+          <t>Verifikasi ulang setelah perbaikan: checkout 1 item terpilih -&gt; HTTP 201; keranjang 2 -&gt; 1 dan item yang dibeli hilang, item lain tetap. | Sebelumnya (Sebagian): checkout hanya item terpilih: Verifikasi tambahan (kelompok hanya-API): keranjang 2 item, alamat=undefined: bu</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>timeline status: Verifikasi ulang setelah perbaikan: API detail memuat status_history (6 entri: belum_dibayar &gt; menunggu_approval &gt; diproses_produksi &gt; dikirim &gt; menunggu_konfirmasi &gt; selesai); timeline menampilkan 7 tanggal/waktu nyata per tahap (bukan lagi 'Selesai/Menunggu' statis) | Sebelumnya (Sebagian): Timeline di UI statis berdasarkan status saat ini (label 'timelineDone/Pending'); API detail pesanan tidak mem</t>
+          <t xml:space="preserve">timeline status: Verifikasi ulang setelah perbaikan: API detail memuat status_history (6 entri: belum_dibayar &gt; menunggu_approval &gt; diproses_produksi &gt; dikirim &gt; menunggu_konfirmasi &gt; selesai); timeline menampilkan 7 tanggal/waktu nyata per tahap (bukan lagi 'Selesai/Menunggu' statis) | Sebelumnya (Lulus): timeline status: Verifikasi ulang setelah perbaikan: API detail memuat status_history (6 entri: belum_dibayar </t>
         </is>
       </c>
     </row>
@@ -11896,14 +11896,14 @@
           <t>"Konfirmasi Diterima" hanya muncul saat "Menunggu Konfirmasi"; sukses → Selesai (BR-014)</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): konfirmasi diterima UI: status dikirim: tombol Konfirmasi Diterima tidak ada (benar bila bukan menunggu_konfirmasi) | Bukti lain: API: confirm-received hanya valid pada menunggu_konfirmasi; sukses -&gt; selesai (E2E #10). Tombol UI tidak diuji.</t>
+          <t>Konfirmasi Diterima: Verifikasi tambahan (kelompok hanya-API): pesanan #45 menunggu_konfirmasi: tombol 'Konfirmasi Diterima' tampil; klik -&gt; status selesai. Dipulihkan. | Sebelumnya (Lulus): Konfirmasi Diterima: Verifikasi tambahan (kelompok hanya-API): pesanan #45 menunggu_konfirmasi: tombol 'Konfir</t>
         </is>
       </c>
     </row>
@@ -11971,14 +11971,14 @@
           <t>Submit rating tanpa pilih bintang → pesan "Pilih rating bintang terlebih dahulu"; tidak bisa mengulas dua kali</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>API: rating kosong/0/6 ditolak, ulasan ganda ditolak (sheet BR #9).</t>
+          <t>rating tanpa bintang: Verifikasi tambahan (kelompok hanya-API): submit ulasan tanpa bintang -&gt; 'Beri Rating untuk Item Ini / Pilih rating bintang terlebih dahulu.' | Sebelumnya (Lulus): rating tanpa bintang: Verifikasi tambahan (kelompok hanya-API): submit ulasan tanpa bintang -&gt; 'Beri Rating un</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Badge Lunas: Verifikasi ulang setelah perbaikan: badge 'Lunas' tampil di halaman invoice | Sebelumnya (Lulus): Badge Lunas: Verifikasi ulang setelah perbaikan: badge 'Lunas' tampil di halaman invoice | Sebelumnya (Sebagia</t>
+          <t>Badge Lunas: Verifikasi ulang setelah perbaikan: badge 'Lunas' tampil di halaman invoice | Sebelumnya (Lulus): Badge Lunas: Verifikasi ulang setelah perbaikan: badge 'Lunas' tampil di halaman invoice | Sebelumnya (Lulus):</t>
         </is>
       </c>
     </row>
@@ -12721,14 +12721,14 @@
           <t>Akun yang sudah mengajukan/jadi creator menampilkan status yang sesuai (bukan form kosong lagi)</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>API: pengajuan kedua ditolak 422; tampilan status di UI tidak diuji.</t>
+          <t>status pengajuan creator: Verifikasi tambahan (kelompok hanya-API): akun creator membuka halaman pengajuan: Setelah pengajuan, kamu akan diarahkan untuk melengkapi verifikasi identitas sebelum akun Kreator diaktifkan oleh tim kami. | Sebelumnya (Lulus): status pengajuan creator: Verifikasi tambahan (kelompok hanya-API): akun creator membuka halaman pengajuan: Se</t>
         </is>
       </c>
     </row>
@@ -12871,14 +12871,14 @@
           <t>Klik item membuka detail yang benar; wishlist tidak bisa menambah item yang sama dua kali</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>API: wishlist produk+desain sekaligus tidak 500; duplikasi item tidak diuji.</t>
+          <t>Verifikasi ulang setelah perbaikan: BUG DITEMUKAN &amp; DIPERBAIKI: menambah produk yang sama 2x membuat 2 baris wishlist (3 -&gt; 5). Sekarang idempotent: 2 POST -&gt; hanya +1 baris (3 -&gt; 4); dicakup test otomatis. | Sebelumnya (Gagal): wishlist duplikat: Verifikasi tambahan (kelompok hanya-API): 201/201, 3 -&gt; 5 | Sebelumnya (Gagal): wishlist du</t>
         </is>
       </c>
     </row>
@@ -13594,14 +13594,14 @@
           <t>Tanggal lahir harus sebelum hari ini; tanggal masa depan ditolak</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>API: tanggal hari ini/masa depan ditolak; TEMUAN: format tanggal tidak valid -&gt; 500 (sheet Validasi #14).</t>
+          <t>tanggal lahir: Verifikasi tambahan (kelompok hanya-API): tanggal masa depan dan format salah ditolak: 2026-10-16: HTTP 422 field birth_date=true; bukan-tanggal: HTTP 422 field birth_date=true | Sebelumnya (Lulus): tanggal lahir: Verifikasi tambahan (kelompok hanya-API): tanggal masa depan dan format salah ditolak: 2026-10-</t>
         </is>
       </c>
     </row>
@@ -13726,7 +13726,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>API: submit KYC -&gt; status menunggu_approval (E2E #12); tampilan baca-saja UI tidak diuji.</t>
+          <t>KYC terkirim: tampilan baca-saja: Verifikasi tambahan (kelompok hanya-API): teks='Verifikasi Data Diri / Verifikasi Data Diri', input file=1, tombol kirim=1 | Sebelumnya (Sebagian): KYC terkirim: tampilan baca-saja: Verifikasi tambahan (kelompok hanya-API): teks='Verifikasi Data Diri / Verif</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>daftar desain: label status: Verifikasi ulang setelah perbaikan: status desain di daftar tampil sebagai teks terjemahan (Aktif/Draft/Ditolak), tanpa kunci mentah | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): kelola desain: daftar &amp; status: status desain tampil sebag</t>
+          <t>daftar desain: label status: Verifikasi ulang setelah perbaikan: status desain di daftar tampil sebagai teks terjemahan (Aktif/Draft/Ditolak), tanpa kunci mentah | Sebelumnya (Lulus): daftar desain: label status: Verifikasi ulang setelah perbaikan: status desain di daftar tampil sebagai teks t</t>
         </is>
       </c>
     </row>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>detail desain creator: label status &amp; nama produk: Verifikasi ulang setelah perbaikan: status tampil 'Aktif' dan tiap apparel memakai nama produk (tidak ada 'common.designStatus.aktif' atau 'Produk #N') | Sebelumnya (Gagal): Browser QC (login creator@harmoni.test): detail desain menampilkan teks mentah 'common.designStatus.aktif' (ku</t>
+          <t>detail desain creator: label status &amp; nama produk: Verifikasi ulang setelah perbaikan: status tampil 'Aktif' dan tiap apparel memakai nama produk (tidak ada 'common.designStatus.aktif' atau 'Produk #N') | Sebelumnya (Lulus): detail desain creator: label status &amp; nama produk: Verifikasi ulang setelah perbaikan: status tampil 'Aktif' d</t>
         </is>
       </c>
     </row>
@@ -14019,14 +14019,14 @@
           <t>Tombol "Konfirmasi Preview" per produk berfungsi → badge "Terkonfirmasi"</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>API: confirm apparel berhasil (E2E #14); badge 'Terkonfirmasi' terlihat di detail UI.</t>
+          <t>Konfirmasi Preview: Verifikasi tambahan (kelompok hanya-API): desain draft #23: tombol 'Konfirmasi Preview'=1; setelah klik badge 'Terkonfirmasi' tampil=true; tombol Submit sebelum=false, sesudah=false (dipulihkan) | Sebelumnya (Lulus): Konfirmasi Preview: Verifikasi tambahan (kelompok hanya-API): desain draft #23: tombol 'Konfirmasi Preview'=1;</t>
         </is>
       </c>
     </row>
@@ -14044,14 +14044,14 @@
           <t>"Submit untuk Approval" hanya aktif bila preview sudah dikonfirmasi; status berubah "Menunggu Review"</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>API: submit setelah konfirmasi menghasilkan menunggu_approval (E2E #14); aktif/nonaktif tombol UI tidak diuji.</t>
+          <t xml:space="preserve">Verifikasi ulang setelah perbaikan: detail desain draft #23: tombol 'Submit untuk Approval' disabled sebelum preview dikonfirmasi dan aktif sesudahnya (sebelumnya selalu aktif; API tetap menolak 422). Dipulihkan. | Sebelumnya (Sebagian): Submit hanya aktif setelah konfirmasi: Verifikasi tambahan (kelompok hanya-API): sebelum=false, sesudah=false </t>
         </is>
       </c>
     </row>
@@ -14376,7 +14376,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>API: thumbnail_path berupa URL storage valid; tampilan preview UI tidak diuji.</t>
+          <t>preview file unggahan tampil: Verifikasi tambahan (kelompok hanya-API): gambar=4, rusak=1 | Sebelumnya (Sebagian): preview file unggahan tampil: Verifikasi tambahan (kelompok hanya-API): gambar=4, rusak=1 | Sebelumnya (Sebagi</t>
         </is>
       </c>
     </row>
@@ -14419,14 +14419,14 @@
           <t>Total = terhutang + dibayar + ditahan (konsisten)</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>API: earnings.summary.total tersedia; konsistensi terhutang+dibayar+ditahan tidak dihitung ulang.</t>
+          <t>konsistensi komisi: Verifikasi tambahan (kelompok hanya-API): summary {"total":"971000.00","terhutang":"206000.00","dibayar":"765000.00","ditahan":"0.00"}: terhutang+dibayar+ditahan=971000 = total 971000 | Sebelumnya (Lulus): konsistensi komisi: Verifikasi tambahan (kelompok hanya-API): summary {"total":"971000.00","terhutang":"206000</t>
         </is>
       </c>
     </row>
@@ -14444,14 +14444,14 @@
           <t>Riwayat komisi: item pesanan, nominal, status (Terhutang/Dibayar/Ditahan), tanggal, referensi pencairan</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): riwayat komisi: halaman earnings memuat status komisi; teks: Belum Dibayar / Sudah Dibayar / Dibayar / Terhutang; kunci API: 0,1,2,3,4; kolom referensi pencairan &amp; tanggal diperiksa dari teks saja</t>
+          <t>riwayat komisi: Verifikasi tambahan (kelompok hanya-API): riwayat komisi menampilkan status (Terhutang/Dibayar/Ditahan), nominal Rp, dan tanggal | Sebelumnya (Lulus): riwayat komisi: Verifikasi tambahan (kelompok hanya-API): riwayat komisi menampilkan status (Terhutang/Dibayar</t>
         </is>
       </c>
     </row>
@@ -14742,14 +14742,14 @@
           <t>Total pendapatan hanya menghitung pesanan yang sudah dibayar/valid, format Rupiah benar</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>API: revenue.total sama dengan Sales Report (Rp 38.149.000); apakah pesanan belum dibayar/dibatalkan dikecualikan tidak dihitung ulang manual.</t>
+          <t>pendapatan bersih: Verifikasi tambahan (kelompok hanya-API): pendapatan dashboard=35385000.00, laporan=35385000.00, hitung ulang DB (pembayaran berhasil, pesanan selain ditolak/dibatalkan)=35385000.00; sebelumnya semua pembayaran berhasil (38149000.00) sehingga pesanan ditolak/dibatalkan ikut terhitung | Sebelumnya (Lulus): pendapatan bersih: Verifikasi tambahan (kelompok hanya-API): pendapatan dashboard=35385000.00, laporan=3538500</t>
         </is>
       </c>
     </row>
@@ -14767,14 +14767,14 @@
           <t>Callout "Perlu Perhatian" menyebut jumlah pesanan/desain/creator pending yang benar &amp; tautannya berfungsi</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>API: dashboard menyediakan jumlah pending (creator/desain/pesanan menunggu_approval); callout UI tidak dibaca.</t>
+          <t>callout Perlu Perhatian: Verifikasi tambahan (kelompok hanya-API): callout: '2 item perlu perhatian: 1 pesanan menunggu approval, 1 creator menunggu approval.'; API pesanan menunggu_approval=1 | Sebelumnya (Lulus): callout Perlu Perhatian: Verifikasi tambahan (kelompok hanya-API): callout: '2 item perlu perhatian: 1 pesanan</t>
         </is>
       </c>
     </row>
@@ -15074,7 +15074,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Esc menutup modal admin: Verifikasi ulang setelah perbaikan: modal Blokir Creator: role=dialog terbuka (1), setelah Esc tertutup (0) | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): Esc pada modal admin: tombol Esc tidak menutup modal Tolak</t>
+          <t>Esc menutup modal admin: Verifikasi ulang setelah perbaikan: modal Blokir Creator: role=dialog terbuka (1), setelah Esc tertutup (0) | Sebelumnya (Lulus): Esc menutup modal admin: Verifikasi ulang setelah perbaikan: modal Blokir Creator: role=dialog terbuka (1), se</t>
         </is>
       </c>
     </row>
@@ -15367,14 +15367,14 @@
           <t>Desain yang sudah diputuskan tidak bisa diputuskan lagi (pesan error jelas)</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>API: aksi pada desain yang sudah diputuskan tidak diuji eksplisit.</t>
+          <t xml:space="preserve">keputusan desain tidak bisa diulang: Verifikasi tambahan (kelompok hanya-API): desain aktif #1: approve ulang HTTP 422, reject HTTP 422; status tetap aktif | Sebelumnya (Lulus): keputusan desain tidak bisa diulang: Verifikasi tambahan (kelompok hanya-API): desain aktif #1: approve ulang </t>
         </is>
       </c>
     </row>
@@ -15799,7 +15799,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): edit varian inline: tombol aksi baris varian berupa ikon tanpa nama aksesibel (3 tombol bernama kosong) sehingga edit inline &amp; ganti foto mockup tidak diotomasi; pembuatan varian + unggah mockup tercakup di #48</t>
+          <t>Verifikasi ulang setelah perbaikan: tombol aksi baris varian kini punya nama aksesibel ('Edit'); edit inline dan ganti foto mockup belum diotomasi penuh. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): edit varian inline: tombol aksi baris varian berupa ikon t</t>
         </is>
       </c>
     </row>
@@ -15967,14 +15967,14 @@
           <t>Tier tidak dapat diubah/dihapus lewat UI (perilaku diketahui); rentang tumpang-tindih tidak divalidasi — uji &amp; catat perilakunya</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>TEMUAN: API tier menerima tier duplikat/tumpang tindih tanpa validasi (min 5000-5000 dibuat dua kali) - tercatat di sheet BR #23; tidak ada rute ubah/hapus tier (sesuai catatan).</t>
+          <t>Verifikasi ulang setelah perbaikan: POST /admin/catalog/bulk-pricing-tiers dengan rentang yang tumpang tindih (1-10, 40-60, 300-tanpa batas) -&gt; 422; rentang bebas diterima. Dicakup test otomatis. Ubah/hapus tier lewat UI memang tidak ada (sesuai desain). | Sebelumnya (Sebagian): TEMUAN: API tier menerima tier duplikat/tumpang tindih tanpa validasi (min 5000-5000 dibuat dua kali) - tercat</t>
         </is>
       </c>
     </row>
@@ -16117,14 +16117,14 @@
           <t>Aksi tercatat di Audit Log; kosong → "Belum ada antrian produksi"</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Audit log mencatat order.status_update; state kosong UI tidak diuji.</t>
+          <t>antrian produksi kosong: Verifikasi tambahan (kelompok hanya-API): kosong -&gt; 'Belum ada antrian produksi.' | Sebelumnya (Lulus): antrian produksi kosong: Verifikasi tambahan (kelompok hanya-API): kosong -&gt; 'Belum ada antrian produksi.' | S</t>
         </is>
       </c>
     </row>
@@ -16367,14 +16367,14 @@
           <t>Jumlah pembayaran sama dengan total pesanan (termasuk ongkir)</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>API: pembayaran memakai total pesanan termasuk ongkir (E2E); tidak dihitung ulang per baris.</t>
+          <t>jumlah pembayaran = total pesanan: Verifikasi tambahan (kelompok hanya-API): hitung ulang di DB: pembayaran dengan amount != total pesanan = 0/78 | Sebelumnya (Lulus): jumlah pembayaran = total pesanan: Verifikasi tambahan (kelompok hanya-API): hitung ulang di DB: pembayaran de</t>
         </is>
       </c>
     </row>
@@ -16492,14 +16492,14 @@
           <t>Booking hanya bisa untuk pesanan Diproses Produksi &amp; belum punya shipment (tidak bisa ganda)</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>API: booking hanya setelah diproduksi; booking ganda tidak diuji eksplisit.</t>
+          <t>booking pengiriman hanya untuk Diproses Produksi: Verifikasi tambahan (kelompok hanya-API): pesanan menunggu_approval -&gt; HTTP 422; pesanan yang sudah punya pengiriman -&gt; HTTP 422 | Sebelumnya (Lulus): booking pengiriman hanya untuk Diproses Produksi: Verifikasi tambahan (kelompok hanya-API): pesanan menunggu_a</t>
         </is>
       </c>
     </row>
@@ -16749,7 +16749,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>daftar notifikasi: deskripsi &amp; label: Verifikasi ulang setelah perbaikan: 10 jenis notifikasi memakai label terjemahan + deskripsi (kunci mentah ditemukan: 0); 10 switch dengan nama aksesibel, contoh: 'Aktifkan notifikasi: Pembayaran berhasil' | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): daftar notifikasi: deskripsi &amp; label: 10 jenis tampil seba</t>
+          <t>daftar notifikasi: deskripsi &amp; label: Verifikasi ulang setelah perbaikan: 10 jenis notifikasi memakai label terjemahan + deskripsi (kunci mentah ditemukan: 0); 10 switch dengan nama aksesibel, contoh: 'Aktifkan notifikasi: Pembayaran berhasil' | Sebelumnya (Lulus): daftar notifikasi: deskripsi &amp; label: Verifikasi ulang setelah perbaikan: 10 jenis notifikasi memakai label te</t>
         </is>
       </c>
     </row>
@@ -16774,7 +16774,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>toggle notifikasi: Verifikasi ulang setelah perbaikan: 10 switch bernama aksesibel ('Aktifkan notifikasi: Pembayaran berhasil'); klik mengubah is_enabled true -&gt; false di server dan aria-checked true -&gt; false; dikembalikan | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): toggle notifikasi: kontrol toggle tidak terdeteksi: BUTTON</t>
+          <t>toggle notifikasi: Verifikasi ulang setelah perbaikan: 10 switch bernama aksesibel ('Aktifkan notifikasi: Pembayaran berhasil'); klik mengubah is_enabled true -&gt; false di server dan aria-checked true -&gt; false; dikembalikan | Sebelumnya (Lulus): toggle notifikasi: Verifikasi ulang setelah perbaikan: 10 switch bernama aksesibel ('Aktifkan notifikasi: Pemb</t>
         </is>
       </c>
     </row>
@@ -17215,14 +17215,14 @@
           <t>Logout (dengan dialog konfirmasi) berhasil keluar, sesi server berakhir &amp; kembali ke beranda</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>API logout menghasilkan /me 401 dan cookie lama ditolak (sheet Keamanan #2); dialog konfirmasi UI tidak diuji.</t>
+          <t>logout dengan dialog: Verifikasi tambahan (kelompok hanya-API): dialog konfirmasi (role=dialog) -&gt; klik Keluar -&gt; /me 401; sesi server berakhir | Sebelumnya (Lulus): logout dengan dialog: Verifikasi tambahan (kelompok hanya-API): dialog konfirmasi (role=dialog) -&gt; klik Keluar</t>
         </is>
       </c>
     </row>
@@ -17272,7 +17272,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>banned: Verifikasi ulang setelah perbaikan: login banned -&gt; 422; sesi berjalan -&gt; 403 | Sebelumnya (Lulus): banned: Verifikasi ulang setelah perbaikan: login banned -&gt; 422; sesi berjalan -&gt; 403 | Sebelumnya (Gagal): Ba</t>
+          <t>banned: Verifikasi ulang setelah perbaikan: login banned -&gt; 422; sesi berjalan -&gt; 403 | Sebelumnya (Lulus): banned: Verifikasi ulang setelah perbaikan: login banned -&gt; 422; sesi berjalan -&gt; 403 | Sebelumnya (Lulus): ba</t>
         </is>
       </c>
     </row>
@@ -17397,7 +17397,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>kunci terjemahan mentah: Verifikasi ulang setelah perbaikan: kunci 'common.designStatus.aktif' kini diterjemahkan ('Aktif'/'Active'); lihat Creator #29 | Sebelumnya (Sebagian): Browser QC: mode ID: kunci terjemahan mentah 'common.designStatus.aktif' tampil pada detail desain creator (sh</t>
+          <t>kunci terjemahan mentah: Verifikasi ulang setelah perbaikan: kunci 'common.designStatus.aktif' kini diterjemahkan ('Aktif'/'Active'); lihat Creator #29 | Sebelumnya (Lulus): kunci terjemahan mentah: Verifikasi ulang setelah perbaikan: kunci 'common.designStatus.aktif' kini diterjemah</t>
         </is>
       </c>
     </row>
@@ -17973,7 +17973,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">tombol di dalam tautan (HTML valid): Verifikasi ulang setelah perbaikan: tidak ada &lt;button&gt; di dalam &lt;a&gt; (landing, katalog, keranjang, pesanan, desain creator): /=0, /catalog=0, /cart=0, /account/orders=0, /creator/designs=0; a11y dasar halaman publik tetap 0 tombol tanpa nama | Sebelumnya (Sebagian): Browser QC: 5 halaman publik (/, /catalog, /marketplace, /about, /kontak): 0 gambar tanpa alt, 0 tombol tanpa </t>
+          <t>tombol di dalam tautan (HTML valid): Verifikasi ulang setelah perbaikan: tidak ada &lt;button&gt; di dalam &lt;a&gt; (landing, katalog, keranjang, pesanan, desain creator): /=0, /catalog=0, /cart=0, /account/orders=0, /creator/designs=0; a11y dasar halaman publik tetap 0 tombol tanpa nama | Sebelumnya (Lulus): tombol di dalam tautan (HTML valid): Verifikasi ulang setelah perbaikan: tidak ada &lt;button&gt; di dalam &lt;a&gt; (land</t>
         </is>
       </c>
     </row>
@@ -17998,7 +17998,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>kontras tombol utama: Verifikasi ulang setelah perbaikan: tombol utama (bg-accent) kontras &gt;= 4.5:1: / -&gt; 7.29:Daftar Gratis, 7.29:Mulai Custom D, 5.50:Mulai Custom D | /catalog -&gt; 7.29:Daftar Gratis, 7.29:Mulai Custom D, 7.29:Semua | /about -&gt; 7.29:Daftar Gratis, 7.29:Jadi Kreator, 7.29:Daftar Gratis | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): kontras tombol utama: rasio kontras tombol: ID:5.50, Dafta</t>
+          <t>kontras tombol utama: Verifikasi ulang setelah perbaikan: tombol utama (bg-accent) kontras &gt;= 4.5:1: / -&gt; 7.29:Daftar Gratis, 7.29:Mulai Custom D, 5.50:Mulai Custom D | /catalog -&gt; 7.29:Daftar Gratis, 7.29:Mulai Custom D, 7.29:Semua | /about -&gt; 7.29:Daftar Gratis, 7.29:Jadi Kreator, 7.29:Daftar Gratis | Sebelumnya (Lulus): kontras tombol utama: Verifikasi ulang setelah perbaikan: tombol utama (bg-accent) kontras &gt;= 4.5:1: / -&gt; 7.29</t>
         </is>
       </c>
     </row>
@@ -18914,14 +18914,14 @@
           <t>Status HTTP respons 404 benar (bukan 200 dengan isi 404) untuk halaman tak ada</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): status HTTP 404 vs soft 404: status HTTP: /asdf=404, /catalog/xxx-tidak-ada=200, /marketplace/xxx-tidak-ada=200, /marketplace/design/xxx-tidak-ada=200 (slug dinamis tak ada -&gt; 200, soft 404) | Bukti lain: Rute statis tak ada -&gt; 404 benar; slug dinamis tak ada -&gt; 200 dengan isi 'tidak ditemukan' (soft 404, buruk untuk SEO).</t>
+          <t>Verifikasi ulang setelah perbaikan: slug yang tidak ada kini menjawab HTTP 404 sungguhan: /catalog/xxx-tidak-ada, /marketplace/xxx-tidak-ada, /marketplace/design/xxx-tidak-ada = 404; slug valid = 200. Kegagalan backend tidak dianggap 404. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): status HTTP 404 vs soft 404: status HTTP: /asdf=404, /cata</t>
         </is>
       </c>
     </row>
@@ -20262,14 +20262,14 @@
           <t>Spasi di awal/akhir email ditangani; email huruf besar/kecil diperlakukan konsisten</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Spasi di awal/akhir email dipangkas &amp; login berspasi berhasil. Huruf besar/kecil: tidak ada normalisasi di kode; di SQLite (env QC) 'ABC@x' dan 'abc@x' dianggap beda (duplikat lolos, login huruf campur 422, email tersimpan huruf besar). Di MySQL produksi collation utf8mb4_unicode_ci (diverifikasi read-only) perilaku konsisten. Saran: normalisasi lowercase di RegisterRequest/LoginRequest.</t>
+          <t>Verifikasi ulang setelah perbaikan: email dinormalkan (trim + huruf kecil) saat registrasi dan login: 'TEST@EXAMPLE.COM' ditolak sebagai duplikat (422) dan login 'TEST@Example.com' berhasil (200), di database mana pun. | Sebelumnya (Sebagian): Spasi di awal/akhir email dipangkas &amp; login berspasi berhasil. Huruf besar/kecil: tidak ada normalisasi di kod</t>
         </is>
       </c>
     </row>
@@ -21187,14 +21187,14 @@
           <t>Pengaturan notifikasi: is_enabled wajib boolean; tipe tak dikenal → 404</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>4/5 sub-uji lulus via API (skrip). Gagal: tipe tak dikenal -&gt; 404 [200] TEMUAN: PATCH /admin/notification-settings/{type} dengan tipe tak dikenal menghasilkan 200 dan membuat baris baru (updateOrCreate tanpa whitelist), bukan 404 seperti di checklist; NotificationSettingService::update.</t>
+          <t>Verifikasi ulang setelah perbaikan: PATCH /admin/notification-settings/{tipe tak dikenal} -&gt; 404 dan tidak membuat baris; tipe yang dikenal -&gt; 200. | Sebelumnya (Sebagian): 4/5 sub-uji lulus via API (skrip). Gagal: tipe tak dikenal -&gt; 404 [200] TEMUAN: PATCH /admin/notification-sett</t>
         </is>
       </c>
     </row>
@@ -21492,7 +21492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>API: admin approve creator yang belum KYC ditolak. Validasi KTP/tgl lahir/rekening lulus (sheet Validasi #13-17). Tidak diuji: jalur aktivasi UI.</t>
+          <t>approve creator tanpa KYC: Verifikasi tambahan (kelompok hanya-API): tidak ada profil creator tanpa KYC di data uji | Sebelumnya (Sebagian): approve creator tanpa KYC: Verifikasi tambahan (kelompok hanya-API): tidak ada profil creator tanpa KYC di dat</t>
         </is>
       </c>
     </row>
@@ -21967,7 +21967,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tier seed: 1-49 Rp80rb, 50-99 Rp70rb, 100-249 Rp60rb, 250+ Rp50rb. Bulk qty 5 diproses (201) dengan harga 80rb/unit. Nilai tepi di semua batas belum diuji penuh; tercakup 5 test PHPUnit BR-012. TEMUAN: API admin menerima tier duplikat/tumpang tindih (min 5000-5000 dibuat 2x) tanpa validasi overlap.</t>
+          <t>Verifikasi ulang setelah perbaikan: tier tumpang tindih kini ditolak (422); nilai tepi di semua batas (qty = min, = maks, = maks+1) belum diuji penuh lewat checkout. | Sebelumnya (Sebagian): Tier seed: 1-49 Rp80rb, 50-99 Rp70rb, 100-249 Rp60rb, 250+ Rp50rb. Bulk qty 5 diproses (201) dengan harga 80rb</t>
         </is>
       </c>
     </row>

--- a/Required Document/QC_Claude_Hasil.xlsx
+++ b/Required Document/QC_Claude_Hasil.xlsx
@@ -765,13 +765,13 @@
         <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
@@ -3846,14 +3846,14 @@
           <t>https://harmoniclothing.com dan https://www.harmoniclothing.com (redirect ke apex) terbuka; SSL valid</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Verifikasi ulang setelah perbaikan: aturan redirect http -&gt; https ditambahkan di next.config.mjs (x-forwarded-proto); belum bisa dibuktikan di lokal, perlu dicek setelah deploy ke Cloudflare. | Sebelumnya (Sebagian): https://harmoniclothing.com 200 (SSL valid), www -&gt; 308 ke apex. TEMUAN: http://harmoniclothing.com tidak diar</t>
+          <t>Verifikasi ulang setelah perbaikan: produksi: http://harmoniclothing.com/catalog -&gt; HTTP 308 Location https://harmoniclothing.com/catalog (aturan redirect x-forwarded-proto di next.config.mjs); https dan www-&gt;apex sudah benar sebelumnya. | Sebelumnya (Sebagian): https://harmoniclothing.com 200 (SSL valid), www -&gt; 308 ke apex. TEMUAN: http://harmoniclothing.com tidak diar</t>
         </is>
       </c>
     </row>

--- a/Required Document/QC_Claude_Hasil.xlsx
+++ b/Required Document/QC_Claude_Hasil.xlsx
@@ -513,10 +513,10 @@
         <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>37</v>
@@ -541,10 +541,10 @@
         <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>19</v>
@@ -597,10 +597,10 @@
         <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>16</v>
@@ -625,10 +625,10 @@
         <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>20</v>
@@ -765,10 +765,10 @@
         <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>16</v>
@@ -793,10 +793,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -4196,14 +4196,14 @@
           <t>`composer audit` &amp; `pnpm audit` tanpa kerentanan tingkat tinggi/kritis</t>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>composer audit 7 advisory (commonmark high); pnpm audit --prod 14 kerentanan (2 critical, 8 high) - lihat sheet Keamanan #35.</t>
+          <t>Verifikasi ulang setelah perbaikan: composer audit dan pnpm audit --prod bersih (0 advisory) setelah pembaruan dependensi; lihat Keamanan #35. | Sebelumnya (Gagal): composer audit 7 advisory (commonmark high); pnpm audit --prod 14 kerentanan (2 critical, 8 high) - lihat shee</t>
         </is>
       </c>
     </row>
@@ -4869,14 +4869,14 @@
           <t>Header keamanan (X-Content-Type-Options, X-Frame-Options/frame-ancestors, Referrer-Policy, HSTS) hadir di respons produksi</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Probe GET produksi https://harmoniclothing.com/: respons hanya server: cloudflare, tanpa X-Content-Type-Options, X-Frame-Options/CSP frame-ancestors, Referrer-Policy, maupun Strict-Transport-Security. Perlu header lewat next.config/Cloudflare.</t>
+          <t>header keamanan: Verifikasi setelah perbaikan: respons memuat X-Content-Type-Options=nosniff, X-Frame-Options=DENY, CSP frame-ancestors 'none', Referrer-Policy=strict-origin-when-cross-origin, Permissions-Policy, Strict-Transport-Security (max-age 1 tahun). Perlu dicek ulang di produksi setelah deploy. | Sebelumnya (Gagal): Probe GET produksi https://harmoniclothing.com/: respons hanya server: cloudflare, tanpa X-Content-Type-Option</t>
         </is>
       </c>
     </row>
@@ -4894,14 +4894,14 @@
           <t>Situs tidak dapat di-embed iframe oleh domain lain (clickjacking)</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Tanpa X-Frame-Options/frame-ancestors di produksi, situs bisa di-embed iframe domain lain (clickjacking). Belum dites dengan iframe sungguhan.</t>
+          <t>clickjacking: Verifikasi setelah perbaikan: halaman dibuka di dalam &lt;iframe&gt; domain lain: diblokir (X-Frame-Options=DENY + frame-ancestors 'none'); frame yang memuat /about=0, isi=0 karakter | Sebelumnya (Gagal): Tanpa X-Frame-Options/frame-ancestors di produksi, situs bisa di-embed iframe domain lain (clickjacking). Belu</t>
         </is>
       </c>
     </row>
@@ -5119,14 +5119,14 @@
           <t>Dependensi tanpa kerentanan tinggi/kritis (composer audit, pnpm audit)</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>composer audit: 7 advisory di 4 paket (enshrined/svg-sanitize medium x3, laravel/framework low, league/commonmark high+medium, league/flysystem low). pnpm audit --prod: 14 kerentanan (2 critical, 8 high, 4 moderate): next 15.5.23 -&gt; perlu &gt;=15.5.24/15.5.27 (RCE kritis di Image Optimization), sharp &lt;0.35.5, brace-expansion, glob, source-map-js. Perlu upgrade.</t>
+          <t>Verifikasi ulang setelah perbaikan: pnpm audit --prod: No known vulnerabilities (next 15.5.23 -&gt; 15.5.28; override sharp, brace-expansion, source-map-js, glob dinaikkan). composer audit: No security vulnerability advisories (enshrined/svg-sanitize 1.0, league/commonmark, symfony/http-foundation, league/flysystem, laravel/framework diperbarui). 252 test backend lulus. | Sebelumnya (Gagal): composer audit: 7 advisory di 4 paket (enshrined/svg-sanitize medium x3, laravel/framework low, league/commonm</t>
         </is>
       </c>
     </row>
@@ -6267,14 +6267,14 @@
           <t>State filter tersimpan di URL (query string): refresh/bagikan URL menghasilkan hasil yang sama</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): state filter di URL marketplace: filter kategori tidak muncul di URL (http://localhost:3001/marketplace) | Bukti lain: Browser QC (localhost:3001 + backend QC): katalog: memilih kategori mengubah hasil tetapi location.search tetap kosong -&gt; state filter tidak</t>
+          <t>Verifikasi ulang setelah perbaikan: filter, sort, dan pencarian tersimpan di URL: /catalog?ukuran=M&amp;urut=harga_asc&amp;q=ut menerapkan ukuran M, pencarian 'ut' (Menampilkan 1 dari 10 produk); klik filter L -&gt; ?ukuran=M%2CL; setelah reload tetap sama dan L aktif. Berlaku juga di tab Desain Lapak Desain; parameter lain (?tab=creator) tidak tertimpa. | Sebelumnya (Sebagian): filter tersimpan di URL: Verifikasi setelah perbaikan: q='', M aktif=true, url1=?ukuran=M%2CL&amp;urut=harga_asc&amp;q</t>
         </is>
       </c>
     </row>
@@ -7392,14 +7392,14 @@
           <t>"Beli Sekarang" menambah item lalu mengarah ke keranjang/checkout yang benar</t>
         </is>
       </c>
-      <c r="D85" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Beli Sekarang (login): URL /catalog/ut-doloremque-neque</t>
+          <t>Verifikasi ulang setelah perbaikan: 'Beli Sekarang' menambah item ke keranjang lalu membuka /checkout?items=&lt;id item baru&gt;: ringkasan hanya berisi item itu (1 item, Rp 452.000) walau keranjang berisi 4 item. Sebelumnya checkout memuat seluruh isi keranjang. Catatan lama (URL tetap di produk) hanya karena compile awal dev server. | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): Beli Sekarang (login): URL /catalog/ut-doloremque-neque</t>
         </is>
       </c>
     </row>
@@ -9167,14 +9167,14 @@
           <t>Rate limit endpoint auth (20/menit per IP) memberi pesan 429 yang jelas bila terlampaui</t>
         </is>
       </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): rate limit auth 20/menit: tidak ada 429 setelah 22 request</t>
+          <t>rate limit auth 20/menit: Verifikasi setelah perbaikan: request ke-21 dalam semenit dari IP yang sama -&gt; HTTP 429 'Terlalu banyak percobaan. Silakan tunggu sebentar lalu coba lagi.' (20 request pertama lolos) | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): rate limit auth 20/menit: tidak ada 429 setelah 22 request</t>
         </is>
       </c>
     </row>
@@ -10246,14 +10246,14 @@
           <t>Halaman termuat dengan produk yang benar; slug salah → pesan "tidak ditemukan" (bukan crash)</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): slug salah customize: skeleton 5 elemen, tanpa pesan 'tidak ditemukan' setelah 9 detik | Bukti lain: Browser QC (login test@example.com): /customize/{slug-tidak-ada} tetap menampilkan skeleton tanpa batas (API 404, tidak ada pesan 'tidak dit</t>
+          <t>customize slug salah: Verifikasi setelah perbaikan: /customize/slug-tidak-ada-qc menampilkan 'Produk tidak ditemukan.' dan tombol kembali ke katalog (bukan skeleton selamanya) | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): slug salah customize: skeleton 5 elemen, tanpa pesan 'tida</t>
         </is>
       </c>
     </row>
@@ -14992,14 +14992,14 @@
           <t>"Lihat Foto KTP" membuka gambar KTP (bukan 404/403); hanya admin yang bisa melihat</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Lihat Foto KTP file hilang: GET kyc-document untuk berkas yang tidak ada di storage -&gt; HTTP 500 (seharusnya 404 yang rapi) | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): Lihat Foto KTP: tautan http://localhost:8001/api/admin/creators/9/kyc-document target=_b</t>
+          <t>Verifikasi ulang setelah perbaikan: profil creator dengan berkas KTP yang tidak ada di storage -&gt; GET /admin/creators/{id}/kyc-document = HTTP 404 (bukan 500); id tak dikenal = 404. Dicakup test otomatis. | Sebelumnya (Sebagian): foto KTP hilang: Verifikasi setelah perbaikan: tidak ada berkas hilang di data uji; id tak dikenal -&gt; 401 | Se</t>
         </is>
       </c>
     </row>
@@ -15017,14 +15017,14 @@
           <t>"Setujui" → creator aktif, notifikasi "creator.approved" terkirim, hilang dari daftar pending, muncul di "Creator Aktif"</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Setujui creator: pending 3 -&gt; 1 | Bukti lain: API E2E-02: approve -&gt; creator aktif, notifikasi ke creator, area /creator terbuka.</t>
+          <t xml:space="preserve">Setujui creator: Verifikasi setelah perbaikan: satu klik 'Setujui' pada creator #10: pending 1 -&gt; 0 (tepat 1), status 'aktif', notifikasi creator.approved +1. Dipulihkan. | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): Setujui creator: pending 3 -&gt; 1 | Bukti lain: API E2E-02: </t>
         </is>
       </c>
     </row>
@@ -16067,14 +16067,14 @@
           <t>"Mulai Produksi" pada pesanan Menunggu Approval → status Diproses; tidak bisa dipanggil pada status lain</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Mulai Produksi UI: 4 -&gt; 2 | Bukti lain: API: Mulai Produksi hanya dari menunggu_approval; pada belum_dibayar -&gt; 422 (sheet BR #5).</t>
+          <t>Mulai Produksi: Verifikasi setelah perbaikan: pesanan #72 menunggu_approval: tombol 'Mulai Produksi'=1; klik -&gt; status diproses_produksi, riwayat status +1 (tepat satu transisi). Dipulihkan. | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): Mulai Produksi UI: 4 -&gt; 2 | Bukti lain: API: Mulai Produks</t>
         </is>
       </c>
     </row>
@@ -17665,14 +17665,14 @@
           <t>Orientasi portrait ↔ landscape tidak merusak layout</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Gagal</t>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): landscape 800x375: landscape 800x375: scroll horizontal pada /=6px, /catalog=42px, /catalog/ut-doloremque-neque=17px, /marketplace=42px, /marketplace/design/culpa-quia-quia=17px, /about=6px, /faq=4px, /kontak=4px, /legal/terms=4px</t>
+          <t>orientasi landscape: Verifikasi setelah perbaikan: landscape 800x375 tanpa scroll horizontal: /=0, /catalog=0, /marketplace=0, /about=0, /faq=0, /catalog/ut-dolo=0 | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): landscape 800x375: landscape 800x375: scroll horizontal pa</t>
         </is>
       </c>
     </row>

--- a/Required Document/QC_Claude_Hasil.xlsx
+++ b/Required Document/QC_Claude_Hasil.xlsx
@@ -4876,7 +4876,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>header keamanan: Verifikasi setelah perbaikan: respons memuat X-Content-Type-Options=nosniff, X-Frame-Options=DENY, CSP frame-ancestors 'none', Referrer-Policy=strict-origin-when-cross-origin, Permissions-Policy, Strict-Transport-Security (max-age 1 tahun). Perlu dicek ulang di produksi setelah deploy. | Sebelumnya (Gagal): Probe GET produksi https://harmoniclothing.com/: respons hanya server: cloudflare, tanpa X-Content-Type-Option</t>
+          <t>Verifikasi ulang setelah perbaikan: produksi https://harmoniclothing.com/ kini mengirim X-Content-Type-Options=nosniff, X-Frame-Options=DENY, Content-Security-Policy=frame-ancestors 'none', Referrer-Policy=strict-origin-when-cross-origin, Permissions-Policy, Strict-Transport-Security=max-age=31536000; includeSubDomains. CSP script penuh sengaja tidak dipasang (Snap/Pusher/inline Next). | Sebelumnya (Lulus): header keamanan: Verifikasi setelah perbaikan: respons memuat X-Content-Type-Options=nosniff, X-Frame-Options=</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>clickjacking: Verifikasi setelah perbaikan: halaman dibuka di dalam &lt;iframe&gt; domain lain: diblokir (X-Frame-Options=DENY + frame-ancestors 'none'); frame yang memuat /about=0, isi=0 karakter | Sebelumnya (Gagal): Tanpa X-Frame-Options/frame-ancestors di produksi, situs bisa di-embed iframe domain lain (clickjacking). Belu</t>
+          <t>Verifikasi ulang setelah perbaikan: produksi mengirim X-Frame-Options=DENY dan CSP frame-ancestors 'none'; uji iframe lokal (dev server dengan konfigurasi yang sama): halaman tidak termuat di dalam iframe domain lain. | Sebelumnya (Lulus): clickjacking: Verifikasi setelah perbaikan: halaman dibuka di dalam &lt;iframe&gt; domain lain: diblokir (X-Frame-Op</t>
         </is>
       </c>
     </row>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>rate limit auth 20/menit: Verifikasi setelah perbaikan: request ke-21 dalam semenit dari IP yang sama -&gt; HTTP 429 'Terlalu banyak percobaan. Silakan tunggu sebentar lalu coba lagi.' (20 request pertama lolos) | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): rate limit auth 20/menit: tidak ada 429 setelah 22 request</t>
+          <t xml:space="preserve">rate limit auth 20/menit: Verifikasi setelah perbaikan: request ke-21 dalam semenit dari IP yang sama -&gt; HTTP 429 'Terlalu banyak percobaan. Silakan tunggu sebentar lalu coba lagi.' (20 request pertama lolos) | Sebelumnya (Lulus): rate limit auth 20/menit: Verifikasi setelah perbaikan: request ke-21 dalam semenit dari IP yang sama -&gt; HTTP </t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>customize slug salah: Verifikasi setelah perbaikan: /customize/slug-tidak-ada-qc menampilkan 'Produk tidak ditemukan.' dan tombol kembali ke katalog (bukan skeleton selamanya) | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): slug salah customize: skeleton 5 elemen, tanpa pesan 'tida</t>
+          <t>customize slug salah: Verifikasi setelah perbaikan: /customize/slug-tidak-ada-qc menampilkan 'Produk tidak ditemukan.' dan tombol kembali ke katalog (bukan skeleton selamanya) | Sebelumnya (Lulus): customize slug salah: Verifikasi setelah perbaikan: /customize/slug-tidak-ada-qc menampilkan 'Produk tidak dit</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Setujui creator: Verifikasi setelah perbaikan: satu klik 'Setujui' pada creator #10: pending 1 -&gt; 0 (tepat 1), status 'aktif', notifikasi creator.approved +1. Dipulihkan. | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): Setujui creator: pending 3 -&gt; 1 | Bukti lain: API E2E-02: </t>
+          <t>Setujui creator: Verifikasi setelah perbaikan: satu klik 'Setujui' pada creator #10: pending 1 -&gt; 0 (tepat 1), status 'aktif', notifikasi creator.approved +1. Dipulihkan. | Sebelumnya (Lulus): Setujui creator: Verifikasi setelah perbaikan: satu klik 'Setujui' pada creator #10: pending 1 -&gt; 0 (tepat 1),</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Mulai Produksi: Verifikasi setelah perbaikan: pesanan #72 menunggu_approval: tombol 'Mulai Produksi'=1; klik -&gt; status diproses_produksi, riwayat status +1 (tepat satu transisi). Dipulihkan. | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): Mulai Produksi UI: 4 -&gt; 2 | Bukti lain: API: Mulai Produks</t>
+          <t>Mulai Produksi: Verifikasi setelah perbaikan: pesanan #72 menunggu_approval: tombol 'Mulai Produksi'=1; klik -&gt; status diproses_produksi, riwayat status +1 (tepat satu transisi). Dipulihkan. | Sebelumnya (Lulus): Mulai Produksi: Verifikasi setelah perbaikan: pesanan #72 menunggu_approval: tombol 'Mulai Produksi'=1; klik -</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>orientasi landscape: Verifikasi setelah perbaikan: landscape 800x375 tanpa scroll horizontal: /=0, /catalog=0, /marketplace=0, /about=0, /faq=0, /catalog/ut-dolo=0 | Sebelumnya (Gagal): UI (Playwright, Edge headless, :3001 + backend QC): landscape 800x375: landscape 800x375: scroll horizontal pa</t>
+          <t>orientasi landscape: Verifikasi setelah perbaikan: landscape 800x375 tanpa scroll horizontal: /=0, /catalog=0, /marketplace=0, /about=0, /faq=0, /catalog/ut-dolo=0 | Sebelumnya (Lulus): orientasi landscape: Verifikasi setelah perbaikan: landscape 800x375 tanpa scroll horizontal: /=0, /catalog=0,</t>
         </is>
       </c>
     </row>

--- a/Required Document/QC_Claude_Hasil.xlsx
+++ b/Required Document/QC_Claude_Hasil.xlsx
@@ -49,12 +49,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -513,13 +513,13 @@
         <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -541,13 +541,13 @@
         <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -569,13 +569,13 @@
         <v>51</v>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -597,13 +597,13 @@
         <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -625,13 +625,13 @@
         <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -653,13 +653,13 @@
         <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -709,13 +709,13 @@
         <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -737,13 +737,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
@@ -765,13 +765,13 @@
         <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
@@ -793,13 +793,13 @@
         <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -898,7 +898,7 @@
           <t>Registrasi akun baru (centang syarat &amp; privasi) → email verifikasi tiba → klik tautan → "Email berhasil diverifikasi"</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -950,12 +950,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>API: tambah alamat Bandung 40132 + is_default berfungsi (sheet Validasi #11); UI Address Book tidak diuji.</t>
+          <t>tambah alamat di UI: Putaran 80 baris: form Address Book via UI (label terhubung ke input: 8/8) menyimpan alamat 'Kos QC' kota Bandung 40135; dijadikan utama. | Sebelumnya (Sebagian): API: tambah alamat Bandung 40132 + is_default berfungsi (sheet Validasi #11); UI Address Book tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
           <t>Keranjang → pilih item → Beli → Checkout: alamat otomatis terpilih, pilih kurir, ongkir muncul, total benar</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -998,7 +998,7 @@
           <t>Buat Pesanan → Midtrans Snap → bayar (Sandbox) → kembali ke situs; status pesanan "Menunggu Approval"; notifikasi "pesanan dibayar"; invoice tersedia; pembayaran tercatat di admin</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -1023,7 +1023,7 @@
           <t>Admin: Antrian Produksi melihat pesanan + pratinjau file desain → "Mulai Produksi" → customer melihat status "Diproses"</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1048,7 +1048,7 @@
           <t>Admin: Kelola Pengiriman → "Proses Pengiriman" → resi muncul; webhook Biteship "inTransit" → pesanan "Dikirim" + notifikasi "order.shipped"</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -1073,7 +1073,7 @@
           <t>Webhook Biteship "delivered" → pesanan "Menunggu Konfirmasi" + notifikasi "order.delivered"</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1098,7 +1098,7 @@
           <t>Customer "Konfirmasi Diterima" → "Selesai"; form rating tampil → beri bintang &amp; komentar → tersimpan; ulasan muncul di halaman produk</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1123,7 +1123,7 @@
           <t>Seluruh riwayat status (timeline) pada detail pesanan lengkap &amp; berurutan; Audit Log admin mencatat aksi admin</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1148,7 +1148,7 @@
           <t>Customer ajukan upgrade creator → isi KYC (+ wali bila &lt; 18 th) → status "Menunggu Review"</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1173,7 +1173,7 @@
           <t>Admin Approval Creator → Setujui → creator mendapat notifikasi; area /creator terbuka</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1198,7 +1198,7 @@
           <t>Creator upload desain (PNG/SVG, produk, tag) → konfirmasi preview → Submit untuk Approval</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1223,7 +1223,7 @@
           <t>Admin Approval Desain → Setujui → desain muncul di Marketplace &amp; profil creator</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1248,7 +1248,7 @@
           <t>Customer lain membeli produk dengan desain tersebut (rincian harga: produk + kontribusi desainer) sampai pembayaran sukses</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1273,7 +1273,7 @@
           <t>Creator: Earnings menampilkan komisi "Terhutang" = persentase komisi × subtotal item</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1298,7 +1298,7 @@
           <t>Menjalankan `php artisan commissions:payout`: komisi di bawah minimum (Rp 50.000) TIDAK dicairkan; di atas minimum + ada rekening → diproses (catatan: disbursement masih stub — status tetap terhutang bila provider belum aktif)</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1323,7 +1323,7 @@
           <t>Creator tanpa data rekening dilewati dengan log peringatan (tidak error)</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1348,7 +1348,7 @@
           <t>Detail produk → "Pesan lewat Bulk Order" → isi qty beberapa ukuran; tier harga mengikuti TOTAL qty</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1373,7 +1373,7 @@
           <t>Lanjut Checkout Bulk → alamat, kurir → Buat Pesanan Bulk → bayar</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -1398,7 +1398,7 @@
           <t>Pesanan bertipe bulk di admin; harga per unit sesuai tier; total benar</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1423,7 +1423,7 @@
           <t>Bulk Order dan keranjang reguler tidak bisa digabung dalam satu checkout (BR-026)</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1448,7 +1448,7 @@
           <t>Pembatalan Bulk Order bersifat penuh (BR-022) — tidak ada pembatalan parsial</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1473,7 +1473,7 @@
           <t>Customer membatalkan saat "Menunggu Approval" → Dibatalkan (BR-010); refund diproses manual admin (BR-006)</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1498,7 +1498,7 @@
           <t>Setelah "Diproses Produksi" tombol batal tidak ada &amp; API menolak (422)</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1523,7 +1523,7 @@
           <t>Pesanan "Belum Dibayar" &gt; 24 jam → otomatis Dibatalkan oleh `orders:cancel-unpaid` (jalankan manual untuk uji) + notifikasi (BR-017)</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1548,7 +1548,7 @@
           <t>Pesanan belum dibayar &lt; 24 jam TIDAK dibatalkan oleh job</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1573,7 +1573,7 @@
           <t>Pembatalan hanya per-order, tidak per-item (BR-018)</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1598,7 +1598,7 @@
           <t>Admin menolak pesanan "Menunggu Approval" dengan alasan ≥ 10 karakter → status Ditolak</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1623,7 +1623,7 @@
           <t>Customer menerima notifikasi berisi alasan; detail pesanan menampilkan "Pesanan Ditolak" + alasan</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1648,7 +1648,7 @@
           <t>Menolak pesanan yang statusnya sudah berubah → 409 Conflict (bukan 422)</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1698,7 +1698,7 @@
           <t>Pesanan "Menunggu Konfirmasi" tanpa konfirmasi: sebelum 3 hari kerja → TIDAK diselesaikan; setelah 3 hari kerja (Sen–Jum, akhir pekan tidak dihitung) → otomatis Selesai (BR-014)</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1723,7 +1723,7 @@
           <t>Notifikasi "otomatis diselesaikan" terkirim; rating tetap bisa diberikan belakangan lewat riwayat pesanan (BR-004)</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1798,7 +1798,7 @@
           <t>Blokir biasa: desain hilang dari marketplace &amp; profil, akun customer tetap bisa login &amp; belanja, komisi tetap terhutang/dibayar</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1823,7 +1823,7 @@
           <t>Blokir hak cipta: akun tidak bisa login sama sekali; komisi terhutang berubah "Ditahan"</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1848,7 +1848,7 @@
           <t>Pesanan yang sudah dibayar sebelum blokir tetap berjalan sampai selesai</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1873,7 +1873,7 @@
           <t>Item wishlist/keranjang dari desain creator terblokir ditandai tidak tersedia &amp; tidak bisa di-checkout (BR-024)</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1898,7 +1898,7 @@
           <t>Admin menolak desain dengan alasan → creator melihat alasan &amp; notifikasi</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1923,7 +1923,7 @@
           <t>Creator revisi (edit judul/file/produk) pada desain YANG SAMA → submit ulang → status kembali "Menunggu Review" (bukan entri baru)</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1948,7 +1948,7 @@
           <t>Admin setujui hasil revisi → tayang di marketplace</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1973,7 +1973,7 @@
           <t>Tambah item ke keranjang → admin mengubah harga dasar produk → item di keranjang tetap harga lama</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -1998,7 +1998,7 @@
           <t>Hapus item lalu tambah lagi → memakai harga baru</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2023,7 +2023,7 @@
           <t>"Pesan Lagi" dari pesanan lama memakai harga TERKINI; produk nonaktif dilewati tanpa error</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2048,7 +2048,7 @@
           <t>Batal di Snap → pesanan tetap "Belum Dibayar" tanpa memajukan status</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2073,7 +2073,7 @@
           <t>VA kedaluwarsa → status pembayaran gagal; pesanan akhirnya dibatalkan otomatis (24 jam)</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2098,7 +2098,7 @@
           <t>Kartu ditolak (deny) → pesan jelas, pesanan tidak masuk produksi</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2123,7 +2123,7 @@
           <t>Webhook sukses dikirim dua kali → pesanan/komisi tidak ganda</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2148,7 +2148,7 @@
           <t>Webhook status onHold/rejected/courierNotFound/returned/cancelled/disposed → shipment "bermasalah"</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2173,7 +2173,7 @@
           <t>Admin menerima notifikasi; status PESANAN tidak berubah (admin menyelesaikan manual)</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2198,7 +2198,7 @@
           <t>Admin dapat berkomunikasi ke customer lewat chat &amp; menawarkan alternatif/refund manual (BR-015)</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2223,7 +2223,7 @@
           <t>Lupa Password → email diterima → buka tautan → set password baru → login dengan password baru berhasil</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2248,7 +2248,7 @@
           <t>Tautan reset dipakai ulang atau lewat masa berlaku → ditolak dengan pesan jelas</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2273,7 +2273,7 @@
           <t>Sesi lama tidak lagi valid setelah password diganti (uji bila diimplementasikan)</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2373,7 +2373,7 @@
           <t>Customer A tidak menerima pesan/notifikasi milik customer B</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -2398,7 +2398,7 @@
           <t>Jalankan alur belanja penuh dalam mode EN → semua teks UI, pesan error validasi, &amp; email berbahasa Inggris</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Seed QC memakai name_en = name_id sehingga perbedaan bahasa tidak teramati; logika lang diuji di sheet Validasi.</t>
+          <t>data produk ganti bahasa: Putaran 80 baris: nama dan deskripsi produk berganti sesuai bahasa: lihat Umum #9 (API Accept-Language dan UI katalog EN menampilkan 'Vel Temporibus Qui (EN)'). | Sebelumnya (Sebagian): Seed QC memakai name_en = name_id sehingga perbedaan bahasa tidak teramati; logika lang diuji di sheet Validasi.</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
           <t>`php artisan schedule:list` menampilkan 3 job: orders:cancel-unpaid (per jam), orders:auto-complete-deliveries (per jam), commissions:payout (mingguan)</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2571,7 +2571,7 @@
           <t>orders:cancel-unpaid: pesanan Belum Dibayar &gt; 24 jam → Dibatalkan + riwayat + notifikasi; &lt; 24 jam tidak disentuh</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tercakup test PHPUnit test_auto_complete_command_completes_orders_delivered_over_...; command dijalankan 2x di QC (0 diproses karena tak ada data). Hari kerja/akhir pekan tidak dibangun ulang manual.</t>
+          <t>Putaran 80 baris: test baru: Jumat 10:00 delivered -&gt; Minggu/Selasa 23:59 belum diselesaikan (akhir pekan tidak dihitung, &lt;3 hari kerja), Rabu 10:00 selesai. | Sebelumnya (Sebagian): Tercakup test PHPUnit test_auto_complete_command_completes_orders_delivered_over_...; command dijalankan 2x di QC (0 diproses karena tak ada data). Hari kerja/akhir pekan tidak dibangun ulang manual.</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
           <t>commissions:payout: ambang minimum, rekening kosong dilewati, tanpa provider tidak menandai dibayar</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2646,7 +2646,7 @@
           <t>Menjalankan job dua kali berturut-turut tidak memproses ulang item yang sama (idempoten)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2671,7 +2671,7 @@
           <t>Nilai 24 jam / 3 hari kerja / komisi / minimum diubah di config/business.php (atau env) dan job mengikutinya</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2696,7 +2696,7 @@
           <t>Output command (jumlah yang diproses) &amp; log tercatat</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2721,7 +2721,7 @@
           <t>Signature SHA512 salah/hilang → ditolak</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2746,7 +2746,7 @@
           <t>Status dibaca ulang dari Midtrans Get Status API (bukan dipercaya dari body)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Test: settlement -&gt; order paid + invoice; komisi untuk item berdesain. Notifikasi order.paid tidak diverifikasi; tanpa kunci Midtrans tidak diuji end-to-end.</t>
+          <t>Putaran 80 baris: test: settlement -&gt; pesanan Menunggu Approval, pembayaran berhasil, invoice dibuat, komisi untuk item berdesain (20%), notifikasi order.paid satu kali; tanpa kunci Midtrans nyata tidak ada uji end-to-end ke gateway. | Sebelumnya (Sebagian): Test: settlement -&gt; order paid + invoice; komisi untuk item berdesain. Notifikasi order.paid tidak diverifikasi; tanpa kunci Midtrans tidak diuji end-to-end.</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
           <t>capture dengan fraud_status=accept → sukses; capture dengan challenge/deny → tidak sukses</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2821,7 +2821,7 @@
           <t>deny / cancel / expire → pembayaran gagal; pesanan tidak maju</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2848,12 +2848,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Pending tidak memajukan pesanan (kode/test challenge); tidak diuji dengan webhook asli.</t>
+          <t>Putaran 80 baris: test data-provider: pending -&gt; pembayaran tetap belum_dibayar dan pesanan tidak maju; capture+challenge juga tidak maju. | Sebelumnya (Sebagian): Pending tidak memajukan pesanan (kode/test challenge); tidak diuji dengan webhook asli.</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Idempoten untuk order tak dikenal (test); idempoten untuk settlement ganda tidak terbukti dengan test spesifik.</t>
+          <t>Putaran 80 baris: test: webhook settlement dikirim dua kali -&gt; tepat 1 komisi, 1 invoice, 1 notifikasi order.paid, 1 baris riwayat status; keduanya 200. | Sebelumnya (Sebagian): Idempoten untuk order tak dikenal (test); idempoten untuk settlement ganda tidak terbukti dengan test spesifik.</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
           <t>order_id tak dikenal → 404/diabaikan tanpa 500</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2946,7 +2946,7 @@
           <t>Endpoint webhook dikecualikan dari CSRF &amp; sesi; tidak butuh login</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2971,7 +2971,7 @@
           <t>Tanpa/token salah → ditolak (fail-closed); token benar → diterima</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -2996,7 +2996,7 @@
           <t>Ping verifikasi instalasi kosong dari Biteship dijawab 200</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Kode BiteshipWebhookService::STATUS_MAP memetakan confirmed/allocated/pickingUp/picked -&gt; menunggu_pickup dst.; 14 status tidak dihitung satu per satu; ada test status tak dikenal.</t>
+          <t>Putaran 80 baris: test data-provider memetakan ke-14 status Biteship satu per satu: confirmed/allocated/pickingUp/picked -&gt; menunggu_pickup; inTransit/droppingOff -&gt; dikirim; delivered -&gt; delivered; returnInTransit/onHold/rejected/courierNotFound/returned/cancelled/disposed -&gt; bermasalah. | Sebelumnya (Sebagian): Kode BiteshipWebhookService::STATUS_MAP memetakan confirmed/allocated/pickingUp/picked -&gt; menunggu_pickup dst.; 14 status tidak dihitung satu per satu; ada test status tak dikenal.</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
           <t>inTransit/dikirim → status PESANAN Dikirim + notifikasi shipped; delivered → Menunggu Konfirmasi + delivered_at terisi + notifikasi</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3071,7 +3071,7 @@
           <t>bermasalah → notifikasi ke admin; status pesanan tidak berubah</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Status tak dikenal diabaikan (test); webhook ganda/status mundur tidak diuji khusus.</t>
+          <t>Putaran 80 baris: test: inTransit dua kali tidak menggandakan riwayat; delivered lalu inTransit terlambat (mundur) tidak mengubah pesanan dari menunggu_konfirmasi dan tidak menambah riwayat. | Sebelumnya (Sebagian): Status tak dikenal diabaikan (test); webhook ganda/status mundur tidak diuji khusus.</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3121,7 @@
           <t>biteship_order_id tak dikenal → diabaikan tanpa 500</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3146,7 +3146,7 @@
           <t>Semua endpoint privat tanpa login → 401; salah role → 403; resource orang lain → 404</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3171,7 +3171,7 @@
           <t>Validasi gagal → 422 dengan struktur errors per-field berbahasa sesuai (Accept-Language / ?lang)</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Transisi tidak valid -&gt; 422 (cancel selesai, ubah status belum_dibayar). 409 untuk konflik tidak diverifikasi.</t>
+          <t>Putaran 80 baris: reject pesanan yang sudah berpindah status -&gt; 409 (test AdminOrderTest); transisi tidak valid lain (cancel selesai, ubah status belum_dibayar) -&gt; 422 dengan pesan. | Sebelumnya (Sebagian): Transisi tidak valid -&gt; 422 (cancel selesai, ubah status belum_dibayar). 409 untuk konflik tidak diverifikasi.</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
           <t>Paginasi konsisten: meta current_page/per_page/total; per_page maksimum dibatasi</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3246,14 +3246,14 @@
           <t>Respons uang konsisten (string 2 desimal) di semua endpoint</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Contoh respons uang berupa string 2 desimal ('120000.00'); tidak semua endpoint disapu.</t>
+          <t>format uang: Putaran 80 baris: 304 bidang; tidak konsisten: /orders.meta.total=8 ; /catalog/products?per_page=3.meta.total=11 ; /marketplace/designs?per_page=3.data.0.starting_price=58000 ; /marketplace/designs?per_page=3.data.1.starting_price=191000 ; /marketplace/designs?per_page=3.data.2.starting_price=174000 | Sebelumnya (Sebagian): Contoh respons uang berupa string 2 desimal ('120000.00'); tidak semua endpoint disapu.</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
           <t>CORS: hanya origin yang diizinkan; origin lain ditolak; credentials didukung</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3321,7 +3321,7 @@
           <t>Rate limit: login 5/menit (per email+IP), grup auth 20/menit (per IP)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3346,7 +3346,7 @@
           <t>Status pesanan diubah dalam transaksi + lock (dua request bersamaan tidak membuat status ganda/lompat)</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -3371,7 +3371,7 @@
           <t>Respons tidak memuat field sensitif (password, remember_token, path file privat, nomor KTP pada endpoint publik)</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3421,7 +3421,7 @@
           <t>Email reset password: tombol &amp; tautan ke /reset-password (token+email), masa berlaku (menit) tercantum</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3546,7 +3546,7 @@
           <t>RESEND_API_KEY &amp; MAIL_FROM_ADDRESS terpasang di produksi; MAIL_MAILER bukan `log`</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3571,7 +3571,7 @@
           <t>Kanal privat chat.{thread} hanya bisa di-subscribe peserta thread; admin.chat hanya admin</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -3646,7 +3646,7 @@
           <t>Event dikirim langsung (tanpa queue worker) dan sampai &lt; 2 detik</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -3671,7 +3671,7 @@
           <t>Konfigurasi produksi memakai satu jalur (Pusher atau Reverb) konsisten di backend &amp; frontend (kunci NEXT_PUBLIC_*)</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -3696,14 +3696,14 @@
           <t>Disk publik (desain, mockup, foto profil) &amp; privat (KYC) terpisah; bucket R2 benar</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>filesystems.php: r2_public/r2_private terpisah (FILESYSTEM_DISK_PUBLIC/PRIVATE). Isi bucket R2 tidak diperiksa.</t>
+          <t>bucket R2: Putaran 80 baris: CDN https://cdn.harmoniclothing.com (bucket publik harmoni-public) melayani objek yang diunggah (mockups/placeholder.png=200, thumbnails/db71c7b9-d7df-30c0-b008-05a0edebdf28.png=200, image/png); disk publik dan privat (KYC) terpisah di filesystems.php (r2_public/r2_private). Isi bucket privat tidak diperiksa (butuh kredensial R2). | Sebelumnya (Sebagian): filesystems.php: r2_public/r2_private terpisah (FILESYSTEM_DISK_PUBLIC/PRIVATE). Isi bucket R2 tidak diperiksa.</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3721,7 @@
           <t>URL file publik valid (pub-...r2.dev / domain) dan diizinkan di next.config (images.remotePatterns)</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3746,7 +3746,7 @@
           <t>Domain produksi ada di allowlist gambar Next.js; gambar tampil melalui optimizer (/_next/image)</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -3771,14 +3771,14 @@
           <t>Upload besar (20MB) berhasil tanpa timeout (batas PHP upload_max_filesize/post_max_size &amp; Cloudflare 100MB)</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Upload PNG 20MB berhasil di QC (artisan serve). Batas PHP/Cloudflare produksi tidak diverifikasi.</t>
+          <t>batas upload PHP: Putaran 80 baris: PHP CLI di mesin ini: upload_max_filesize=2G, post_max_size=2G, memory_limit=512M (C:\laragon\bin\php\php-8.5.11-Win32-vs17-x64\php.ini); cukup untuk berkas 20MB. Backend produksi berjalan di PHP yang sama lewat tunnel Cloudflare (batas body 100MB). Upload 20MB lewat jalur produksi belum diuji (menulis ke R2 asli). | Sebelumnya (Sebagian): Upload PNG 20MB berhasil di QC (artisan serve). Batas PHP/Cloudflare produksi tidak diverifikasi.</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
           <t>https://harmoniclothing.com dan https://www.harmoniclothing.com (redirect ke apex) terbuka; SSL valid</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3871,7 +3871,7 @@
           <t>Rewrite /api, /sanctum, /broadcasting, /storage ke BACKEND_ORIGIN bekerja; cookie sesi pihak pertama</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3896,7 +3896,7 @@
           <t>Variabel produksi: FRONTEND_URL, SANCTUM_STATEFUL_DOMAINS, CORS_ALLOWED_ORIGINS memuat harmoniclothing.com</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -3921,7 +3921,7 @@
           <t>APP_DEBUG=false &amp; APP_ENV=production di produksi; tidak ada stack trace di respons error</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4096,7 +4096,7 @@
           <t>`php artisan test` → semua tes lulus (saat ini 234)</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4121,7 +4121,7 @@
           <t>`pnpm exec tsc --noEmit` tanpa error</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4146,7 +4146,7 @@
           <t>`pnpm lint` tanpa error (peringatan diketahui: 2 literal string)</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4196,7 +4196,7 @@
           <t>`composer audit` &amp; `pnpm audit` tanpa kerentanan tingkat tinggi/kritis</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>API QC: cookie sesi HttpOnly + SameSite terdeteksi. Flag Secure &amp; penyimpanan token di localStorage tidak diverifikasi (env QC http; frontend tidak diperiksa).</t>
+          <t>token di storage: Putaran 80 baris: cookie sesi httpOnly=true sameSite=Lax (secure=false karena QC memakai http); localStorage=[], sessionStorage=[]: tidak ada token; cookie yang terbaca JS hanya XSRF-TOKEN. | Sebelumnya (Sebagian): API QC: cookie sesi HttpOnly + SameSite terdeteksi. Flag Secure &amp; penyimpanan token di localStorage tidak diverifikasi (env QC http; frontend tidak diperiksa).</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
           <t>Sesi lama tidak valid setelah logout; session fixation tidak mungkin (ID sesi diganti saat login)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4319,7 +4319,7 @@
           <t>Password disimpan hash (bcrypt) — tidak pernah muncul di respons/log</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4344,7 +4344,7 @@
           <t>Brute-force login diblokir rate limit; pesan error login tidak membedakan email salah vs password salah</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4369,7 +4369,7 @@
           <t>Enumerasi akun: lupa password &amp; kirim ulang verifikasi memberi pesan sama untuk email terdaftar/tidak</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4394,7 +4394,7 @@
           <t>Tautan verifikasi email bertanda tangan (signed) &amp; tidak dapat dimanipulasi (id/hash/expires)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4419,7 +4419,7 @@
           <t>Token reset password sekali pakai &amp; kedaluwarsa</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4444,7 +4444,7 @@
           <t>Akun banned/nonaktif tidak dapat login &amp; sesi aktif ditolak</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4469,7 +4469,7 @@
           <t>Ganti ID pada /orders/{id}, /orders/{id}/invoice, /account/addresses/{id}, /cart/{id}, /wishlist/{id}, /notifications/{id}, /chat/threads/{id} dengan milik user lain → 404</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4494,7 +4494,7 @@
           <t>Customer memanggil semua endpoint /admin/* → 403; customer memanggil /creator/* → 403</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4519,7 +4519,7 @@
           <t>Creator memanggil /admin/* → 403; creator mengubah/men-submit desain creator lain → 404</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4546,12 +4546,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Checkout oleh admin ditolak (403/422), tetapi POST /cart oleh admin menghasilkan 201 (admin dapat menambah keranjang). Periksa Permission Matrix.</t>
+          <t>Putaran 80 baris: PERBAIKAN: admin kini ditolak 403 pada POST/GET /cart, /wishlist, /checkout (middleware not.admin) sesuai Permission Matrix; endpoint admin tetap 200. Dicakup test. | Sebelumnya (Sebagian): Checkout oleh admin ditolak (403/422), tetapi POST /cart oleh admin menghasilkan 201 (admin dapat menambah keranjang). Periksa Permission Matrix.</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
           <t>Endpoint foto KTP (kyc-document) hanya admin; customer/creator lain → 403</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4594,7 +4594,7 @@
           <t>Mass assignment: kirim field ekstra (role, status, is_admin, user_id, total, price) pada register/profile/checkout/cart → diabaikan</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4619,7 +4619,7 @@
           <t>Harga/ongkir/total tidak bisa diatur dari klien: dihitung server</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4644,7 +4644,7 @@
           <t>Order status tidak bisa dimajukan oleh customer lewat endpoint yang tidak semestinya</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4669,7 +4669,7 @@
           <t>XSS: &lt;script&gt;/&lt;img onerror&gt; pada nama, bio, judul desain, deskripsi, catatan, chat, alamat → ditampilkan sebagai teks (tidak dieksekusi) di semua tampilan termasuk admin</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4694,7 +4694,7 @@
           <t>SVG unggahan berisi script/onload/foreignObject disanitasi saat disimpan &amp; saat ditampilkan</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4719,7 +4719,7 @@
           <t>SQL injection pada search, filter, sort, slug (mis. ' OR 1=1 --) → tidak ada error SQL/kebocoran</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4744,7 +4744,7 @@
           <t>Sort/field dinamis hanya dari daftar putih; parameter aneh → 422</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4769,7 +4769,7 @@
           <t>Header injection/CRLF pada input email/nama tidak berdampak</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4794,7 +4794,7 @@
           <t>Tidak ada penggunaan dangerouslySetInnerHTML di halaman (verifikasi cepat)</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4819,7 +4819,7 @@
           <t>Request POST/PATCH/DELETE tanpa X-XSRF-TOKEN → 419</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4844,7 +4844,7 @@
           <t>Origin tak dikenal diblokir CORS; credentials hanya untuk origin resmi</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4869,7 +4869,7 @@
           <t>Header keamanan (X-Content-Type-Options, X-Frame-Options/frame-ancestors, Referrer-Policy, HSTS) hadir di respons produksi</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4894,7 +4894,7 @@
           <t>Situs tidak dapat di-embed iframe oleh domain lain (clickjacking)</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4944,7 +4944,7 @@
           <t>Redirect www → apex berfungsi tanpa membocorkan cookie</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4969,7 +4969,7 @@
           <t>Upload: validasi mimetype sisi server (bukan hanya ekstensi); file .php/.html/.exe menyamar ditolak; nama file di-UUID-kan</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -4994,7 +4994,7 @@
           <t>File yang diunggah tidak dapat dieksekusi di server; direktori storage tidak dapat di-listing</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5019,7 +5019,7 @@
           <t>File KYC hanya via endpoint terotorisasi (tidak ada URL publik)</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5044,7 +5044,7 @@
           <t>Webhook Midtrans: signature + verifikasi status server-ke-server; Biteship: token rahasia di URL</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5069,7 +5069,7 @@
           <t>Tidak ada rahasia (.env, kunci API, token) di repo Git, bundle frontend, atau respons error; hanya NEXT_PUBLIC_* publik di bundle</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -5094,7 +5094,7 @@
           <t>File debug/endpoint pengembang (telescope, phpinfo, /storage listing) tidak terekspos di produksi</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5119,7 +5119,7 @@
           <t>Dependensi tanpa kerentanan tinggi/kritis (composer audit, pnpm audit)</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5144,7 +5144,7 @@
           <t>Data pribadi (telepon, alamat, KTP, rekening) tidak tampil di halaman/API publik</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5169,7 +5169,7 @@
           <t>Telepon/penerima alamat terenkripsi di database (kolom PII) dan terdekripsi benar saat ditampilkan</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5194,7 +5194,7 @@
           <t>Persetujuan kebijakan privasi &amp; syarat tercatat saat registrasi</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5244,7 +5244,7 @@
           <t>Log aplikasi tidak memuat password/token/nomor KTP</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5319,12 +5319,12 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): h1 'Wujudkan Ide. Ciptakan Produk. Bergerak Bersama.', subjudul &amp; kartu 'Custom by You' ada di teks; ilustrasi hoodie/kaos tidak dicek secara visual.</t>
+          <t>Putaran 80 baris: tangkapan layar beranda: 3 baris headline, subjudul, ilustrasi hoodie putih + kaos hijau + topi di panggung, kartu 'Custom by You' (12.3K) tampil lengkap. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): h1 'Wujudkan Ide. Ciptakan Produk. Bergerak Bersama.', subjudul &amp; kartu 'Custom by You' ada di teks; ilustrasi hoodie/kaos tidak dicek secara visual.</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5342,7 @@
           <t>Tombol "Mulai Custom Design" &amp; "Jelajahi Produk" di hero mengarah ke halaman yang benar</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5367,7 +5367,7 @@
           <t>4 lencana kepercayaan (Tanpa Minimum Order, Kualitas Premium, Produksi Cepat, Garansi Kepuasan) tampil lengkap &amp; teksnya benar</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5392,7 +5392,7 @@
           <t>Section "Cara Kerja": 4 langkah (Pilih Produk, Buat Desain, Konfirmasi Pesanan, Terima Produk) tampil berurutan</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5417,7 +5417,7 @@
           <t>"Produk Populer" menampilkan produk nyata (gambar, nama, harga "Mulai dari Rp...", jumlah terjual)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5442,7 +5442,7 @@
           <t>Link "Lihat Semua Produk →" membuka /catalog; klik kartu produk membuka detail produk yang benar</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5467,7 +5467,7 @@
           <t>"Desain Populer" menampilkan desain nyata (thumbnail, nama desain, nama creator, harga)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5492,7 +5492,7 @@
           <t>Link "Lihat Semua Desain →" membuka /marketplace; klik kartu desain membuka detail desain yang benar</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): marquee testimoni: elemen beranimasi: 11; jumlah testimoni &amp; kelancaran animasi tidak dapat diukur secara headless</t>
+          <t>marquee testimoni: Putaran 80 baris: animasi CSS 'marquee' berjalan (linear, 100s) tanpa jeda; 8 testimoni unik dalam pita (16 termasuk salinan untuk loop mulus); kelancaran visual per frame tidak diukur. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): marquee testimoni: elemen beranimasi: 11; jumlah testimoni &amp; kelancaran animasi tidak dapat diukur secara headless</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5542,7 @@
           <t>Section CTA bawah: tombol "Mulai Custom Design" &amp; "Daftar Gratis" (membuka modal registrasi) berfungsi</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5567,7 +5567,7 @@
           <t>Saat data produk/desain sedang dimuat tampil skeleton/loading, bukan layar kosong</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5592,7 +5592,7 @@
           <t>Jika data produk/desain kosong atau API gagal, section menampilkan empty/error state (bukan crash)</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Reveal saat scroll: 4 elemen bertulisan masih opacity 0 setelah scroll</t>
+          <t>Reveal sekali tampil: Putaran 80 baris: setelah menggulir ke bawah lalu kembali ke atas tidak ada elemen bertulisan yang tersisa tersembunyi (opacity 0); Reveal kini sekali tampil (sebelumnya menyembunyikan lagi saat keluar layar). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): Reveal saat scroll: 4 elemen bertulisan masih opacity 0 setelah scroll</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
           <t>Tidak ada gambar rusak (broken image) di seluruh halaman; tidak ada layout shift saat gambar termuat</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5667,7 +5667,7 @@
           <t>Judul tab browser &amp; meta description sesuai; ikon (favicon) tampil</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5692,7 +5692,7 @@
           <t>Tampilan rapi di mobile (375px), tablet (768px), dan desktop (1280px+)</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5717,7 +5717,7 @@
           <t>Logo mengarah ke beranda</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5742,7 +5742,7 @@
           <t>Menu Beranda, Produk, Desain, Tentang Kami mengarah ke halaman yang benar; menu aktif ter-highlight</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5767,7 +5767,7 @@
           <t>Tombol "Masuk" membuka modal login; "Daftar Gratis" membuka modal registrasi</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5794,12 +5794,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): ikon keranjang guest: header tamu tidak menampilkan ikon keranjang (sesuai desain bila disengaja) | Bukti lain: Browser QC (localhost:3001 + backend QC): header tamu tidak menampilkan ikon keranjang (hanya Masuk/Daftar) - sesuai bila disengaja.</t>
+          <t>Putaran 80 baris: header tamu tidak menampilkan ikon keranjang (hanya Masuk/Daftar Gratis); sesuai dokumen IA (tidak ada keranjang untuk Guest; aksi tambah ke keranjang memicu modal login). Tidak ada error. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): ikon keranjang guest: header tamu tidak menampilkan ikon keranjang (sesuai desain bila disengaja) | Bukti lain: Browser QC (localhost:3001 + backend QC): header tamu tidak menampilkan ikon</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
           <t>Saklar bahasa ID/EN tampil dan berfungsi</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5842,7 +5842,7 @@
           <t>Di mobile: ikon hamburger membuka drawer menu, tombol tutup menutup, menu dalam drawer berfungsi</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): flicker header: tidak dapat diukur secara headless; tidak ditemukan kilatan state guest pada pengamatan browser (header langsung memuat nama setelah login)</t>
+          <t>header tidak berkedip (tamu): Putaran 80 baris: header tamu dicuplik tiap 250ms: hanya satu keadaan konsisten (guest); tidak ada kilatan keadaan login/lain. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): flicker header: tidak dapat diukur secara headless; tidak ditemukan kilatan state guest pada pengamatan browser (header langsung memuat nama setelah login)</t>
         </is>
       </c>
     </row>
@@ -5892,14 +5892,14 @@
           <t>Tautan PRODUK (T-Shirt, Hoodie, Jacket) mengarah ke katalog dengan filter yang benar</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): footer: /catalog?kategori=t-shirt|hoodie|jacket; kategori seed QC acak, jadi hasil filter tidak bisa diverifikasi.</t>
+          <t>Putaran 80 baris: footer memakai /catalog?kategori=t-shirt|hoodie|jacket (slug sesuai kategori produksi menurut catatan sebelumnya); verifikasi ulang ke API produksi tidak bisa dilakukan sekarang karena backend laptop (tunnel Cloudflare) sedang mati (HTTP 530). Data QC memakai kategori acak sehingga hasil filter tidak dapat dicocokkan. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): footer: /catalog?kategori=t-shirt|hoodie|jacket; kategori seed QC acak, jadi hasil filter tidak bisa diverifikasi.</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
           <t>Tautan BANTUAN (FAQ, Pusat Bantuan, Kontak) membuka halaman yang benar</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5942,7 +5942,7 @@
           <t>Tautan KEBIJAKAN (Syarat &amp; Ketentuan, Kebijakan Privasi, Retur &amp; Refund, Pengiriman) membuka halaman yang benar</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5967,7 +5967,7 @@
           <t>Teks hak cipta menampilkan tahun yang benar</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -5992,7 +5992,7 @@
           <t>Saklar bahasa di footer berfungsi &amp; sinkron dengan saklar di header</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6017,7 +6017,7 @@
           <t>Tidak ada tautan mati (404) di footer</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6042,7 +6042,7 @@
           <t>Grid desain menampilkan data nyata (thumbnail, nama desain, nama creator, harga, terjual)</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6067,7 +6067,7 @@
           <t>Search bar mencari berdasarkan nama desain/tag; tombol "Hapus pencarian" mengosongkan kata kunci</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6092,7 +6092,7 @@
           <t>Filter kategori, tag, dan rentang harga (min/maks) mengubah hasil sesuai pilihan</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6117,7 +6117,7 @@
           <t>Tombol naik/turun harga minimum &amp; maksimum bekerja; min tidak boleh melebihi maks</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6142,7 +6142,7 @@
           <t>Urutkan: Terbaru, Harga Rendah→Tinggi, Harga Tinggi→Rendah, Terlaris, Rating Tertinggi — hasil sesuai</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6167,7 +6167,7 @@
           <t>Teks "Menampilkan X dari Y desain" sesuai jumlah sebenarnya</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6192,7 +6192,7 @@
           <t>Tombol "Muat Lebih Banyak" memuat halaman berikutnya, hilang saat semua desain sudah tampil</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6217,7 +6217,7 @@
           <t>Kombinasi filter + pencarian + urutan bekerja bersamaan; "Reset pencarian &amp; filter" mengembalikan semua</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6244,12 +6244,12 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): katalog: hasil kosong -&gt; 'Belum ada produk ditemukan untuk filter ini.' + tombol reset; versi marketplace tidak diuji.</t>
+          <t>marketplace kosong: Putaran 80 baris: /marketplace?q=zzzqqq menampilkan 'Belum ada desain ditemukan untuk filter ini.' dan tombol 'Reset pencarian &amp; filter'. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): katalog: hasil kosong -&gt; 'Belum ada produk ditemukan untuk filter ini.' + tombol reset; versi marketplace tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
           <t>State filter tersimpan di URL (query string): refresh/bagikan URL menghasilkan hasil yang sama</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6292,7 +6292,7 @@
           <t>Klik kartu desain membuka Detail Desain yang benar</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6317,7 +6317,7 @@
           <t>Ikon wishlist (love) pada kartu: guest diminta login; user login bisa menambah/menghapus</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6342,7 +6342,7 @@
           <t>Tombol "Jadi Kreator" &amp; "Lihat Produk" mengarah ke halaman yang benar</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6367,7 +6367,7 @@
           <t>Loading skeleton tampil saat data dimuat; error state + tombol "Coba Lagi" tampil saat API gagal</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6392,7 +6392,7 @@
           <t>Pindah ke tab "Kreator" menampilkan grid kreator (foto, nama, jumlah desain, rating)</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6417,7 +6417,7 @@
           <t>Search kreator, filter kategori &amp; tag, serta urutan (Terbaru, Terlaris, Rating Tertinggi) berfungsi</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6442,7 +6442,7 @@
           <t>Teks "Menampilkan X dari Y kreator" benar; "Muat Lebih Banyak" berfungsi</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6467,7 +6467,7 @@
           <t>Hasil kosong menampilkan pesan "Belum ada kreator ditemukan" + reset</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (Playwright, putaran 2): tab Kreator memuat 7 kartu kreator; seluruh 7 kreator seed tidak punya foto (photo_url null) dan kartu tampil tanpa elemen &lt;img&gt; rusak (avatar default). Kasus kreator dengan foto nyata tidak ada di data seed sehingga belum diuji.</t>
+          <t>foto profil kreator: Putaran 80 baris: kreator berfoto tampil sebagai gambar yang termuat (naturalWidth 64px, bukan broken); kreator lain tanpa foto memakai avatar default (ikon). | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): tab Kreator memuat 7 kartu kreator; seluruh 7 kreator seed tidak punya foto (photo_url null) dan kartu tampil tanpa elemen &lt;img&gt; rusak (avatar default). Kasus kreator dengan foto nyata tidak ada di data s</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
           <t>Kreator yang di-ban / belum aktif TIDAK muncul di daftar (BR-019)</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6542,7 +6542,7 @@
           <t>Klik kartu kreator membuka profil publik kreator yang benar</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): profil kreator termuat (h1 nama brand 'Bartell LLC').</t>
+          <t>profil publik kreator: Putaran 80 baris: h1='Harmoni Creator Studio', foto termuat, teks 'Kreator sejak ...' ada. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): profil kreator termuat (h1 nama brand 'Bartell LLC').</t>
         </is>
       </c>
     </row>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tombol Lihat Portofolio: tidak ada kreator dengan portfolio_url di data seed; dengan portofolio: tidak ada data; tanpa portofolio: tombol=0</t>
+          <t>tombol portofolio: Putaran 80 baris: kreator dengan portfolio_url: tombol 'Lihat Portofolio' -&gt; https://example.com/portfolio target=_blank rel='noopener noreferrer'. Tanpa portofolio tombol tidak tampil (diuji di putaran sebelumnya: tombol=0). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): tombol Lihat Portofolio: tidak ada kreator dengan portfolio_url di data seed; dengan portofolio: tidak ada data; tanpa portofolio: tombol=0</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6617,7 @@
           <t>Statistik (Desain, Rating, Total Terjual) sesuai data nyata</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6642,7 +6642,7 @@
           <t>Daftar "Desain oleh {nama}" menampilkan hanya desain published milik kreator tsb</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6667,7 +6667,7 @@
           <t>Kreator tanpa desain menampilkan "Belum ada desain yang dipublikasikan"</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6692,7 +6692,7 @@
           <t>Slug yang tidak ada → pesan "Kreator tidak ditemukan" + tombol kembali ke Lapak Desain (bukan crash)</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6717,7 +6717,7 @@
           <t>Slug kreator yang sudah di-ban → tidak dapat diakses publik</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6742,7 +6742,7 @@
           <t>Judul tab &amp; meta description memuat nama kreator</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6767,7 +6767,7 @@
           <t>Grid produk menampilkan data nyata (gambar, nama, harga "Mulai dari", terjual, rating)</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6792,7 +6792,7 @@
           <t>Search bar &amp; tombol hapus pencarian berfungsi</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6817,7 +6817,7 @@
           <t>Filter sidebar: Kategori, Segmen (Men's/Women's/Unisex/Kids), Warna, Ukuran, Material, Area Cetak, Harga — semua mengubah hasil benar</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6842,7 +6842,7 @@
           <t>Opsi filter (warna/ukuran/material) berasal dari data nyata katalog; "Semua" &amp; "Reset" berfungsi</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6867,7 +6867,7 @@
           <t>Urutkan: Terbaru, Harga Rendah→Tinggi, Harga Tinggi→Rendah, Terlaris, Rating Tertinggi</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6892,7 +6892,7 @@
           <t>Teks "Menampilkan X dari Y produk" benar; "Muat Lebih Banyak" berfungsi</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6917,7 +6917,7 @@
           <t>Hasil kosong menampilkan pesan + "Reset pencarian &amp; filter"</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6942,7 +6942,7 @@
           <t>Produk NONAKTIF (is_active=false) tidak muncul di katalog</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -6967,14 +6967,14 @@
           <t>Filter via URL dari footer (mis. kategori T-Shirt) menghasilkan hasil benar</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (Playwright, putaran 2): tautan footer 'T-Shirt' -&gt; /catalog?kategori=t-shirt menghasilkan 'Menampilkan 0 dari 10 produk': slug kategori di footer tidak cocok dengan kategori data QC (seed faker: Dolorum ipsam, dst.), jadi hasil filter benar hanya bisa dipastikan dengan kategori produksi 'T-Shirt'.</t>
+          <t xml:space="preserve">Putaran 80 baris: tautan footer menghasilkan filter kategori lewat URL (diuji berfungsi di QC dengan kategori seed); hasil untuk kategori produksi T-Shirt/Hoodie/Jacket belum diverifikasi ulang karena backend produksi sedang mati (HTTP 530). | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): tautan footer 'T-Shirt' -&gt; /catalog?kategori=t-shirt menghasilkan 'Menampilkan 0 dari 10 produk': slug kategori di footer tidak cocok dengan kategori data QC (seed faker: Dolorum ipsam, dst.), jadi hasil </t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
           <t>Tombol "Mulai Custom Design" &amp; "Lihat Desain" berfungsi</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7017,7 +7017,7 @@
           <t>Klik kartu produk membuka Detail Produk yang benar</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7042,7 +7042,7 @@
           <t>Di mobile: filter dapat dibuka/ditutup dan tidak menutupi hasil</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7067,7 +7067,7 @@
           <t>Loading skeleton &amp; error state + "Coba Lagi" tampil sesuai kondisi</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): detail produk memuat h1 nama produk tanpa error; harga/rating tidak dirinci.</t>
+          <t>info produk: Putaran 80 baris: detail 'Sequi explicabo nisi': nama, harga Rupiah, rating 3 (8 ulasan) dan jumlah terjual (35) tampil; lencana Terlaris tampil. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): detail produk memuat h1 nama produk tanpa error; harga/rating tidak dirinci.</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
           <t>Galeri gambar berganti sesuai warna yang dipilih; thumbnail dapat diklik</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -7142,7 +7142,7 @@
           <t>Pilih warna &amp; ukuran mengubah preview, harga (harga dasar + tambahan varian), dan ketersediaan</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7169,12 +7169,12 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): tidak ditemukan 'NaN'/'undefined'/'null' pada teks detail produk dan halaman publik lain.</t>
+          <t>format Rupiah: Putaran 80 baris: harga tampil Rp 312.000, Rp 409.000, Rp 429.000; tidak ada NaN/undefined/null/negatif pada halaman detail. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): tidak ditemukan 'NaN'/'undefined'/'null' pada teks detail produk dan halaman publik lain.</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
           <t>Tombol "Size Chart" membuka tabel ukuran (Lebar Dada, Panjang) yang benar</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7217,7 +7217,7 @@
           <t>Area upload "Upload Desain Sendiri (opsional)": file PNG/JPG ≤ 20MB berhasil, status berubah "File terunggah", dapat diganti</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7244,12 +7244,12 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): upload salah format ditolak: tidak ada pesan error terdeteksi untuk berkas .txt: Upload Desain Sendiri (opsional) / Klik atau drag file di sini (PNG/SVG, maks 20MB)</t>
+          <t>upload salah format: Putaran 80 baris: berkas .txt ditolak di klien dengan pesan 'Format file harus PNG atau SVG dengan ukuran maksimal 20MB.' (tanpa permintaan ke server). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): upload salah format ditolak: tidak ada pesan error terdeteksi untuk berkas .txt: Upload Desain Sendiri (opsional) / Klik atau drag file di sini (PNG/SVG, maks 20MB)</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
           <t>Quantity stepper (+/−) bekerja; minimum 1; tidak bisa 0/negatif</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7292,7 +7292,7 @@
           <t>Kolom catatan (opsional) dapat diisi dan ikut tersimpan ke keranjang</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7317,7 +7317,7 @@
           <t>"Tambah ke Keranjang" tanpa memilih warna/ukuran → pesan "Pilih warna dan ukuran terlebih dahulu"</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7342,7 +7342,7 @@
           <t>"Tambah ke Keranjang" sebagai guest → diminta login (modal) lalu aksi dilanjutkan/tidak hilang</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7367,7 +7367,7 @@
           <t>"Tambah ke Keranjang" berhasil: toast sukses, badge keranjang di navbar bertambah tanpa refresh</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7392,7 +7392,7 @@
           <t>"Beli Sekarang" menambah item lalu mengarah ke keranjang/checkout yang benar</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7417,7 +7417,7 @@
           <t>Tautan "atau pilih desain siap pakai dari Lapak Desain →" mengarah ke marketplace</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7442,7 +7442,7 @@
           <t>Tautan "Pesan lewat Bulk Order →" membuka /bulk-order/[slug] produk yang benar</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7467,7 +7467,7 @@
           <t>Ikon wishlist produk berfungsi (guest diminta login)</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7492,7 +7492,7 @@
           <t>Tab Deskripsi, Spesifikasi (Bahan, Jenis Potongan, Area Cetak), Bahan &amp; Perawatan, Pengiriman, Ulasan semua dapat dibuka &amp; isinya benar</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7519,12 +7519,12 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tab ulasan: API ulasan=5; UI: 3.4 (5 ulasan) / Ulasan (5); kosong -&gt; 'tidak terdeteksi'</t>
+          <t>tab ulasan: Putaran 80 baris: produk dengan ulasan menampilkan daftar (nama pembeli, bintang, komentar, tanggal); produk tanpa ulasan menampilkan 'Belum ada ulasan untuk produk ini.' Paginasi muncul bila ulasan melebihi satu halaman (meta dari API). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): tab ulasan: API ulasan=5; UI: 3.4 (5 ulasan) / Ulasan (5); kosong -&gt; 'tidak terdeteksi'</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7542,7 @@
           <t>Bagian "Kamu Mungkin Suka" menampilkan produk terkait; klik membuka produk yang benar</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7567,7 +7567,7 @@
           <t>Slug produk tidak ada / produk nonaktif → halaman "Produk tidak ditemukan" + tombol kembali ke katalog</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7592,7 +7592,7 @@
           <t>Breadcrumb "Katalog Produk" berfungsi; judul tab memuat nama produk</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7617,7 +7617,7 @@
           <t>Skeleton loading detail produk tampil saat data dimuat</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7644,12 +7644,12 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): detail desain termuat (h1 nama desain) tanpa error.</t>
+          <t>info desain: Putaran 80 baris: detail desain 'Blanditiis deleniti tempore': nama, nama creator, rating (n ulasan), 'Terjual N kali', deskripsi tampil; gambar mengikuti file storage (placeholder seed QC tidak ada di disk, jadi memakai placeholder netral). | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): detail desain termuat (h1 nama desain) tanpa error.</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
           <t>Daftar produk yang tersedia untuk desain ini tampil; pilih produk, warna, ukuran berfungsi</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7692,7 +7692,7 @@
           <t>Preview menampilkan desain di atas produk yang dipilih (bukan gambar rusak)</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7717,14 +7717,14 @@
           <t>Rincian harga (Harga Produk / Kontribusi Desainer / Total) benar</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): rincian harga desain: setelah memilih produk/warna/ukuran baris yang tampil: Rp 380.000 | Rp 149.000 | Rp 380.000 | Mulai dari Rp 169.000 | Mulai dari Rp 201.000 | Mulai dari Rp 73.000 | Mulai dari Rp 201.000 | Total Terjual | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): rincian harga desain: rincian harga tidak ditemukan: Total Terjual | Bukti lain: UI (Pla</t>
+          <t>rincian harga desain: Putaran 80 baris: halaman desain menampilkan harga produk (mulai dari ...) dan total sesuai qty; baris 'Kontribusi Desainer' terpisah tidak ada karena komisi kreator adalah bagian dari harga produk (BR-007) - perlu keputusan pemilik bila ingin dirinci. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): rincian harga desain: setelah memilih produk/warna/ukuran baris yang tampil: Rp 380.000 | Rp 149.000 | Rp 380.000 | Mulai dari Rp 169.000 | Mulai dari Rp 201.000 | Mulai dari Rp 73.000 | M</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7742,7 @@
           <t>Quantity stepper berfungsi; minimum 1</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7767,7 +7767,7 @@
           <t>"Tambah ke Keranjang" tanpa pilih varian → pesan error yang sesuai; sukses → toast + badge keranjang</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7792,7 +7792,7 @@
           <t>"Beli Sekarang" berfungsi; guest diminta login</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7819,12 +7819,12 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): desain tanpa produk cocok: pesan 'Belum ada produk yang tersedia untuk desain ini' tidak terdeteksi: Pilih Produk / Pilih Warna Produk: Hitam</t>
+          <t>desain tanpa produk: Putaran 80 baris: desain tanpa produk cocok (blanditiis-deleniti-tempore) menampilkan 'Belum ada produk yang tersedia untuk desain ini' dan halaman tidak error. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): desain tanpa produk cocok: pesan 'Belum ada produk yang tersedia untuk desain ini' tidak terdeteksi: Pilih Produk / Pilih Warna Produk: Hitam</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
           <t>Kartu creator (foto, nama, Desain/Rating/Total Terjual) benar; "Lihat Profil" membuka profil creator</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7867,7 +7867,7 @@
           <t>"Koleksi Lainnya" menampilkan desain lain milik creator; "Lihat Semua →" berfungsi</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7892,7 +7892,7 @@
           <t>Tab Deskripsi, Detail Produk, Bahan &amp; Perawatan, Pengiriman, Ulasan berfungsi</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7917,7 +7917,7 @@
           <t>Desain yang belum published / creator di-ban → tidak dapat diakses ("Desain tidak ditemukan")</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7942,7 +7942,7 @@
           <t>Slug desain tidak ada → pesan + tombol kembali ke Lapak Desain</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7967,7 +7967,7 @@
           <t>Ikon wishlist desain berfungsi</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -7992,7 +7992,7 @@
           <t>Hero ("Tentang Harmoni Clothing"), Visi &amp; Misi (4 butir misi), "Kenapa Memilih Harmoni?" (6 alasan) tampil lengkap</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8017,7 +8017,7 @@
           <t>Section "Untuk Kreator Lokal" &amp; tombol "Jadi Kreator" berfungsi (guest → login/registrasi, user → /account/become-creator)</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8044,12 +8044,12 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): About: kata kunci: 2023:true 2024:true 2026:true Visi:false Misi:false Testimoni:false | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): timeline &amp; testimoni About: beberapa bagian tidak terdeteksi</t>
+          <t>Tentang kami: Putaran 80 baris: timeline 2023/2024/2026, Visi &amp; Misi, Prinsip, Proses Kami (4 langkah: Desain, Produksi, Quality Check, Sampai ke Kamu), dan Testimoni semuanya tampil. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): About: kata kunci: 2023:true 2024:true 2026:true Visi:false Misi:false Testimoni:false | Bukti lain: UI (Playwright, Edge headless, :3001 + backend QC): timeline &amp; testimoni About: beberap</t>
         </is>
       </c>
     </row>
@@ -8067,7 +8067,7 @@
           <t>Tombol "Daftar Gratis" di CTA akhir membuka modal registrasi</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8092,7 +8092,7 @@
           <t>Semua gambar/ilustrasi termuat, tidak ada broken image</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8117,7 +8117,7 @@
           <t>Konten berganti sesuai bahasa (ID/EN)</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8142,7 +8142,7 @@
           <t>Daftar pertanyaan-jawaban tampil lengkap &amp; dapat dibuka/ditutup (accordion) bila ada</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): isi FAQ/kebijakan konsisten: kata kunci aturan bisnis: /legal/returns: 7 hari=false, produksi ulang=false, refund=true || /legal/terms: Menunggu Approval=true, pembatalan=true || /faq: minimum=true, pengiriman=true || /legal/shipping: Biteship=false, ongkir=false; konsistensi makna perlu dibaca manusia</t>
+          <t>Putaran 80 baris: isi FAQ dibaca satu per satu terhadap aturan bisnis: tanpa minimum order (BR-009), produksi dimulai setelah bayar + approval admin (BR-003), belum dibayar dibatalkan 24 jam (BR-017), klaim lewat Retur &amp; Refund dan Chat admin (BR-016), kurir dan resi. Tidak ada klaim yang bertentangan; FAQ memang tidak menyebut lama produksi (angka ditentukan pemilik). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): isi FAQ/kebijakan konsisten: kata kunci aturan bisnis: /legal/returns: 7 hari=false, produksi ulang=false, refund=true || /legal/terms: Menunggu Approval=true, pembatalan=true || /faq: min</t>
         </is>
       </c>
     </row>
@@ -8194,12 +8194,12 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): tidak ada teks placeholder terdeteksi di FAQ; tanggal 'diperbarui' tidak dicek.</t>
+          <t>Putaran 80 baris: tidak ada teks placeholder atau 'Segera hadir' pada FAQ/legal; tanggal 'Terakhir diperbarui' kini 16 Oktober 2026 untuk FAQ, Retur, Pengiriman, dan Syarat &amp; Ketentuan (isi diubah hari ini); Kebijakan Privasi tetap 1 Juli 2026 (tidak berubah). | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): tidak ada teks placeholder terdeteksi di FAQ; tanggal 'diperbarui' tidak dicek.</t>
         </is>
       </c>
     </row>
@@ -8217,7 +8217,7 @@
           <t>Konten berganti sesuai bahasa; judul tab &amp; meta benar</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8292,7 +8292,7 @@
           <t>Teks intro (sertakan nomor pesanan) tampil; konten berganti sesuai bahasa</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8317,7 +8317,7 @@
           <t>4 kartu bantuan (FAQ, Retur &amp; Refund, Pengiriman, Kontak) tampil; tombol "Buka halaman" mengarah ke halaman yang benar</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8342,7 +8342,7 @@
           <t>Konten berganti sesuai bahasa; tidak ada tautan mati</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8369,12 +8369,12 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): /legal/returns termuat (1389 karakter).</t>
+          <t>Putaran 80 baris: Kebijakan Retur memuat 5 bagian: produk dibuat sesuai pesanan, klaim yang dapat diajukan, cara klaim (7 hari kalender setelah Selesai lewat Chat, BR-016), penyelesaian (cetak ulang atau pengembalian dana, BR-011/006), pembatalan (BR-010). Teks klaim diperbaiki dari '3 hari lewat halaman Kontak' agar sesuai aturan. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): /legal/returns termuat (1389 karakter).</t>
         </is>
       </c>
     </row>
@@ -8394,12 +8394,12 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): konsistensi kebijakan: kata kunci aturan (7 hari, produksi ulang, refund, Menunggu Approval, Biteship, ongkir) ada pada halaman kebijakan (lihat #115); kesesuaian makna dengan aturan bisnis perlu ditinjau manual</t>
+          <t>Putaran 80 baris: setelah perbaikan, isi retur konsisten dengan BR-006/010/011/015/016/018 dan dengan Syarat &amp; Ketentuan (pasal 5 kini juga menyatakan pesanan tidak dapat dibatalkan setelah produksi; klaim mengikuti Kebijakan Retur). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): konsistensi kebijakan: kata kunci aturan (7 hari, produksi ulang, refund, Menunggu Approval, Biteship, ongkir) ada pada halaman kebijakan (lihat #115); kesesuaian makna dengan aturan bisni</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8417,7 @@
           <t>Daftar Isi (TOC) berfungsi; konten berganti sesuai bahasa</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8444,12 +8444,12 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): /legal/shipping termuat (1129 karakter).</t>
+          <t>Putaran 80 baris: Kebijakan Pengiriman memuat kurir, ongkos kirim, waktu proses/estimasi, pelacakan resi, penerimaan, dan kini juga paket terlambat/hilang/bermasalah (hubungi admin via Chat dengan nomor pesanan). | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): /legal/shipping termuat (1129 karakter).</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): konsistensi kebijakan: kata kunci aturan (7 hari, produksi ulang, refund, Menunggu Approval, Biteship, ongkir) ada pada halaman kebijakan (lihat #115); kesesuaian makna dengan aturan bisnis perlu ditinjau manual</t>
+          <t>Putaran 80 baris: isi sesuai perilaku sistem: kurir dari mitra logistik dipilih di checkout sesuai alamat, ongkir dihitung otomatis dari alamat/berat/kurir, resi muncul di detail pesanan, auto-selesai 3 hari kerja (BR-014). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): konsistensi kebijakan: kata kunci aturan (7 hari, produksi ulang, refund, Menunggu Approval, Biteship, ongkir) ada pada halaman kebijakan (lihat #115); kesesuaian makna dengan aturan bisni</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
           <t>Daftar Isi berfungsi; konten berganti sesuai bahasa</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): /legal/privacy-policy termuat (1757 karakter).</t>
+          <t>Putaran 80 baris: Kebijakan Privasi memuat 6 bagian (data yang dikumpulkan, penggunaan, berbagi dengan pihak ketiga, keamanan, hak pengguna, perubahan) dan tanggal 'Terakhir diperbarui: 1 Juli 2026'; terbaca penuh. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): /legal/privacy-policy termuat (1757 karakter).</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
           <t>Daftar Isi (TOC) di sisi kanan berfungsi (klik loncat ke bagian terkait); di mobile tetap rapi</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8567,7 +8567,7 @@
           <t>Tautan dari checkbox registrasi membuka halaman ini (tab baru) tanpa menutup form</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (localhost:3001 + backend QC): /legal/terms termuat (1647 karakter).</t>
+          <t>Putaran 80 baris: Syarat &amp; Ketentuan memuat 7 bagian (definisi, akun, pemesanan &amp; pembayaran, hak kreator, pembatalan, batasan tanggung jawab, perubahan) dan tanggal 'Terakhir diperbarui'. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): /legal/terms termuat (1647 karakter).</t>
         </is>
       </c>
     </row>
@@ -8619,12 +8619,12 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): konsistensi kebijakan: kata kunci aturan (7 hari, produksi ulang, refund, Menunggu Approval, Biteship, ongkir) ada pada halaman kebijakan (lihat #115); kesesuaian makna dengan aturan bisnis perlu ditinjau manual</t>
+          <t>daftar isi: Putaran 80 baris: Daftar Isi punya 7 tautan jangkar; mengklik salah satunya menggulir ke bagiannya. Isi pembatalan di Syarat &amp; Ketentuan kini sama dengan Kebijakan Retur (pesanan dapat dibatalkan hanya saat menunggu approval; klaim kualitas mengikuti Kebijakan Retur &amp; Refund). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): konsistensi kebijakan: kata kunci aturan (7 hari, produksi ulang, refund, Menunggu Approval, Biteship, ongkir) ada pada halaman kebijakan (lihat #115); kesesuaian makna dengan aturan bisni</t>
         </is>
       </c>
     </row>
@@ -8644,12 +8644,12 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (Playwright, putaran 2): checkbox registrasi memiliki tautan /legal/terms; tetapi checkbox 'Saya menyetujui Syarat &amp; Ketentuan Creator' di /account/become-creator berupa teks biasa tanpa tautan ke halaman Syarat &amp; Ketentuan.</t>
+          <t>tautan syarat di become-creator: Putaran 80 baris: checkbox syarat creator kini punya tautan 'Baca Syarat &amp; Ketentuan' -&gt; /legal/terms (tab baru); checkbox registrasi sudah punya tautan sebelumnya. | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): checkbox registrasi memiliki tautan /legal/terms; tetapi checkbox 'Saya menyetujui Syarat &amp; Ketentuan Creator' di /account/become-creator berupa teks biasa tanpa tautan ke halaman Syarat &amp; Ketentuan.</t>
         </is>
       </c>
     </row>
@@ -8667,7 +8667,7 @@
           <t>Modal terbuka dari tombol Masuk, dari halaman terproteksi (redirect), dan dari aksi yang butuh login</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8692,7 +8692,7 @@
           <t>Login dengan data benar berhasil &amp; diarahkan sesuai role (customer/creator/admin) atau kembali ke halaman asal</t>
         </is>
       </c>
-      <c r="D137" s="4" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8717,7 +8717,7 @@
           <t>Login dengan email/password salah menampilkan pesan "Email atau password salah"</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8742,7 +8742,7 @@
           <t>Login akun yang belum verifikasi email menampilkan pesan belum verifikasi + opsi kirim ulang</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8767,7 +8767,7 @@
           <t>Login akun yang di-ban/nonaktif ditolak dengan pesan yang sesuai</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8792,7 +8792,7 @@
           <t>Field kosong / format email salah ditolak (validasi) tanpa request ke server</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8817,7 +8817,7 @@
           <t>Tombol mata "Tampilkan/Sembunyikan password" berfungsi</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8842,7 +8842,7 @@
           <t>Rate limit: 5 percobaan/menit per email+IP — percobaan ke-6 diblokir dengan pesan 429 yang jelas</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8867,7 +8867,7 @@
           <t>Tautan "Lupa password?" &amp; "Daftar" di dalam modal berfungsi</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8894,12 +8894,12 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tutup modal: Esc/X/backdrop menutup; fokus keluar modal pada 14/14 Tab</t>
+          <t>fokus terkunci di modal: Putaran 80 baris: modal kini role=dialog aria-modal; 16x Tab dan 6x Shift+Tab fokus tetap di dalam modal (terkunci), Esc menutup. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): tutup modal: Esc/X/backdrop menutup; fokus keluar modal pada 14/14 Tab</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
           <t>Tombol submit menampilkan loading &amp; tidak bisa diklik ganda</t>
         </is>
       </c>
-      <c r="D146" s="4" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8942,7 +8942,7 @@
           <t>Setelah login, header berubah (avatar/nama), keranjang &amp; notifikasi termuat tanpa refresh manual</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8967,7 +8967,7 @@
           <t>Registrasi dengan data valid berhasil &amp; pesan "Akun berhasil dibuat. Silakan masuk" tampil</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -8992,7 +8992,7 @@
           <t>Nama wajib (maks 150), email valid &amp; unik (maks 255), password min 8 karakter, konfirmasi password harus cocok</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9017,7 +9017,7 @@
           <t>Email yang sudah terdaftar ditolak dengan pesan yang jelas</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9042,7 +9042,7 @@
           <t>Konfirmasi password berbeda → pesan "Konfirmasi password tidak cocok"</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9067,7 +9067,7 @@
           <t>Checkbox Syarat &amp; Ketentuan dan Kebijakan Privasi wajib dicentang; tanpa centang form ditolak</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9092,7 +9092,7 @@
           <t>Tautan Syarat &amp; Ketentuan / Kebijakan Privasi membuka halaman yang benar</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9119,12 +9119,12 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): isi email verifikasi (mail log): email (mail=log): Subject: Verifikasi Alamat Email Anda; tautan ke frontend /verify-email berisi id/hash/expires/signature=true; tombol 'Verifikasi Email' di isi=true; pengiriman ke inbox/spam tidak dapat diuji</t>
+          <t xml:space="preserve">isi email verifikasi: Putaran 80 baris: registrasi 201: email terkirim ke log, subjek 'Verifikasi Alamat Email Anda', tautan http://localhost:3001/verify-email?id=22&amp;hash=ce9bf8cdab970e7eee777d8d9f0df9fc5328c81d&amp;expires=1792117123&amp;sign (domain frontend, bertanda tangan). Pengiriman ke inbox/spam nyata hanya bisa diuji dengan SMTP asli. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): isi email verifikasi (mail log): email (mail=log): Subject: Verifikasi Alamat Email Anda; tautan ke frontend /verify-email berisi id/hash/expires/signature=true; tombol 'Verifikasi Email' </t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
           <t>Tautan "Sudah punya akun? Masuk" berpindah ke modal login</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9167,7 +9167,7 @@
           <t>Rate limit endpoint auth (20/menit per IP) memberi pesan 429 yang jelas bila terlampaui</t>
         </is>
       </c>
-      <c r="D156" s="4" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9192,7 +9192,7 @@
           <t>Password tampil/sembunyi berfungsi pada kedua field password</t>
         </is>
       </c>
-      <c r="D157" s="4" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9217,7 +9217,7 @@
           <t>Submit email terdaftar menampilkan pesan netral "Jika email terdaftar, tautan reset password telah dikirim" &amp; email terkirim</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9242,7 +9242,7 @@
           <t>Submit email TIDAK terdaftar menampilkan pesan yang SAMA (tidak membocorkan keberadaan akun)</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9267,7 +9267,7 @@
           <t>Format email salah / kosong ditolak oleh validasi</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): isi email reset (mail log): email: Subject: Verifikasi Alamat Email Anda; tautan /reset-password?token=...=false; masa berlaku 'tidak ditemukan'; render inbox tidak dapat diuji</t>
+          <t>isi email reset: Putaran 80 baris: email reset: subjek 'Reset Password Anda', tautan http://localhost:3001/reset-password?token=a2cea4e5400449d9d30560e6121aa490dba6f061175205373f752f4f3..., masa berlaku '60 menit', berbahasa Indonesia. Render di inbox nyata tidak diuji. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): isi email reset (mail log): email: Subject: Verifikasi Alamat Email Anda; tautan /reset-password?token=...=false; masa berlaku 'tidak ditemukan'; render inbox tidak dapat diuji</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
           <t>Tautan "Kembali ke Masuk" berfungsi</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9342,7 +9342,7 @@
           <t>Tautan dari email membuka halaman dengan token &amp; email terisi otomatis</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9367,7 +9367,7 @@
           <t>Submit password baru (min 8) + konfirmasi cocok berhasil; pesan sukses tampil; bisa login dengan password baru</t>
         </is>
       </c>
-      <c r="D164" s="4" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9394,12 +9394,12 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Sheet Keamanan #7: reset sukses menyetel password baru; login lama tidak diuji ulang.</t>
+          <t>password lama setelah reset: Putaran 80 baris: lupa password 200 -&gt; reset 200 -&gt; login dengan password lama 422 (ditolak), password baru 200. | Sebelumnya (Sebagian): Sheet Keamanan #7: reset sukses menyetel password baru; login lama tidak diuji ulang.</t>
         </is>
       </c>
     </row>
@@ -9417,7 +9417,7 @@
           <t>Konfirmasi tidak cocok / password terlalu pendek ditolak dengan pesan yang jelas</t>
         </is>
       </c>
-      <c r="D166" s="4" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9442,7 +9442,7 @@
           <t>Token kedaluwarsa / sudah dipakai / tidak valid menampilkan pesan error yang sesuai</t>
         </is>
       </c>
-      <c r="D167" s="4" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9467,7 +9467,7 @@
           <t>Membuka /reset-password tanpa token menampilkan pesan error (bukan crash)</t>
         </is>
       </c>
-      <c r="D168" s="4" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9492,7 +9492,7 @@
           <t>Tombol tampil/sembunyikan password berfungsi</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9517,7 +9517,7 @@
           <t>Klik tautan verifikasi dari email → tampil "Memverifikasi..." lalu "Email berhasil diverifikasi" + tombol Masuk</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9542,7 +9542,7 @@
           <t>Setelah verifikasi, akun dapat login; sebelumnya ditolak login karena belum verifikasi</t>
         </is>
       </c>
-      <c r="D171" s="4" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9567,7 +9567,7 @@
           <t>Tautan kedaluwarsa / signature rusak / id-hash tidak cocok menampilkan pesan error yang sesuai</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9592,7 +9592,7 @@
           <t>Membuka tautan yang sama dua kali (sudah terverifikasi) tidak menimbulkan error fatal</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9617,7 +9617,7 @@
           <t>Fitur "kirim ulang verifikasi" (dari login) mengirim email baru; pesan netral (tidak membocorkan akun)</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9642,7 +9642,7 @@
           <t>Halaman tidak diindeks mesin pencari (noindex)</t>
         </is>
       </c>
-      <c r="D175" s="4" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9669,12 +9669,12 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>/sitemap.xml 200 memuat beranda, catalog, marketplace, about, faq, pusat-bantuan, kontak, legal; halaman dinamis (produk/desain) tidak terdaftar.</t>
+          <t>sitemap dinamis: Putaran 80 baris: /sitemap.xml 200: halaman statis lengkap + 10 URL produk dan 15 URL desain dari API (diperbarui tiap jam). Domain produksi: dicek setelah deploy. | Sebelumnya (Sebagian): /sitemap.xml 200 memuat beranda, catalog, marketplace, about, faq, pusat-bantuan, kontak, legal; halaman dinamis (produk/desain) tidak terdaftar.</t>
         </is>
       </c>
     </row>
@@ -9694,12 +9694,12 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>/robots.txt: Disallow /admin /creator /account /cart /checkout /api + Sitemap; /notifications tidak di-disallow (tetapi noindex pada meta).</t>
+          <t>robots: Putaran 80 baris: robots.txt: Disallow /admin /creator /account /cart /checkout /api + baris Sitemap; /notifications tidak di-disallow tetapi halamannya noindex. | Sebelumnya (Sebagian): /robots.txt: Disallow /admin /creator /account /cart /checkout /api + Sitemap; /notifications tidak di-disallow (tetapi noindex pada meta).</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
           <t>Halaman privat (admin/creator/customer/auth) memiliki meta noindex</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9744,12 +9744,12 @@
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>Title &amp; description unik pada /, /catalog, /marketplace, /about, /faq, /kontak, /legal/terms, /pusat-bantuan; og:title ada. Gambar OG tidak dicek.</t>
+          <t>meta SEO: Putaran 80 baris: /, /catalog, /about, /faq: &lt;title&gt;, meta description, og:title, og:description, og:image (https://harmoniclothing.com/logo.png) ada pada semuanya; kartu pratinjau di platform sosial tidak diuji. | Sebelumnya (Sebagian): Title &amp; description unik pada /, /catalog, /marketplace, /about, /faq, /kontak, /legal/terms, /pusat-bantuan; og:title ada. Gambar OG tidak dicek.</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9767,7 @@
           <t>Favicon &amp; ikon aplikasi tampil</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9840,7 +9840,7 @@
           <t>Avatar/foto &amp; nama user tampil; menu dropdown akun terbuka/tertutup (klik luar menutup)</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9867,12 +9867,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (login test@example.com): menu akun memuat Profil, Address Book, Riwayat Pesanan, Wishlist, Ajukan Upgrade Creator, Notifikasi, Keluar; 'Keranjang' berupa ikon terpisah di header.</t>
+          <t>menu akun: Putaran 80 baris: menu akun (hover) memuat Profil, Address Book, Riwayat Pesanan, Wishlist, Ajukan Upgrade Creator, Notifikasi dengan href benar + Keluar; Keranjang berupa ikon terpisah (CartPopover) sesuai desain. | Sebelumnya (Sebagian): Browser QC (login test@example.com): menu akun memuat Profil, Address Book, Riwayat Pesanan, Wishlist, Ajukan Upgrade Creator, Notifikasi, Keluar; 'Keranjang' berupa ikon terpisah di header.</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tombol Kreator: akun customer biasa melihat tautan 'Kreator' -&gt; /creator/dashboard | Bukti lain: Browser QC (login test@example.com): akun customer biasa melihat tautan 'Kreator' di header; tujuan/versi 'Jadi Kreator' belum diverifikasi.</t>
+          <t>tombol Kreator: Putaran 80 baris: tombol 'Kreator' di header mengarah ke /creator/dashboard; untuk akun customer biasa halaman itu menampilkan ajakan/penjaga akses (CreatorGuard), bukan crash. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): tombol Kreator: akun customer biasa melihat tautan 'Kreator' -&gt; /creator/dashboard | Bukti lain: Browser QC (login test@example.com): akun customer biasa melihat tautan 'Kreator' di header</t>
         </is>
       </c>
     </row>
@@ -9917,12 +9917,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): menu Admin Dashboard: header admin tidak memuat tautan /admin/dashboard (header: Beranda | Produk | Desain | Tentang Kami | ID | EN | 8 | Kreator | Admin Harmoni)</t>
+          <t>menu admin: Putaran 80 baris: akun admin: menu akun memuat 'Admin Dashboard' -&gt; /admin/dashboard (halaman termuat); ikon keranjang dan tombol Kreator disembunyikan untuk admin (Permission Matrix: admin tidak berbelanja). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): menu Admin Dashboard: header admin tidak memuat tautan /admin/dashboard (header: Beranda | Produk | Desain | Tentang Kami | ID | EN | 8 | Kreator | Admin Harmoni)</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
           <t>Logout menampilkan dialog konfirmasi "Apakah Anda yakin ingin keluar?"; Batal tetap login; Konfirmasi keluar &amp; ke beranda</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9965,7 +9965,7 @@
           <t>Setelah logout, tombol Back browser tidak menampilkan data akun sebelumnya</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -9992,12 +9992,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): flicker header: tidak dapat diukur secara headless; tidak ditemukan kilatan state guest pada pengamatan browser (header langsung memuat nama setelah login)</t>
+          <t>header tidak berkedip: Putaran 80 baris: memuat /account/profile sambil login dan mencuplik header tiap 250ms selama 10 detik: tombol 'Masuk' tidak pernah muncul (header menunggu status auth ready sebelum merender; 0 cuplikan sudah memuat nama). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): flicker header: tidak dapat diukur secara headless; tidak ditemukan kilatan state guest pada pengamatan browser (header langsung memuat nama setelah login)</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
           <t>Badge jumlah item benar &amp; ter-update tanpa refresh saat tambah/hapus item</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10040,7 +10040,7 @@
           <t>Popover menampilkan item terbaru (gambar, nama, varian, qty, harga) &amp; subtotal benar</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10065,7 +10065,7 @@
           <t>Keranjang kosong menampilkan "Keranjangmu masih kosong"</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10090,7 +10090,7 @@
           <t>Tombol "Lanjut ke Checkout" membuka /cart atau /checkout yang benar</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10121,7 +10121,7 @@
           <t>Klik di luar popover menutupnya; di mobile tetap dapat dipakai</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10146,7 +10146,7 @@
           <t>Badge jumlah belum dibaca benar; ter-update real-time saat notifikasi baru masuk (tanpa refresh)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10171,7 +10171,7 @@
           <t>Popover menampilkan notifikasi terbaru; kosong → "Belum ada notifikasi"</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10196,7 +10196,7 @@
           <t>"Tandai semua dibaca" mengosongkan badge &amp; mengubah tampilan item</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10221,7 +10221,7 @@
           <t>Klik satu notifikasi menandainya dibaca &amp; mengarah ke halaman terkait</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10246,7 +10246,7 @@
           <t>Halaman termuat dengan produk yang benar; slug salah → pesan "tidak ditemukan" (bukan crash)</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10271,7 +10271,7 @@
           <t>Pilih warna &amp; ukuran mengubah gambar mockup &amp; harga; chip ukuran terpilih tampak aktif (ter-highlight)</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10298,12 +10298,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tampilan Depan/Belakang/Samping: tombol tampilan tidak terdeteksi</t>
+          <t>tombol tampilan: Putaran 80 baris: tiga label 'Depan/Belakang/Samping' yang tidak berfungsi dihapus (hanya satu foto mockup per varian, jadi tidak ada tampilan lain untuk diganti); pratinjau memakai foto sesuai warna. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): tampilan Depan/Belakang/Samping: tombol tampilan tidak terdeteksi</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10321,7 @@
           <t>Mode Custom: upload desain sendiri (PNG/JPG ≤ 20MB) berhasil; file salah format/terlalu besar ditolak</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10348,12 +10348,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI (Playwright, Edge headless, :3001 + backend QC): mode marketplace customize ?design=: teks halaman: </t>
+          <t xml:space="preserve">mode marketplace customize: Putaran 80 baris: ?design=: nama desain, creator ('by ...'), thumbnail dan tautan 'Ganti Desain' (-&gt; /marketplace) tampil; label Depan/Belakang/Samping dihapus karena hanya ada satu foto mockup per varian. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): mode marketplace customize ?design=: teks halaman: </t>
         </is>
       </c>
     </row>
@@ -10371,14 +10371,14 @@
           <t>Rincian harga (Harga Produk / Kontribusi Desainer / Total) terhitung benar sesuai qty</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (login test@example.com): editor menampilkan Harga Produk Rp 452.000 dan Total sesuai qty 1; rincian 'Kontribusi Desainer' (mode marketplace) tidak diuji.</t>
+          <t>rincian harga: Putaran 80 baris: harga terhitung benar sesuai qty (qty 1 -&gt; subtotal Rp 456000.00 di keranjang). Baris 'Kontribusi Desainer' terpisah tidak ada: komisi kreator adalah bagian dari harga produk (BR-007), bukan biaya tambahan - butuh keputusan pemilik bila ingin ditampilkan. | Sebelumnya (Sebagian): Browser QC (login test@example.com): editor menampilkan Harga Produk Rp 452.000 dan Total sesuai qty 1; rincian 'Kontribusi Desainer' (mode marketplace) tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -10398,12 +10398,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (login test@example.com): kolom Jumlah (1) dan Catatan (opsional) tampil; stepper tidak diuji.</t>
+          <t>stepper dan catatan: Putaran 80 baris: stepper: tombol kurang nonaktif di 1, dua klik tambah -&gt; 3; catatan 'Catatan uji QC' tersimpan; item keranjang baru qty=3, notes='Catatan uji QC'. | Sebelumnya (Sebagian): Browser QC (login test@example.com): kolom Jumlah (1) dan Catatan (opsional) tampil; stepper tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10421,7 @@
           <t>"Tambah ke Keranjang" tanpa pilih varian → pesan error; sukses → toast &amp; badge keranjang bertambah</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10448,12 +10448,12 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (login test@example.com): editor memuat catatan 'Preview 3D real-time ... (belum tersedia, menampilkan mockup foto sesuai warna terpilih)' - jujur bahwa 3D belum ada, tetapi teksnya membingungkan ('update otomatis').</t>
+          <t>catatan preview: Putaran 80 baris: catatan kini jelas: 'Pratinjau berupa foto mockup sesuai warna terpilih. Pratinjau 3D real-time belum tersedia.' (tidak lagi menjanjikan update otomatis). | Sebelumnya (Sebagian): Browser QC (login test@example.com): editor memuat catatan 'Preview 3D real-time ... (belum tersedia, menampilkan mockup foto sesuai warna terpilih)' - jujur bahwa 3D belum ada, tetapi teksnya membingungkan ('update otomatis').</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
           <t>Guest yang membuka halaman ini diarahkan/di-prompt login</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10496,7 +10496,7 @@
           <t>Semua item tampil benar (gambar, nama, varian warna/ukuran, desain, catatan, qty, harga satuan, subtotal)</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10521,7 +10521,7 @@
           <t>Ubah qty (+/−) memperbarui subtotal &amp; total; qty minimum 1</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10548,12 +10548,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): hapus item &amp; keranjang kosong: sisa item 1; teks: Keranjang | Pilih Semua (1) | Harmoni Clothing | Ut doloremque neque | L · Hitam | Rp 904.000 | 2 |  | Bukti lain: Browser QC (login test@example.com): keranjang kosong: state kosong + 'Mulai Belanja'. Hapus item via API diuji (sheet Validasi #30).</t>
+          <t>hapus item dan keranjang kosong: Putaran 80 baris: dari 4 item: tombol hapus per item menghapusnya satu per satu; keranjang kosong menampilkan state kosong + tombol 'Mulai Belanja'. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): hapus item &amp; keranjang kosong: sisa item 1; teks: Keranjang | Pilih Semua (1) | Harmoni Clothing | Ut doloremque neque | L · Hitam | Rp 904.000 | 2 |  | Bukti lain: Browser QC (login test@</t>
         </is>
       </c>
     </row>
@@ -10571,7 +10571,7 @@
           <t>Centang item per baris &amp; "Pilih Semua (n)" berfungsi; total hanya menghitung item terpilih</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10596,7 +10596,7 @@
           <t>Tombol "Pindahkan ke wishlist" memindahkan item &amp; menampilkan toast</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10621,7 +10621,7 @@
           <t>Item yang produknya sudah nonaktif ditandai "Produk ini sudah tidak tersedia" &amp; tidak bisa di-checkout</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10646,7 +10646,7 @@
           <t>Harga item mengikuti harga saat ditambahkan ke keranjang (BR-025), bukan harga terbaru bila admin mengubah harga</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10671,7 +10671,7 @@
           <t>Tombol "Beli" tanpa item terpilih tidak aktif; dengan item terpilih membuka /checkout (tidak macet/loading terus)</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10696,7 +10696,7 @@
           <t>Tidak ada infinite re-render / lag saat memilih item (regresi bug lama)</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10721,7 +10721,7 @@
           <t>Setelah checkout berhasil, item yang dibeli hilang dari keranjang; item yang tidak dipilih tetap ada</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10746,7 +10746,7 @@
           <t>Keranjang tetap tersimpan setelah logout-login &amp; lintas perangkat</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10771,7 +10771,7 @@
           <t>Format Rupiah benar di semua angka</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10796,7 +10796,7 @@
           <t>Mengakses /checkout tanpa item terpilih diarahkan kembali ke keranjang (tidak crash)</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10821,7 +10821,7 @@
           <t>Alamat utama otomatis terpilih bila ada; belum ada alamat → pesan + tautan ke Address Book</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10846,7 +10846,7 @@
           <t>Pilih alamat lain berfungsi; ganti alamat memuat ulang pilihan kurir &amp; ongkir</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10871,7 +10871,7 @@
           <t>Pilihan kurir &amp; ongkir dari Biteship tampil (nama kurir, layanan, harga, estimasi); "Menghitung ongkir..." tampil saat loading</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10898,12 +10898,12 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>API: kurir yang tidak tersedia -&gt; 422 'Kurir yang dipilih tidak tersedia untuk alamat ini' (alamat seed acak). UI tidak diuji.</t>
+          <t>kurir tidak tersedia: Putaran 80 baris: alamat tanpa kurir: 'Kurir tidak tersedia untuk alamat ini.'; akun tanpa alamat: Pilih alamat pengiriman untuk melihat pilihan kurir.. | Sebelumnya (Sebagian): API: kurir yang tidak tersedia -&gt; 422 'Kurir yang dipilih tidak tersedia untuk alamat ini' (alamat seed acak). UI tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -10921,7 +10921,7 @@
           <t>Ringkasan pesanan (item, qty, catatan, subtotal, ongkos kirim, total) benar &amp; total = subtotal + ongkir</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10946,7 +10946,7 @@
           <t>Submit tanpa alamat → "Pilih alamat pengiriman terlebih dahulu"; tanpa kurir → "Pilih kurir pengiriman terlebih dahulu"</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10971,7 +10971,7 @@
           <t>Tombol "Buat Pesanan" loading &amp; tidak bisa diklik ganda (tidak membuat pesanan ganda)</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -10996,7 +10996,7 @@
           <t>Submit berhasil membuat pesanan status "Belum Dibayar" &amp; mengarahkan ke halaman pembayaran Midtrans Snap</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11046,7 +11046,7 @@
           <t>Setelah bayar sukses, status pesanan otomatis "Menunggu Approval" (webhook) &amp; notifikasi "pesanan dibayar" masuk</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -11096,7 +11096,7 @@
           <t>Ongkir tidak bisa dimanipulasi dari klien (harga dihitung ulang server dari kurir pilihan)</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11121,7 +11121,7 @@
           <t>Produk yang dinonaktifkan setelah masuk keranjang membuat checkout ditolak dengan pesan yang jelas</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11148,12 +11148,12 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): checkout mobile: keranjang 375px tanpa overflow=true; teks 'Pembayaran aman' tidak dicari</t>
+          <t>teks aman dan mobile: Putaran 80 baris: teks 'Pembayaran aman &amp; terenkripsi' tampil di bawah tombol Buat Pesanan; di 375px tanpa overflow horizontal (0px). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): checkout mobile: keranjang 375px tanpa overflow=true; teks 'Pembayaran aman' tidak dicari</t>
         </is>
       </c>
     </row>
@@ -11171,7 +11171,7 @@
           <t>Halaman termuat dari tautan "Pesan lewat Bulk Order" di detail produk; slug salah → "Produk tidak ditemukan"</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11196,7 +11196,7 @@
           <t>Tabel qty per kombinasi warna/ukuran dapat diisi; "Total Kuantitas" terhitung benar (jumlah semua ukuran)</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11221,7 +11221,7 @@
           <t>Tabel "Tingkat Harga Bulk" tampil sesuai tier di database (min/maks qty, harga per unit)</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11246,7 +11246,7 @@
           <t>Tier aktif ter-highlight otomatis sesuai total kuantitas; "Total Harga" = qty × harga tier</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11271,7 +11271,7 @@
           <t>Harga tier dihitung dari TOTAL kuantitas semua ukuran, bukan per-ukuran (BR-012)</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11296,7 +11296,7 @@
           <t>Total kuantitas di bawah tier terendah → pesan "belum memenuhi tingkat harga"; tombol lanjut ditolak</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11321,7 +11321,7 @@
           <t>Tidak mengisi qty apa pun → pesan "Isi kuantitas minimal satu ukuran"</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11346,7 +11346,7 @@
           <t>Upload desain sendiri (opsional) berfungsi; link pilih desain marketplace berfungsi; catatan opsional tersimpan</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -11371,7 +11371,7 @@
           <t>"Lanjut ke Checkout Bulk" membawa draft (varian, qty, desain, catatan) ke /checkout/bulk</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11396,7 +11396,7 @@
           <t>Bulk Order TIDAK tercampur dengan item keranjang reguler (BR-026)</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11421,7 +11421,7 @@
           <t>Membuka tanpa draft → pesan "Belum ada draft Bulk Order" + tombol ke katalog</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11446,7 +11446,7 @@
           <t>Alamat &amp; kurir berfungsi sama seperti checkout reguler (ongkos dihitung dari total qty)</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11471,7 +11471,7 @@
           <t>Ringkasan menampilkan desain, catatan, "Harga per unit (n pcs)", subtotal, ongkir, total benar (harga tier, bukan harga satuan biasa)</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11496,7 +11496,7 @@
           <t>Validasi: tanpa alamat/kurir ditolak dengan pesan yang sesuai; tombol loading anti klik ganda</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11521,7 +11521,7 @@
           <t>Submit berhasil membuat pesanan bertipe bulk (status Belum Dibayar) &amp; mengarah ke pembayaran</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11546,7 +11546,7 @@
           <t>Draft dibersihkan setelah pesanan dibuat; refresh halaman tidak membuat pesanan ganda</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11573,12 +11573,12 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (login test@example.com): /account/orders memuat daftar pesanan (1.597 karakter).</t>
+          <t>riwayat pesanan: Putaran 80 baris: 8 pesanan tampil urut terbaru (cocok dengan urutan API), tiap kartu memuat nomor, tanggal (8 tanggal), total Rp, dan badge status. | Sebelumnya (Sebagian): Browser QC (login test@example.com): /account/orders memuat daftar pesanan (1.597 karakter).</t>
         </is>
       </c>
     </row>
@@ -11596,7 +11596,7 @@
           <t>Filter/tab status (Semua + 8 status termasuk Ditolak &amp; Dibatalkan) berfungsi</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11621,7 +11621,7 @@
           <t>Badge status berwarna sesuai status; tombol "Lihat Detail" membuka pesanan yang benar</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11646,7 +11646,7 @@
           <t>Belum ada pesanan menampilkan state kosong</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11671,7 +11671,7 @@
           <t>Customer hanya melihat pesanannya sendiri; mengakses ID pesanan orang lain → 404 (bukan 403/data bocor)</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11696,7 +11696,7 @@
           <t>Paginasi/muat lebih banyak berfungsi bila pesanan banyak</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11721,7 +11721,7 @@
           <t>Timeline (Dibuat, Menunggu Approval, Diproduksi, Dikirim, Menunggu Konfirmasi, Selesai) sesuai status aktual</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11746,7 +11746,7 @@
           <t>Pesanan Ditolak menampilkan judul "Pesanan Ditolak" + alasan penolakan admin</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11771,7 +11771,7 @@
           <t>Pesanan Dibatalkan (manual/otomatis) menampilkan status yang jelas</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11796,7 +11796,7 @@
           <t>Info item (produk, varian, qty, harga), alamat, kurir, nomor resi (bila ada) benar</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11821,7 +11821,7 @@
           <t>Ringkasan subtotal + ongkir = total benar</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11846,7 +11846,7 @@
           <t>"Batalkan Pesanan" hanya muncul saat "Menunggu Approval" (BR-010); sukses → status Dibatalkan; di status lain tombol tidak ada &amp; API menolak</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11871,7 +11871,7 @@
           <t>Pesanan "Belum Dibayar": tautan/tombol bayar (jika ada) berfungsi; setelah 24 jam otomatis Dibatalkan (BR-017)</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11896,7 +11896,7 @@
           <t>"Konfirmasi Diterima" hanya muncul saat "Menunggu Konfirmasi"; sukses → Selesai (BR-014)</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11921,7 +11921,7 @@
           <t>"Pesan Lagi" (reorder) menambah item ke keranjang pada HARGA TERKINI; produk nonaktif dilewati</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11946,7 +11946,7 @@
           <t>Form rating &amp; ulasan muncul per item saat "Selesai" (BR-004): pilih bintang 1–5, komentar opsional, kirim berhasil → tampilan baca-saja</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11971,7 +11971,7 @@
           <t>Submit rating tanpa pilih bintang → pesan "Pilih rating bintang terlebih dahulu"; tidak bisa mengulas dua kali</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -11996,7 +11996,7 @@
           <t>Tautan "Lihat Invoice" membuka invoice pesanan</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12021,14 +12021,14 @@
           <t>Pratinjau desain per item (file yang dikirim customer / desain marketplace) tampil benar</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (Playwright, putaran 2): detail pesanan HC-20261013-7551 (item dengan desain marketplace): pratinjau desain tampil sebagai thumbnail kecil 64px (placeholder seed 'designs/thumbnails/placeholder.png'); API mengirim design_file_url dan custom_design_url. File desain unggahan customer sendiri belum diuji.</t>
+          <t>pratinjau desain per item: Putaran 80 baris: pratinjau desain marketplace di detail pesanan tampil (thumbnail), dan API mengirim custom_design_url untuk unggahan customer sendiri; render berkas unggahan customer di UI butuh pesanan berisi unggahan (checkout Snap) - belum dibuat di data QC. | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): detail pesanan HC-20261013-7551 (item dengan desain marketplace): pratinjau desain tampil sebagai thumbnail kecil 64px (placeholder seed 'designs/thumbnails/placeholder.png'); API mengirim design_file_url</t>
         </is>
       </c>
     </row>
@@ -12046,7 +12046,7 @@
           <t>Status berubah dari sisi admin → tampilan customer ter-update (setelah refresh/real-time)</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12071,7 +12071,7 @@
           <t>ID pesanan tidak ada / milik orang lain → "Pesanan tidak ditemukan"</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12096,7 +12096,7 @@
           <t>Nomor invoice, tanggal terbit, data penjual &amp; pembeli, rincian item, subtotal, ongkir, total dibayar sesuai pesanan</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12121,7 +12121,7 @@
           <t>Badge "Lunas" hanya untuk pesanan yang sudah dibayar</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12146,7 +12146,7 @@
           <t>Pesanan belum dibayar → pesan "Invoice belum tersedia" (bukan invoice kosong)</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12171,7 +12171,7 @@
           <t>Tombol Print membuka dialog cetak dengan tata letak rapi; tombol Kembali berfungsi</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12196,7 +12196,7 @@
           <t>Invoice pesanan orang lain tidak dapat diakses</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12221,7 +12221,7 @@
           <t>Data awal (nama, telepon, email) terisi benar; email tidak dapat diubah</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12246,7 +12246,7 @@
           <t>Ubah nama (wajib, maks 150) &amp; nomor telepon (maks 20) tersimpan; toast sukses; header ikut berubah</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12271,7 +12271,7 @@
           <t>Nama kosong ditolak validasi</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12296,7 +12296,7 @@
           <t>Upload foto: JPG/PNG/WebP ≤ 5MB; dialog crop persegi muncul; "Simpan Foto" menyimpan &amp; foto langsung tampil di header</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12321,7 +12321,7 @@
           <t>Foto salah format / &gt; 5MB ditolak dengan pesan error</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12346,7 +12346,7 @@
           <t>Batal pada dialog crop tidak mengubah foto lama</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12373,12 +12373,12 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): hapus foto: tombol 'Hapus Foto' tidak tampil (belum ada foto)</t>
+          <t>hapus foto profil: Putaran 80 baris: setelah unggah tombol 'Hapus Foto' muncul; menekannya menghapus foto (photo_url null) dan kembali ke avatar default. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): hapus foto: tombol 'Hapus Foto' tidak tampil (belum ada foto)</t>
         </is>
       </c>
     </row>
@@ -12398,12 +12398,12 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): foto profil tidak broken setelah reload: user tidak punya foto (kunci /me: id,name,email,phone,photo_url,role,status,email_verified_at); unggah foto nyata tidak diuji</t>
+          <t>foto tidak broken: Putaran 80 baris: unggah foto: API /me photo_url terisi; setelah reload gambar termuat (naturalWidth 64px) dari storage. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): foto profil tidak broken setelah reload: user tidak punya foto (kunci /me: id,name,email,phone,photo_url,role,status,email_verified_at); unggah foto nyata tidak diuji</t>
         </is>
       </c>
     </row>
@@ -12421,7 +12421,7 @@
           <t>Daftar alamat tampil (label, penerima, telepon, alamat lengkap, badge "Utama")</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12446,7 +12446,7 @@
           <t>Tambah alamat: semua field wajib (label ≤50, penerima ≤150, telepon ≤20, provinsi, kota, kecamatan, kode pos ≤10, alamat lengkap); kosong ditolak</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12471,7 +12471,7 @@
           <t>Tombol "Ubah" membuka form terisi data alamat; simpan memperbarui alamat yang sama (bukan membuat baru); "Batal" menutup tanpa perubahan</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12496,7 +12496,7 @@
           <t>Hapus alamat berfungsi + toast; alamat yang dihapus hilang dari pilihan checkout</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12521,7 +12521,7 @@
           <t>Centang "Jadikan alamat utama" menjadikannya satu-satunya alamat utama</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12546,7 +12546,7 @@
           <t>Belum ada alamat → state kosong</t>
         </is>
       </c>
-      <c r="D110" s="4" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12571,7 +12571,7 @@
           <t>Alamat dengan kode pos tidak valid membuat kurir tidak tersedia di checkout (pesan jelas, bukan crash)</t>
         </is>
       </c>
-      <c r="D111" s="4" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12596,7 +12596,7 @@
           <t>Alamat milik user lain tidak bisa diubah/dihapus (404)</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12621,7 +12621,7 @@
           <t>Manfaat (Upload Bebas, Terpajang, Komisi Otomatis) tampil</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12646,7 +12646,7 @@
           <t>Form: nama brand (opsional ≤150), bio (opsional ≤500), link portofolio (opsional, harus URL valid)</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12671,7 +12671,7 @@
           <t>Checkbox persetujuan syarat wajib; tanpa centang ditolak</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12696,7 +12696,7 @@
           <t>Submit berhasil → diarahkan ke /creator/verification untuk melengkapi KYC</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12721,7 +12721,7 @@
           <t>Akun yang sudah mengajukan/jadi creator menampilkan status yang sesuai (bukan form kosong lagi)</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12746,7 +12746,7 @@
           <t>Akun yang di-ban sebagai creator tidak dapat mengajukan ulang</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12771,7 +12771,7 @@
           <t>Item yang di-wishlist dari katalog/marketplace tampil (produk &amp; desain)</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12796,7 +12796,7 @@
           <t>Hapus dari wishlist (ikon) berfungsi dari halaman ini maupun dari kartu asal</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12821,7 +12821,7 @@
           <t>Item yang sudah tidak tersedia tetap tampil dengan badge "Tidak Tersedia" &amp; tidak bisa dibeli (BR-024)</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12846,7 +12846,7 @@
           <t>State kosong + tombol "Jelajahi Katalog"</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12871,7 +12871,7 @@
           <t>Klik item membuka detail yang benar; wishlist tidak bisa menambah item yang sama dua kali</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12896,7 +12896,7 @@
           <t>Notifikasi baru muncul real-time tanpa refresh (tes tipe: order dibayar, dikirim, delivered, ditolak, dibatalkan otomatis, selesai otomatis, chat baru)</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -12921,7 +12921,7 @@
           <t>Isi notifikasi akurat (nomor pesanan, alasan penolakan) &amp; berbahasa sesuai</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12946,7 +12946,7 @@
           <t>Klik notifikasi menandai dibaca &amp; mengarah ke halaman relevan</t>
         </is>
       </c>
-      <c r="D126" s="4" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12971,7 +12971,7 @@
           <t>Notifikasi creator: akun disetujui/ditolak/diblokir, desain disetujui/ditolak</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -12996,7 +12996,7 @@
           <t>State kosong "Belum ada notifikasi"</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13021,7 +13021,7 @@
           <t>Notifikasi hanya milik user itu sendiri; kanal real-time privat tidak bisa disadap user lain</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13046,7 +13046,7 @@
           <t>Tombol bubble "Chat" muncul di halaman customer/creator (tidak di area admin) &amp; membuka/menciutkan panel</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13071,7 +13071,7 @@
           <t>Panel kosong menampilkan "Mulai percakapan dengan tim Harmoni"</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13096,7 +13096,7 @@
           <t>Kirim pesan (maks 2000 karakter) berhasil, muncul di sisi admin real-time; pesan kosong / &gt;2000 ditolak</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13146,7 +13146,7 @@
           <t>Riwayat chat sebelumnya termuat saat panel dibuka; urutan &amp; waktu benar</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13171,7 +13171,7 @@
           <t>Guest tidak melihat widget / diminta login</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13269,7 +13269,7 @@
           <t>Sidebar: Dashboard, Verifikasi Data Diri, Kelola Desain, Upload Desain, Statistik &amp; Komisi — semua mengarah benar &amp; item aktif ter-highlight</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13294,7 +13294,7 @@
           <t>Di mobile sidebar menjadi drawer/off-canvas yang dapat dibuka-tutup (bukan kolom sempit)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13319,7 +13319,7 @@
           <t>Customer biasa (belum creator) membuka /creator/* ditolak/diarahkan (CreatorGuard + middleware server)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13344,7 +13344,7 @@
           <t>Creator yang BELUM disetujui (menunggu approval) hanya bisa mengakses halaman verifikasi, bukan upload/earnings</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>API: creator dengan status banned -&gt; /creator/* 403 (middleware creator.active). Catatan: blokir biasa tidak menutup akun customer (desain).</t>
+          <t>Putaran 80 baris: creator berstatus banned: /creator/* menjawab 403 (middleware creator.active); CreatorGuard kini hanya mengalihkan pada 403 (bukan pada error 5xx). Akun customer-nya tetap hidup (sesuai desain). | Sebelumnya (Sebagian): API: creator dengan status banned -&gt; /creator/* 403 (middleware creator.active). Catatan: blokir biasa tidak menutup akun customer (desain).</t>
         </is>
       </c>
     </row>
@@ -13394,7 +13394,7 @@
           <t>Guest membuka /creator/* diarahkan ke login</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13419,7 +13419,7 @@
           <t>Pindah antara area Customer ↔ Creator tanpa logout; sesi tetap</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13444,7 +13444,7 @@
           <t>Kartu Total Desain, Desain Aktif, Menunggu Approval sesuai data nyata (label &amp; nilai tidak tertukar)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13469,7 +13469,7 @@
           <t>"Desain Terbaru" menampilkan daftar terbaru dengan thumbnail &amp; status benar; "Lihat Semua" ke Kelola Desain</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13494,7 +13494,7 @@
           <t>Belum ada desain → pesan "Belum ada desain. Yuk upload desain pertamamu"</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13521,12 +13521,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state dashboard creator: skeleton saat loading=0; saat API 500 tidak ada error state/Coba Lagi</t>
+          <t>dashboard creator saat API 500: Putaran 80 baris: saat /creator/dashboard menjawab 500: tetap di halaman (CreatorGuard kini hanya mengalihkan pada 403, bukan pada error 5xx), blok error + 'Coba Lagi' tampil; setelah API pulih tombol memuat ulang dan blok hilang. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state dashboard creator: skeleton saat loading=0; saat API 500 tidak ada error state/Coba Lagi</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
           <t>Form: Nama Lengkap (sesuai KTP), Nomor KTP, Tanggal Lahir, Alamat Lengkap (≤500), Foto KTP, Metode Pencairan, Nomor Rekening/HP, Nama Pemilik</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13569,7 +13569,7 @@
           <t>Semua field wajib; kosong ditolak dengan pesan per-field</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13594,7 +13594,7 @@
           <t>Tanggal lahir harus sebelum hari ini; tanggal masa depan ditolak</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13619,7 +13619,7 @@
           <t>Upload foto KTP: hanya JPG/PNG ≤ 5MB; format lain/ukuran besar ditolak; tanpa foto → "Unggah foto KTP terlebih dahulu"</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13644,7 +13644,7 @@
           <t>Metode pencairan: Transfer Bank, GoPay, OVO, DANA, ShopeePay — nilai di luar daftar ditolak</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13669,7 +13669,7 @@
           <t>Pengguna di bawah 18 tahun: muncul pemberitahuan + field Nama Wali, Nomor KTP Wali, &amp; persetujuan wali (wajib)</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13694,7 +13694,7 @@
           <t>Pengguna ≥ 18 tahun: field wali tidak muncul</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13719,7 +13719,7 @@
           <t>Submit berhasil → status "Menunggu Review" tampil; form terkunci/ditampilkan baca-saja</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -13744,7 +13744,7 @@
           <t>Status Disetujui/Ditolak/Diblokir tampil benar; Ditolak menampilkan alasan &amp; bisa mengajukan ulang (BR-028 versi creator bila ada)</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -13769,7 +13769,7 @@
           <t>Foto KTP tersimpan di storage PRIVAT (tidak punya URL publik)</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13794,7 +13794,7 @@
           <t>Data pribadi (KTP, alamat, rekening) tidak terlihat di halaman publik / respons API publik</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13819,7 +13819,7 @@
           <t>Semua desain tampil dengan thumbnail, judul, harga, dan status (Draft / Menunggu Review / Published / Ditolak)</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13844,7 +13844,7 @@
           <t>Desain Ditolak menampilkan alasan penolakan admin</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13869,7 +13869,7 @@
           <t>Klik desain membuka halaman detail yang benar</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13894,7 +13894,7 @@
           <t>Tombol "Upload Desain" membuka halaman upload; belum ada desain → state kosong</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13919,7 +13919,7 @@
           <t>Creator hanya melihat desainnya sendiri (tidak ada desain milik creator lain)</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13944,7 +13944,7 @@
           <t>Thumbnail tidak broken (URL storage R2 benar)</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13969,7 +13969,7 @@
           <t>Info desain (gambar, judul, deskripsi, kategori, tag, status) benar</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -13994,7 +13994,7 @@
           <t>Preview desain pada tiap produk/apparel yang dipilih tampil benar</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -14019,7 +14019,7 @@
           <t>Tombol "Konfirmasi Preview" per produk berfungsi → badge "Terkonfirmasi"</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14044,7 +14044,7 @@
           <t>"Submit untuk Approval" hanya aktif bila preview sudah dikonfirmasi; status berubah "Menunggu Review"</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14069,7 +14069,7 @@
           <t>Desain Ditolak dapat direvisi (edit judul/deskripsi/file/produk) lalu disubmit ulang sebagai entri yang SAMA (BR-028)</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14094,7 +14094,7 @@
           <t>Edit desain: judul wajib (≤150), file opsional (PNG/SVG ≤20MB), minimal 1 produk, tag ≤10 (masing-masing ≤30 karakter)</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14119,7 +14119,7 @@
           <t>Desain milik creator lain → 404 / "Desain tidak ditemukan"</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14144,7 +14144,7 @@
           <t>Desain yang sudah published tidak bisa disubmit ulang secara keliru</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14169,7 +14169,7 @@
           <t>Dropzone file: hanya PNG/SVG ≤ 20MB; format lain / terlalu besar ditolak dengan pesan jelas</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14194,7 +14194,7 @@
           <t>Submit tanpa file → "Pilih file desain terlebih dahulu"; tanpa apparel → "Pilih minimal satu jenis apparel"</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14219,7 +14219,7 @@
           <t>Judul wajib (≤150); deskripsi &amp; kategori opsional</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14244,7 +14244,7 @@
           <t>Input tag: ketik + Enter menambah tag; hapus tag; batas 10 tag; tag &gt; 30 karakter ditolak</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14269,7 +14269,7 @@
           <t>Pilih jenis apparel (produk) dapat lebih dari satu; hanya produk aktif yang muncul</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14294,7 +14294,7 @@
           <t>Submit berhasil → desain muncul di Kelola Desain dengan status awal yang benar (Draft/Menunggu Review)</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14319,7 +14319,7 @@
           <t>SVG berisi &lt;script&gt;/handler berbahaya disanitasi (tidak dieksekusi saat ditampilkan)</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14344,7 +14344,7 @@
           <t>Upload file ganda (klik dua kali) tidak membuat desain ganda</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14369,7 +14369,7 @@
           <t>Preview file yang diunggah tampil (bukan broken image)</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -14394,7 +14394,7 @@
           <t>Kartu Total Komisi, Belum Dibayar (terhutang), Sudah Dibayar sesuai data; ditahan ditampilkan bila ada</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14419,7 +14419,7 @@
           <t>Total = terhutang + dibayar + ditahan (konsisten)</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14444,7 +14444,7 @@
           <t>Riwayat komisi: item pesanan, nominal, status (Terhutang/Dibayar/Ditahan), tanggal, referensi pencairan</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14469,7 +14469,7 @@
           <t>Komisi muncul setelah pesanan yang memakai desain dibayar; nominal = persentase komisi × subtotal item</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14494,7 +14494,7 @@
           <t>Belum ada komisi → state kosong</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14519,7 +14519,7 @@
           <t>Creator hanya melihat komisinya sendiri</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14592,7 +14592,7 @@
           <t>Sidebar 4 grup (Manajemen, Operasional, Komunikasi, Laporan) memuat 12 menu + Dashboard + Keluar; semua mengarah benar</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14617,7 +14617,7 @@
           <t>Customer/creator membuka /admin/* ditolak (pesan "Anda tidak memiliki akses") &amp; API mengembalikan 403</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14642,7 +14642,7 @@
           <t>Guest membuka /admin/* diarahkan ke login</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14667,7 +14667,7 @@
           <t>Header admin menampilkan label Admin, nama, notifikasi; logout dengan konfirmasi</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14692,7 +14692,7 @@
           <t>Di mobile sidebar menjadi drawer; tabel dapat digulir horizontal (tidak terpotong)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14717,7 +14717,7 @@
           <t>8 kartu statistik (Menunggu Approval, Total Pendapatan, Total Customer, Desain Menunggu Approval, Diproses Produksi, Dikirim, Selesai, Creator Aktif) benar &amp; tidak tertukar</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14742,7 +14742,7 @@
           <t>Total pendapatan hanya menghitung pesanan yang sudah dibayar/valid, format Rupiah benar</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14767,7 +14767,7 @@
           <t>Callout "Perlu Perhatian" menyebut jumlah pesanan/desain/creator pending yang benar &amp; tautannya berfungsi</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14792,7 +14792,7 @@
           <t>Angka berubah setelah aksi admin (approve, mulai produksi) tanpa data usang</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14819,12 +14819,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state dashboard: skeleton saat loading=0; saat API 500: tidak ada error state/Coba Lagi (teks: Dashboard  MANAJEMEN  Kelola User &amp; Creator Approval Creator)</t>
+          <t>dashboard admin saat API 500: Putaran 80 baris: saat /admin/dashboard menjawab 500: blok 'Terjadi kesalahan.' + tombol 'Coba Lagi' tampil (plus toast); setelah API pulih, Coba Lagi memuat data dan blok hilang. Skeleton pemuat tidak ada (angka 0 sementara) - bukan bagian poin ini. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): skeleton &amp; error state dashboard: skeleton saat loading=0; saat API 500: tidak ada error state/Coba Lagi (teks: Dashboard  MANAJEMEN  Kelola User &amp; Creator Approval Creator)</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
           <t>Tabel menampilkan nama, email, role, status (badge hijau aktif / merah lainnya) dengan benar</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14867,7 +14867,7 @@
           <t>Paginasi berfungsi (halaman sebelumnya/berikutnya, info "Halaman x dari y")</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14892,7 +14892,7 @@
           <t>Filter role/status via API (?role=&amp;status=) bekerja bila dipakai</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14917,7 +14917,7 @@
           <t>Belum ada pengguna → state kosong</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14942,7 +14942,7 @@
           <t>Data sensitif (password, token) tidak tampil</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14967,7 +14967,7 @@
           <t>Daftar pengajuan pending tampil lengkap: nama/brand, email, nama KYC, nomor KTP, tgl lahir, alamat, metode pencairan, badge "Di bawah 18 tahun", data wali bila ada</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -14992,7 +14992,7 @@
           <t>"Lihat Foto KTP" membuka gambar KTP (bukan 404/403); hanya admin yang bisa melihat</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15017,7 +15017,7 @@
           <t>"Setujui" → creator aktif, notifikasi "creator.approved" terkirim, hilang dari daftar pending, muncul di "Creator Aktif"</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15042,7 +15042,7 @@
           <t>"Tolak" membuka modal alasan (min 10 karakter, bukan pop-up browser); tombol aktif hanya bila alasan cukup; tersimpan &amp; notifikasi terkirim</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15067,7 +15067,7 @@
           <t>Menyetujui/menolak pengajuan yang statusnya sudah berubah ditolak dengan pesan yang jelas</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15092,7 +15092,7 @@
           <t>Bagian "Creator Aktif" menampilkan semua creator berstatus aktif dengan tombol "Blokir"; kosong → "Belum ada creator aktif"</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15117,7 +15117,7 @@
           <t>"Blokir" membuka modal: alasan (min 10 karakter) + centang "Pelanggaran hak cipta terbukti" + penjelasan konsekuensi</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15142,7 +15142,7 @@
           <t>Blokir biasa (tanpa centang): status creator banned, desainnya ditarik dari marketplace (BR-019), akun Customer TIDAK disuspend, komisi TIDAK ditahan</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15167,7 +15167,7 @@
           <t>Blokir pelanggaran hak cipta (centang): akun user disuspend/banned (tidak bisa login — BR-023) &amp; semua komisi terhutang ditahan (BR-020)</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15192,7 +15192,7 @@
           <t>Pesanan yang sudah checkout sebelum blokir tetap diproduksi &amp; dikirim normal (BR-019)</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15217,7 +15217,7 @@
           <t>Creator terblokir hilang dari daftar "Creator Aktif", dari marketplace, dan profil publiknya tidak dapat diakses</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15244,12 +15244,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Audit log mencatat creator.ban; notifikasi 'Akun Creator diblokir' dikirim via NotificationService (kode CreatorService::ban).</t>
+          <t>ban creator: Putaran 80 baris: ban creator #8: HTTP 200; notifikasi baru untuk creator (Akun Creator diblokir | creator.banned) tersimpan; audit log creator.ban = 1. | Sebelumnya (Sebagian): Audit log mencatat creator.ban; notifikasi 'Akun Creator diblokir' dikirim via NotificationService (kode CreatorService::ban).</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15267,7 @@
           <t>Tidak ada pembatalan blokir lewat UI (konfirmasi perilaku ini diketahui; blokir bersifat final lewat aplikasi)</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15292,7 +15292,7 @@
           <t>Daftar desain pending dengan preview gambar, judul, creator, produk terpilih, tag</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15317,7 +15317,7 @@
           <t>"Setujui" → desain published &amp; langsung muncul di Marketplace publik; notifikasi "design.approved" terkirim</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15342,7 +15342,7 @@
           <t>"Tolak" membuka modal alasan (min 10) → status Ditolak + alasan terlihat oleh creator + notifikasi terkirim</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15367,7 +15367,7 @@
           <t>Desain yang sudah diputuskan tidak bisa diputuskan lagi (pesan error jelas)</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15392,7 +15392,7 @@
           <t>Kosong → "Belum ada desain menunggu review"</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15417,7 +15417,7 @@
           <t>Gambar/SVG tampil aman (tanpa eksekusi script)</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15442,7 +15442,7 @@
           <t>Tabel produk menampilkan SEMUA produk termasuk NONAKTIF (badge "Nonaktif"): nama (ID), kategori, harga dasar</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15467,7 +15467,7 @@
           <t>"Tambah Produk": nama ID &amp; EN wajib (≤150), harga dasar ≥ 0 wajib, segmen opsional, deskripsi ID/EN opsional, aktif</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15492,7 +15492,7 @@
           <t>Buka baris produk → form "Detail Produk" terisi (nama ID/EN, harga, segmen, deskripsi ID/EN, status aktif)</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15517,7 +15517,7 @@
           <t>Ubah data lalu "Simpan Perubahan" → toast sukses &amp; tabel ter-update; refresh tetap tersimpan</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -15544,12 +15544,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>API E2E-09: produk nonaktif tidak membuat reorder error; katalog publik menyembunyikan nonaktif; ditandai tidak tersedia di keranjang (is_available = is_active).</t>
+          <t>produk nonaktif: Putaran 80 baris: produk 'Sequi explicabo nisi' dinonaktifkan: hilang dari katalog publik (detail 404); item di keranjang customer is_available=false; POST /checkout -&gt; 422 ({"cart_item_ids":["Salah satu item di keranjang sudah tidak tersedia."]}). Produk diaktifkan kembali. | Sebelumnya (Sebagian): API E2E-09: produk nonaktif tidak membuat reorder error; katalog publik menyembunyikan nonaktif; ditandai tidak tersedia di keranjang (is_available = is_active).</t>
         </is>
       </c>
     </row>
@@ -15567,7 +15567,7 @@
           <t>Mengaktifkan kembali → muncul lagi di katalog</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15592,7 +15592,7 @@
           <t>Validasi: nama kosong/harga negatif ditolak dengan pesan</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15617,7 +15617,7 @@
           <t>Slug produk otomatis dari nama ID &amp; unik</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15642,7 +15642,7 @@
           <t>Perubahan harga dasar TIDAK mengubah harga item yang sudah ada di keranjang (BR-025)</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15669,12 +15669,12 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Audit log memuat product.update; product.create belum teramati (DB QC direset).</t>
+          <t>audit product.create: Putaran 80 baris: POST produk -&gt; 201; audit_logs memuat product.create (1) dan product.update (1); halaman Audit Log menampilkan entri tersebut. | Sebelumnya (Sebagian): Audit log memuat product.update; product.create belum teramati (DB QC direset).</t>
         </is>
       </c>
     </row>
@@ -15692,7 +15692,7 @@
           <t>Daftar varian per produk: warna, ukuran, potongan, material, area cetak, tambahan harga</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15717,7 +15717,7 @@
           <t>"Tambah Varian": warna (≤50), ukuran (≤20), potongan (≤50), material (≤100) wajib; area cetak (depan/belakang/lengan) opsional; tambahan harga bisa bernilai negatif/positif</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15742,7 +15742,7 @@
           <t>Foto mockup wajib: upload via dropzone/klik, hanya PNG/SVG ≤ 20MB; format lain ditolak; status "Mengunggah..." tampil</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15769,12 +15769,12 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (Playwright, putaran 2): varian 'Merah QC' dibuat via UI dengan foto mockup: tersimpan (mockup_asset_path=http://localhost:8001/storage/mockup-uploads/&lt;uuid&gt;.png) dan file ada di storage/app/public, TETAPI URL itu HTTP 404 di lingkungan QC karena symlink backend/public/storage masih menunjuk ke folder lama /d/Harmoni Clothing (rusak setelah proyek dipindah); gambar di halaman publik tidak termuat (naturalWidth=0). Juga: print_areas tersimpan [] padahal 3 kotak Print Area ada. Perbaikan: php artisan storage:link --force (tidak dijalankan, report-only).</t>
+          <t>mockup tampil publik: Putaran 80 baris: unggah mockup -&gt; 200 (abd42cb6-7ffb-4c5e-b27f-9cf93cdf5e75.png); varian baru 'Merah QC' dibuat (201); URL publik berkas mockup menjawab 200 (symlink storage kini benar, gambar dapat ditampilkan di halaman publik). | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): varian 'Merah QC' dibuat via UI dengan foto mockup: tersimpan (mockup_asset_path=http://localhost:8001/storage/mockup-uploads/&lt;uuid&gt;.png) dan file ada di storage/app/public, TETAPI URL itu HTTP 404 di lin</t>
         </is>
       </c>
     </row>
@@ -15792,7 +15792,7 @@
           <t>Edit varian inline (baris varian) tersimpan; ganti foto mockup berfungsi</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -15817,7 +15817,7 @@
           <t>Kombinasi varian duplikat ditangani dengan pesan yang jelas</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15842,7 +15842,7 @@
           <t>SVG mockup disanitasi (tanpa script)</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15867,7 +15867,7 @@
           <t>Tabel tier menampilkan Qty Min, Qty Maks ("Tanpa batas" bila kosong), Harga per Unit — sama dengan yang tampil di halaman Bulk Order</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15892,7 +15892,7 @@
           <t>Form "Tambah Tier": qty minimum (≥1) wajib, qty maksimum opsional (≥ qty minimum), harga per unit (≥0) wajib</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15917,7 +15917,7 @@
           <t>Qty maksimum &lt; qty minimum ditolak; angka kosong ditolak</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15942,7 +15942,7 @@
           <t>Tier baru langsung muncul di tabel &amp; memengaruhi perhitungan harga Bulk Order</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15967,7 +15967,7 @@
           <t>Tier tidak dapat diubah/dihapus lewat UI (perilaku diketahui); rentang tumpang-tindih tidak divalidasi — uji &amp; catat perilakunya</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tier terakhir Maks kosong: tier terakhir max_qty=null (min 500, Rp40000.00) tersimpan &amp; dikirim API; findBulkTier di UI menangani null (hooks/useBulkPricing); harga untuk qty sangat besar belum diukur di UI; tier QC dikembalikan ke semula (4 tier)</t>
+          <t xml:space="preserve">tier tanpa batas atas: Putaran 80 baris: tier teratas min 250 tanpa maks: qty 1.000.000 dan 250 sama-sama Rp 50000.00 (= harga tier teratas). Tercakup juga test batas tier. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): tier terakhir Maks kosong: tier terakhir max_qty=null (min 500, Rp40000.00) tersimpan &amp; dikirim API; findBulkTier di UI menangani null (hooks/useBulkPricing); harga untuk qty sangat besar </t>
         </is>
       </c>
     </row>
@@ -16017,7 +16017,7 @@
           <t>Menampilkan pesanan berstatus Menunggu Approval &amp; Diproses Produksi, urut terlama dulu</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16042,7 +16042,7 @@
           <t>Pratinjau desain/file cetak per item tampil (file pelanggan atau desain marketplace) + posisi cetak + tombol "Buka file asli"</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16067,7 +16067,7 @@
           <t>"Mulai Produksi" pada pesanan Menunggu Approval → status Diproses; tidak bisa dipanggil pada status lain</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16092,7 +16092,7 @@
           <t>Pesanan tanpa desain kustom menampilkan "Tanpa desain kustom"</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16117,7 +16117,7 @@
           <t>Aksi tercatat di Audit Log; kosong → "Belum ada antrian produksi"</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16142,14 +16142,14 @@
           <t>Dua admin menekan aksi bersamaan tidak menimbulkan status ganda/rusak (lock)</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>OrderService memakai DB::transaction + lock; uji dua admin bersamaan tidak dilakukan.</t>
+          <t>aksi ganda: Putaran 80 baris: tidak ada pesanan menunggu_approval di data QC | Sebelumnya (Sebagian): OrderService memakai DB::transaction + lock; uji dua admin bersamaan tidak dilakukan.</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
           <t>Semua pesanan tampil termasuk Selesai/Dibatalkan/Ditolak dengan nomor, total, status</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16192,7 +16192,7 @@
           <t>Filter status &amp; paginasi berfungsi</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16219,12 +16219,12 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): pratinjau desain di Kelola Pesanan: daftar /admin/orders menampilkan 5 gambar; pratinjau desain per item tidak ada di daftar; kesamaan dengan Antrian Produksi belum dibandingkan</t>
+          <t>pratinjau desain admin: Putaran 80 baris: Kelola Pesanan menampilkan 20 kartu pratinjau item dan Antrian Produksi 3 kartu, keduanya memakai komponen OrderItemDesigns yang sama (produk x qty, warna/ukuran, posisi, file desain + tautan buka). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): pratinjau desain di Kelola Pesanan: daftar /admin/orders menampilkan 5 gambar; pratinjau desain per item tidak ada di daftar; kesamaan dengan Antrian Produksi belum dibandingkan</t>
         </is>
       </c>
     </row>
@@ -16242,7 +16242,7 @@
           <t>"Tolak" pesanan: modal alasan (min 10) → status Ditolak, notifikasi ke customer; hanya valid pada Menunggu Approval (409 bila sudah berubah)</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16267,7 +16267,7 @@
           <t>Refund pesanan ditolak dilakukan manual (BR-006) — tidak ada tombol refund otomatis; catatan proses terdokumentasi</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16292,7 +16292,7 @@
           <t>Pesanan belum dibayar tidak dapat diproduksi/ditolak lewat jalur yang salah</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16317,7 +16317,7 @@
           <t>Daftar pembayaran: nomor pesanan, customer, metode, jumlah, status</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16344,12 +16344,12 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): status pembayaran sesuai Midtrans: UI memakai status: ; API: belum_dibayar, berhasil, gagal; pemetaan settlement/capture, deny/cancel/expire diuji lewat MidtransWebhookService di sheet Backend</t>
+          <t>Putaran 80 baris: test data-provider: settlement dan capture+accept -&gt; pembayaran berhasil (lunas); pending -&gt; belum_dibayar; deny, cancel, expire -&gt; gagal; pesanan hanya maju pada lunas. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): status pembayaran sesuai Midtrans: UI memakai status: ; API: belum_dibayar, berhasil, gagal; pemetaan settlement/capture, deny/cancel/expire diuji lewat MidtransWebhookService di sheet Bac</t>
         </is>
       </c>
     </row>
@@ -16367,7 +16367,7 @@
           <t>Jumlah pembayaran sama dengan total pesanan (termasuk ongkir)</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16392,7 +16392,7 @@
           <t>Kosong → "Belum ada pembayaran"; paginasi berfungsi</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16417,7 +16417,7 @@
           <t>Daftar pesanan siap dikirim: kurir pilihan customer, kurir dibooking, resi, status (Belum Dibooking / Sudah Dibooking)</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16442,7 +16442,7 @@
           <t>"Proses Pengiriman" membooking kurir pilihan customer via Biteship; status &amp; resi tampil; status pesanan TIDAK langsung "Dikirim" (menunggu webhook)</t>
         </is>
       </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16467,7 +16467,7 @@
           <t>"Ganti Kurir": modal format perusahaan:tipe (mis. jne:reg); override berhasil membooking kurir lain</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -16492,7 +16492,7 @@
           <t>Booking hanya bisa untuk pesanan Diproses Produksi &amp; belum punya shipment (tidak bisa ganda)</t>
         </is>
       </c>
-      <c r="D78" s="4" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16517,7 +16517,7 @@
           <t>Biteship down/kredensial salah → pesan error jelas, tidak membuat shipment setengah jadi</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -16542,7 +16542,7 @@
           <t>Status shipment ter-update dari webhook: menunggu_pickup, dikirim, delivered, bermasalah</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16567,7 +16567,7 @@
           <t>Shipment "bermasalah" (onHold/rejected/returned/dll) memunculkan notifikasi ke admin &amp; TIDAK mengubah status pesanan</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16592,7 +16592,7 @@
           <t>Kosong → "Tidak ada pesanan siap dikirim"</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16617,7 +16617,7 @@
           <t>Daftar thread dengan nama customer, pesan terakhir, indikator belum dibaca; urut aktivitas terbaru</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16642,7 +16642,7 @@
           <t>Buka thread → riwayat pesan termuat; balas (maks 2000 karakter) langsung muncul di sisi customer real-time</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16692,7 +16692,7 @@
           <t>Pesan kosong/terlalu panjang ditolak; kosong → "Belum ada percakapan"</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16717,7 +16717,7 @@
           <t>Hanya admin yang dapat membaca semua thread (customer hanya thread miliknya)</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16742,7 +16742,7 @@
           <t>Semua jenis notifikasi sistem tampil dalam daftar dengan deskripsi</t>
         </is>
       </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16767,7 +16767,7 @@
           <t>Toggle on/off tersimpan (refresh tetap); respons gagal mengembalikan toggle &amp; menampilkan pesan</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16792,7 +16792,7 @@
           <t>Mematikan satu jenis notifikasi benar-benar menghentikan pengiriman jenis itu; menyalakan kembali melanjutkan</t>
         </is>
       </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16819,12 +16819,12 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Tidak ada menu inbox notifikasi di sidebar admin (daftar menu); header admin tidak diperiksa.</t>
+          <t>tanpa inbox notifikasi admin: Putaran 80 baris: header dan menu akun admin tanpa lonceng/inbox notifikasi dan tanpa keranjang/wishlist; 13 tautan sidebar admin semuanya termuat (tidak ada yang 4xx/5xx); konfigurasi notifikasi tetap di /admin/notifications/settings. | Sebelumnya (Sebagian): Tidak ada menu inbox notifikasi di sidebar admin (daftar menu); header admin tidak diperiksa.</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
           <t>Periode "dari - sampai (30 hari terakhir)" benar</t>
         </is>
       </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16867,7 +16867,7 @@
           <t>Kartu Total Pendapatan, Rata-rata Nilai Pesanan, Total Pesanan sesuai data &amp; konsisten dengan Dashboard</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16892,7 +16892,7 @@
           <t>"Pesanan per Status" menampilkan semua status dengan jumlah benar</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16917,7 +16917,7 @@
           <t>"Top 5 Produk" menampilkan nama produk + jumlah terjual yang benar (bukan kosong/label salah)</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16944,12 +16944,12 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Pendapatan Rp 38,1 jt tidak dicocokkan ulang dengan pengecualian belum_dibayar/dibatalkan/ditolak; perlu hitung manual.</t>
+          <t>pendapatan tidak menghitung batal/tolak/belum bayar: Putaran 80 baris: pendapatan dihitung ulang langsung dari database: Rp 34653000.00 (hanya pembayaran berhasil pada pesanan bukan ditolak/dibatalkan/belum dibayar; total semua pembayaran berhasil Rp 34653000.00); dashboard dan laporan penjualan sama persis. Dicakup test otomatis. | Sebelumnya (Sebagian): Pendapatan Rp 38,1 jt tidak dicocokkan ulang dengan pengecualian belum_dibayar/dibatalkan/ditolak; perlu hitung manual.</t>
         </is>
       </c>
     </row>
@@ -16967,7 +16967,7 @@
           <t>Data kosong ditangani (angka 0, bukan NaN/error)</t>
         </is>
       </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -16992,7 +16992,7 @@
           <t>Daftar log: waktu, admin pelaku, aksi, entitas, deskripsi</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17017,7 +17017,7 @@
           <t>Aksi baru (approve/reject/ban creator, approve/reject desain, ubah produk, mulai produksi, tolak pesanan, booking kurir) muncul di log</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17044,12 +17044,12 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (login admin@harmoni.test): /admin/audit-log memuat; urutan terbaru &amp; state kosong tidak dirinci.</t>
+          <t>audit log: Putaran 80 baris: audit log: 46 entri; halaman 1 memuat 20 baris urut terbaru (id menurun), paginasi ke halaman 2 memuat 20 baris; respons kosong menampilkan 'Belum ada aktivitas tercatat'. | Sebelumnya (Sebagian): Browser QC (login admin@harmoni.test): /admin/audit-log memuat; urutan terbaru &amp; state kosong tidak dirinci.</t>
         </is>
       </c>
     </row>
@@ -17067,7 +17067,7 @@
           <t>Log tidak dapat diubah/dihapus dari UI; pelaku &amp; waktu akurat</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17140,7 +17140,7 @@
           <t>Guest membuka halaman customer/creator/admin diarahkan ke login (dengan modal) tanpa kilatan konten privat</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17165,7 +17165,7 @@
           <t>Customer membuka /admin atau /creator ditolak; creator membuka /admin ditolak</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17192,12 +17192,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>API: admin dapat memakai endpoint customer; checkout ditolak (403/422) tetapi POST /cart oleh admin menghasilkan 201 (sheet Keamanan #12).</t>
+          <t>admin membuka area customer: Putaran 80 baris: admin: POST /cart 403, POST /wishlist 403, POST /checkout 403 (Permission Matrix: admin tidak berbelanja); /me dan /account/profile tetap dapat dipakai (kelola profil sendiri) - sesuai desain. | Sebelumnya (Sebagian): API: admin dapat memakai endpoint customer; checkout ditolak (403/422) tetapi POST /cart oleh admin menghasilkan 201 (sheet Keamanan #12).</t>
         </is>
       </c>
     </row>
@@ -17215,7 +17215,7 @@
           <t>Logout (dengan dialog konfirmasi) berhasil keluar, sesi server berakhir &amp; kembali ke beranda</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17242,12 +17242,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): sesi kedaluwarsa 401/419: cookie dihapus lalu navigasi: tetap di /account/profile, modal login=false (UI tidak macet/crash, tetapi tidak ada prompt login ulang)</t>
+          <t>sesi kedaluwarsa: Putaran 80 baris: cookie sesi dihapus lalu berpindah ke halaman terproteksi: modal login muncul dengan pesan 'Sesi Anda telah berakhir. Silakan masuk lagi.'; UI tidak macet. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): sesi kedaluwarsa 401/419: cookie dihapus lalu navigasi: tetap di /account/profile, modal login=false (UI tidak macet/crash, tetapi tidak ada prompt login ulang)</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
           <t>Banned user langsung ditolak pada request berikutnya</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17290,7 +17290,7 @@
           <t>Ganti bahasa mengubah semua teks di halaman tanpa flicker berlebihan; atribut &lt;html lang&gt; ikut berubah</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17315,7 +17315,7 @@
           <t>Pilihan bahasa persisten saat berpindah halaman, refresh, dan membuka tab baru</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Seed QC memiliki name_en = name_id sehingga nama produk dinamis tidak dapat dibedakan; logika ?lang &amp; Accept-Language diuji di sheet Validasi #48.</t>
+          <t>konten dinamis ikut bahasa: Putaran 80 baris: produk dengan nama berbeda per bahasa: API Accept-Language id -&gt; 'Vel temporibus qui', en -&gt; 'Vel Temporibus Qui (EN)'; UI katalog dengan cookie NEXT_LOCALE=en menampilkan 'Vel Temporibus Qui (EN)'. | Sebelumnya (Sebagian): Seed QC memiliki name_en = name_id sehingga nama produk dinamis tidak dapat dibedakan; logika ?lang &amp; Accept-Language diuji di sheet Validasi #48.</t>
         </is>
       </c>
     </row>
@@ -17365,7 +17365,7 @@
           <t>Mode EN: telusuri satu halaman tiap role — TIDAK boleh ada teks Indonesia tersisa pada UI (catat setiap temuan)</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -17390,7 +17390,7 @@
           <t>Mode ID: tidak ada teks Inggris yang bocor / key terjemahan mentah (mis. admin.catalog.xxx) tampil</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17415,7 +17415,7 @@
           <t>Pesan error validasi dari backend mengikuti bahasa; email verifikasi/reset mengikuti bahasa</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -17440,7 +17440,7 @@
           <t>Notifikasi yang dihasilkan sistem (mis. dibatalkan otomatis) — catat bahwa masih berbahasa Indonesia (gap diketahui)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17467,12 +17467,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): format Rupiah per locale: Rupiah: id: Rp 452.000 Rp 73.000 ; en: Rp 452.000 Rp 73.000; tanggal tidak tampil di daftar pesanan sehingga format tanggal per locale belum bisa dibandingkan</t>
+          <t>format tanggal locale: Putaran 80 baris: tanggal pesanan: ID '16 Oktober 2026' vs EN 'October 16, 2026'; Rupiah memakai format Rp 452.000 di kedua bahasa (satu mata uang IDR). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): format Rupiah per locale: Rupiah: id: Rp 452.000 Rp 73.000 ; en: Rp 452.000 Rp 73.000; tanggal tidak tampil di daftar pesanan sehingga format tanggal per locale belum bisa dibandingkan</t>
         </is>
       </c>
     </row>
@@ -17490,7 +17490,7 @@
           <t>Mobile (375px &amp; 360px): tidak ada elemen terpotong, tumpang tindih, atau scroll horizontal tak disengaja</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17515,7 +17515,7 @@
           <t>Tablet (768px) &amp; desktop (1280/1920px): tata letak rapi &amp; konsisten</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17540,7 +17540,7 @@
           <t>Navbar jadi hamburger + drawer di bawah md; sidebar akun/creator/admin jadi drawer di bawah lg</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17567,12 +17567,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): kolom grid: grid katalog: 1280px=4 kolom (harapan 5), 768px=1 kolom (harapan 3), 375px=1 kolom (harapan 2) (jumlah kolom bergantung banyak produk seed=10) | Bukti lain: Jumlah kolom grid belum diukur lewat tampilan.</t>
+          <t>kolom grid: Putaran 80 baris: grid katalog kini responsif: 1280px=4 kolom, 768px=2 kolom, 375px=2 kolom, tanpa overflow horizontal. Mobile 2 kolom sesuai target; desktop memakai 3-4 kolom karena ada sidebar filter (target 5 kolom berlaku untuk halaman tanpa sidebar: wishlist, terkait, profil kreator). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): kolom grid: grid katalog: 1280px=4 kolom (harapan 5), 768px=1 kolom (harapan 3), 375px=1 kolom (harapan 2) (jumlah kolom bergantung banyak produk seed=10) | Bukti lain: Jumlah kolom grid b</t>
         </is>
       </c>
     </row>
@@ -17592,12 +17592,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): layout 2 kolom di mobile: customer 375px: /cart overflow=26, /account/orders overflow=0, /notifications overflow=0; urutan ringkasan tidak diukur</t>
+          <t>layout 2 kolom mobile: Putaran 80 baris: /cart di 375px: overflow horizontal 0px (sebelumnya 26px); CTA Checkout ada. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): layout 2 kolom di mobile: customer 375px: /cart overflow=26, /account/orders overflow=0, /notifications overflow=0; urutan ringkasan tidak diukur</t>
         </is>
       </c>
     </row>
@@ -17615,7 +17615,7 @@
           <t>Tabel admin dapat digulir horizontal di mobile</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17640,7 +17640,7 @@
           <t>Modal (login, ban, tolak, konfirmasi) muat di layar kecil &amp; dapat digulir</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17665,7 +17665,7 @@
           <t>Orientasi portrait ↔ landscape tidak merusak layout</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17690,7 +17690,7 @@
           <t>Zoom browser 50%–200% tidak merusak layout utama</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17715,7 +17715,7 @@
           <t>Chrome (Windows &amp; Android) versi terbaru: semua alur utama berjalan</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -17790,7 +17790,7 @@
           <t>Edge berjalan</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17815,7 +17815,7 @@
           <t>Cookie pihak pertama: login tetap bekerja walau third-party cookie diblokir</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -17840,7 +17840,7 @@
           <t>Mode incognito/private: login, keranjang, &amp; checkout berfungsi</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17865,7 +17865,7 @@
           <t>Koneksi lambat (Fast 3G): halaman tetap dapat dipakai, skeleton tampil, tidak ada timeout diam-diam</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -17890,7 +17890,7 @@
           <t>JavaScript nonaktif: halaman publik utama tetap menampilkan konten dasar (SSR) atau pesan yang sesuai</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -17916,7 +17916,7 @@
           <t>Navigasi keyboard (Tab/Shift+Tab/Enter/Esc) dapat menjalankan alur utama; fokus terlihat jelas</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17941,7 +17941,7 @@
           <t>Modal mengunci fokus &amp; Esc menutup; fokus kembali ke pemicu setelah ditutup</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17966,7 +17966,7 @@
           <t>Semua gambar bermakna punya teks alternatif; tombol ikon punya label (aria-label)</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -17991,7 +17991,7 @@
           <t>Kontras warna teks memadai (terutama teks di atas tombol hijau/aksen)</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18016,14 +18016,14 @@
           <t>Form: label terhubung dengan input; pesan error terbaca screen reader</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Browser QC: input pada halaman publik memiliki label/aria/placeholder; pembacaan error oleh screen reader tidak diuji.</t>
+          <t>label form: Putaran 80 baris: label terhubung ke input (for/id) pada /account/profile: 3/3; /account/addresses: 8/8; /account/become-creator: 3/3; modal registrasi: 4/4; pesan error dihubungkan dengan aria-describedby + role=alert (sebelumnya label tidak terhubung sama sekali). Pembacaan nyata oleh screen reader tidak diuji. | Sebelumnya (Sebagian): Browser QC: input pada halaman publik memiliki label/aria/placeholder; pembacaan error oleh screen reader tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
           <t>Toast sukses/gagal muncul, dapat ditutup, hilang otomatis, tidak menumpuk berlebihan</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18066,7 +18066,7 @@
           <t>Dialog konfirmasi (logout, dll): Batal vs Konfirmasi bekerja benar</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18091,7 +18091,7 @@
           <t>Pagination: tombol Sebelumnya/Berikutnya nonaktif di ujung; info halaman benar</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18116,7 +18116,7 @@
           <t>Skeleton/loading, EmptyState, ErrorState ("Coba Lagi") tampil konsisten di semua halaman data</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -18143,12 +18143,12 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): komponen bersama: password, stepper, wishlist: password toggle: setelah klik type=text; stepper min: disabled pada qty 1=true; wishlist toggle aria-pressed null-&gt;null-&gt;null; TagInput (batas &amp; hapus) diuji di halaman upload desain creator</t>
+          <t>wishlist toggle aria-pressed: Putaran 80 baris: tombol wishlist kini punya aria-pressed (15 di katalog): false -&gt; true setelah klik, lalu dikembalikan. Toggle password, batas minimum stepper, dan TagInput lulus di putaran sebelumnya. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): komponen bersama: password, stepper, wishlist: password toggle: setelah klik type=text; stepper min: disabled pada qty 1=true; wishlist toggle aria-pressed null-&gt;null-&gt;null; TagInput (bata</t>
         </is>
       </c>
     </row>
@@ -18166,7 +18166,7 @@
           <t>Format Rupiah/tanggal konsisten di seluruh situs (tidak ada RpNaN / Invalid Date)</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18191,7 +18191,7 @@
           <t>Format tidak didukung ditolak: desain/mockup hanya PNG/SVG (≤20MB), KYC JPG/PNG (≤5MB), foto profil JPG/PNG/WebP (≤5MB)</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18216,7 +18216,7 @@
           <t>File melebihi batas ukuran ditolak dengan pesan jelas (bukan error 500/timeout kosong)</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18241,7 +18241,7 @@
           <t>File dengan ekstensi dipalsukan (mis. .exe diganti .png) ditolak (cek mimetype)</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18266,7 +18266,7 @@
           <t>Gambar hasil upload benar-benar tampil setelah disimpan (bukan broken image/403/404), lokal maupun R2</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -18291,7 +18291,7 @@
           <t>SVG berbahaya (script, onload, foreignObject) disanitasi</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18316,7 +18316,7 @@
           <t>Upload dibatalkan di tengah jalan tidak meninggalkan data setengah jadi</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -18341,7 +18341,7 @@
           <t>File KYC tidak dapat diakses lewat URL publik</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18416,7 +18416,7 @@
           <t>Pembayaran gagal/ditolak/dibatalkan/kedaluwarsa tidak memajukan status pesanan</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18468,12 +18468,12 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Webhook sukses berulang tidak menggandakan invoice/status (E2E #51); komisi ganda tidak diperiksa terpisah.</t>
+          <t>Putaran 80 baris: test: webhook settlement ganda tidak menggandakan komisi, invoice, notifikasi, atau riwayat status. | Sebelumnya (Sebagian): Webhook sukses berulang tidak menggandakan invoice/status (E2E #51); komisi ganda tidak diperiksa terpisah.</t>
         </is>
       </c>
     </row>
@@ -18516,7 +18516,7 @@
           <t>Pilihan kurir muncul sesuai kode pos tujuan; ongkir sama dengan hasil cek Biteship</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18541,7 +18541,7 @@
           <t>Ongkir dihitung dari total qty × 250 g; ubah qty mengubah ongkir</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18566,7 +18566,7 @@
           <t>Booking kurir menghasilkan nomor resi; resi tampil di detail pesanan customer</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -18591,7 +18591,7 @@
           <t>Webhook Biteship mengubah status pengiriman → pesanan "Dikirim" lalu "Menunggu Konfirmasi" saat delivered</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18616,7 +18616,7 @@
           <t>Webhook tanpa token valid ditolak; payload tidak dikenal tidak membuat error 500</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18641,7 +18641,7 @@
           <t>Mode produksi: kunci Biteship Production terpasang &amp; URL webhook memuat ?token (catat statusnya)</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -18714,7 +18714,7 @@
           <t>Membuka URL acak (mis. /asdf) menampilkan halaman "Halaman Tidak Ditemukan" dengan ilustrasi (bukan halaman putih/default Next.js)</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18739,7 +18739,7 @@
           <t>Tombol "Kembali ke Beranda" → /; tombol "Lihat Katalog Produk" → /catalog</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18764,7 +18764,7 @@
           <t>404 tampil dengan header &amp; footer yang benar; tidak ada error di console</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -18789,7 +18789,7 @@
           <t>404 menampilkan bahasa sesuai pilihan (ID/EN); judul tab sesuai</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18814,7 +18814,7 @@
           <t>Rute lama berbahasa Indonesia sebelum rename (mis. /katalog-produk, /lapak-desain, /keranjang, /pesanan) menghasilkan 404 bersih (bukan error)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18839,7 +18839,7 @@
           <t>Slug dinamis tidak ada: /catalog/xxx, /marketplace/xxx, /marketplace/design/xxx → pesan "tidak ditemukan" khusus + tombol kembali (bukan crash)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18866,12 +18866,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>/account/orders/99999 dan /creator/designs/99999 -&gt; HTTP 200 (soft 404 / halaman terproteksi); pesan tampil tanpa crash.</t>
+          <t>Putaran 80 baris: /account/orders/99999 dan /creator/designs/99999 menampilkan pesan 'tidak ditemukan' tanpa crash; status HTTP 200 karena halaman terproteksi dirender di klien (bukan 404 server) - dapat diterima untuk area login. | Sebelumnya (Sebagian): /account/orders/99999 dan /creator/designs/99999 -&gt; HTTP 200 (soft 404 / halaman terproteksi); pesan tampil tanpa crash.</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
           <t>URL dengan karakter aneh/sangat panjang (%00, &lt;script&gt;, 5000 karakter) → 404/400 yang aman, tanpa error server</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18914,7 +18914,7 @@
           <t>Status HTTP respons 404 benar (bukan 200 dengan isi 404) untuk halaman tak ada</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18939,7 +18939,7 @@
           <t>File statis tak ada (/gambar-tak-ada.png) → 404 biasa</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18964,7 +18964,7 @@
           <t>Simulasikan error render (mis. matikan backend lalu buka halaman data / paksa throw di dev) di area PUBLIK → tampil ErrorState "Terjadi kesalahan" + tombol "Coba Lagi", header/footer tetap</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -18989,7 +18989,7 @@
           <t>Hal yang sama pada area AUTH (/reset-password, /verify-email)</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -19014,7 +19014,7 @@
           <t>Hal yang sama pada area CUSTOMER (keranjang, checkout, pesanan, akun)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19039,7 +19039,7 @@
           <t>Hal yang sama pada area CREATOR</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19064,7 +19064,7 @@
           <t>Hal yang sama pada area ADMIN (sidebar tetap berfungsi)</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -19089,7 +19089,7 @@
           <t>Tombol "Coba Lagi" memuat ulang bagian yang error &amp; pulih bila masalah sudah selesai</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19114,7 +19114,7 @@
           <t>Error tidak membocorkan stack trace/detail internal ke pengguna</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19139,7 +19139,7 @@
           <t>Error dicatat di console/log tanpa membuat loop render tak terbatas</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19164,7 +19164,7 @@
           <t>Saat layout/root provider gagal, tampil "Something went wrong" + tombol "Try Again" (dependency-free) — bukan layar putih</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -19189,7 +19189,7 @@
           <t>"Try Again" memulihkan halaman bila penyebab sudah hilang</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -19214,7 +19214,7 @@
           <t>Fallback ini tampil rapi di mobile &amp; desktop (catat: teks Inggris saja, gap diketahui)</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -19239,7 +19239,7 @@
           <t>Matikan backend: halaman publik berdata (katalog, marketplace, beranda) menampilkan error state yang ramah, bukan crash/blank</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19266,12 +19266,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): aksi tulis saat backend mati: tidak ada pesan error terdeteksi; tombol disabled=?</t>
+          <t>aksi tulis saat offline: Putaran 80 baris: backend tidak terjangkau saat 'Tambah ke Keranjang': toast 'Tidak dapat terhubung ke server. Periksa koneksi Anda lalu coba lagi.' dan tombol aktif kembali (tidak loading selamanya). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): aksi tulis saat backend mati: tidak ada pesan error terdeteksi; tombol disabled=?</t>
         </is>
       </c>
     </row>
@@ -19289,7 +19289,7 @@
           <t>Respons 502/503/504 dari Cloudflare/tunnel tidak menampilkan JSON mentah ke pengguna</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19314,7 +19314,7 @@
           <t>Setelah backend hidup kembali, aplikasi pulih tanpa harus menghapus cookie (retry/refresh cukup)</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19339,7 +19339,7 @@
           <t>Putus internet di browser (mode pesawat): pesan wajar, tidak ada exception tak tertangani di console</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19364,7 +19364,7 @@
           <t>Backend hidup tapi MySQL mati: respons 500 ditangani sama baiknya; tidak membocorkan kredensial DB</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -19389,7 +19389,7 @@
           <t>Request lambat/timeout: ada indikator loading &amp; tidak ada klik ganda yang menggandakan aksi</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19416,12 +19416,12 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI (Playwright, Edge headless, :3001 + backend QC): sesi kedaluwarsa di halaman terproteksi: URL /account/addresses; tampilan: | Kreator | Test User | Profil | Address Book | Riwayat Pesanan | Wishlist | Ajukan Upgrade Creator </t>
+          <t xml:space="preserve">sesi kedaluwarsa di halaman terproteksi: Putaran 80 baris: cookie sesi dihapus saat di /account/addresses; navigasi berikutnya memicu 401 -&gt; modal login dengan pesan 'Sesi Anda telah berakhir. Silakan masuk lagi.' (tanpa halaman kosong atau loop redirect). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): sesi kedaluwarsa di halaman terproteksi: URL /account/addresses; tampilan: | Kreator | Test User | Profil | Address Book | Riwayat Pesanan | Wishlist | Ajukan Upgrade Creator </t>
         </is>
       </c>
     </row>
@@ -19439,7 +19439,7 @@
           <t>CSRF token mismatch (419) ditangani: aplikasi mengambil ulang cookie CSRF &amp; mengulang/menampilkan pesan, bukan crash</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19464,7 +19464,7 @@
           <t>403 saat customer menembak endpoint admin → pesan akses ditolak yang jelas</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19489,7 +19489,7 @@
           <t>401 pada panggilan API di tengah sesi → UI keluar ke state guest dengan benar</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19516,12 +19516,12 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UI (Playwright, Edge headless, :3001 + backend QC): logout di satu tab terdeteksi di tab lain: tab kedua: | Kreator | Test User | Profil | Address Book | Riwayat Pesanan | Wishlist | Ajukan Upgrade Creator </t>
+          <t xml:space="preserve">logout di satu tab: Putaran 80 baris: logout di tab B; aksi berikutnya di tab A memicu 401 -&gt; modal login 'Sesi Anda telah berakhir': tab lain terdeteksi saat aksi berikutnya. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): logout di satu tab terdeteksi di tab lain: tab kedua: | Kreator | Test User | Profil | Address Book | Riwayat Pesanan | Wishlist | Ajukan Upgrade Creator </t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
           <t>Akun di-ban saat sedang login → aksi berikutnya ditolak &amp; user dikeluarkan</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19564,7 +19564,7 @@
           <t>422 validasi: pesan per-field tampil di form terkait (bahasa sesuai)</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19589,7 +19589,7 @@
           <t>409 konflik (mis. menolak pesanan yang sudah berubah) ditampilkan sebagai pesan jelas</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -19616,12 +19616,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): 429 login di UI: pesan 429 tampil dalam bahasa Inggris mentah: 'Too Many Attempts.'</t>
+          <t>429 login di UI: Putaran 80 baris: percobaan login berulang di UI: pesan berbahasa Indonesia 'Terlalu banyak percobaan. Silakan tunggu sebentar lalu coba lagi.' | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): 429 login di UI: pesan 429 tampil dalam bahasa Inggris mentah: 'Too Many Attempts.'</t>
         </is>
       </c>
     </row>
@@ -19639,7 +19639,7 @@
           <t>404 pada resource milik orang lain tampil sebagai "tidak ditemukan"</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19666,12 +19666,12 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): UI: respons 500 pada simpan profil tidak menampilkan detail teknis (benar), tetapi juga TIDAK menampilkan pesan error apa pun kepada pengguna (kegagalan senyap).</t>
+          <t>500 pada simpan profil: Putaran 80 baris: respons 500 (dengan detail SQL) pada simpan profil -&gt; toast 'Terjadi kesalahan, coba lagi.' tanpa detail teknis. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): UI: respons 500 pada simpan profil tidak menampilkan detail teknis (benar), tetapi juga TIDAK menampilkan pesan error apa pun kepada pengguna (kegagalan senyap).</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19689,7 @@
           <t>Respons bukan JSON (HTML error dari proxy) tidak membuat UI crash</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19714,7 +19714,7 @@
           <t>Setiap halaman daftar punya state loading (skeleton) sebelum data datang — tidak ada kilatan state kosong salah</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19739,7 +19739,7 @@
           <t>Setiap halaman daftar punya state kosong dengan ajakan tindakan yang tepat</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19764,7 +19764,7 @@
           <t>Teks sangat panjang (nama produk 150 karakter, alamat panjang, catatan panjang) tidak merusak layout (terpotong/wrap rapi)</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19789,7 +19789,7 @@
           <t>Karakter khusus &amp; emoji pada nama, catatan, chat, judul desain tampil benar &amp; aman (tanpa XSS)</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19814,7 +19814,7 @@
           <t>Angka ekstrem: harga Rp 0, harga sangat besar, qty besar — format &amp; perhitungan benar</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19839,7 +19839,7 @@
           <t>Data bahasa tertentu kosong (name_en kosong) tidak menampilkan "undefined/null"</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19866,12 +19866,12 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): gambar gagal dimuat: 12 gambar gagal dimuat tampil sebagai ikon rusak (alt terisi pada 12); tidak ada placeholder khusus</t>
+          <t>gambar gagal dimuat: Putaran 80 baris: semua permintaan gambar diblokir: 10 kartu menampilkan placeholder netral (ikon) dengan aria-label nama produk, 0 ikon gambar rusak mentah (komponen SafeImage). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): gambar gagal dimuat: 12 gambar gagal dimuat tampil sebagai ikon rusak (alt terisi pada 12); tidak ada placeholder khusus</t>
         </is>
       </c>
     </row>
@@ -19891,12 +19891,12 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Browser QC (Playwright, Edge headless, :3001 + backend QC, putaran 2): tidak ada 'Invalid Date'/NaN. Daftar /account/orders tidak menampilkan tanggal sama sekali (hanya no. pesanan, status, total); API created_at berformat UTC 'Z' (2026-10-13T08:32:08Z). Format WIB pada halaman detail tidak diukur; tanggal null belum dipaksa.</t>
+          <t>format tanggal WIB: Putaran 80 baris: created_at API 2026-10-16T00:49:46.000000Z (UTC) tampil sebagai '16 Oktober 2026' (WIB) di daftar pesanan; detail pesanan tanpa 'Invalid Date'/NaN. Tanggal null dipaksa tidak diuji (kolom created_at selalu terisi). | Sebelumnya (Sebagian): Browser QC (Playwright, Edge headless, :3001 + backend QC, putaran 2): tidak ada 'Invalid Date'/NaN. Daftar /account/orders tidak menampilkan tanggal sama sekali (hanya no. pesanan, status, total); API created_at berformat UTC 'Z' (2026-10-</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
           <t>Refresh di setiap halaman terproteksi mempertahankan sesi &amp; tidak mengalihkan keliru</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19939,7 +19939,7 @@
           <t>Tombol Back/Forward browser berperilaku wajar di alur checkout &amp; modal (tidak membuat pesanan ganda)</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
@@ -19964,7 +19964,7 @@
           <t>Deep-link ke halaman terproteksi saat belum login → login → kembali ke halaman tujuan semula</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -19989,7 +19989,7 @@
           <t>Membuka dua tab pada keranjang/checkout bersamaan tidak merusak data</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20014,7 +20014,7 @@
           <t>Klik ganda cepat pada tombol submit apa pun tidak menggandakan aksi</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20041,12 +20041,12 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tautan eksternal rel: tautan target=_blank: tidak ada; rel noopener otomatis oleh browser modern bila tidak diisi</t>
+          <t>tautan eksternal rel: Putaran 80 baris: 1 tautan target=_blank di profil kreator semuanya rel noopener noreferrer (https://example.com/portfolio). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): tautan eksternal rel: tautan target=_blank: tidak ada; rel noopener otomatis oleh browser modern bila tidak diisi</t>
         </is>
       </c>
     </row>
@@ -20064,7 +20064,7 @@
           <t>Halaman tidak memicu peringatan/error di console browser (periksa tab Console &amp; Network di tiap halaman utama)</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20137,7 +20137,7 @@
           <t>Login: email kosong → ditolak; password kosong → ditolak; email format salah → ditolak</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20162,7 +20162,7 @@
           <t>Register: nama kosong / 151 karakter → ditolak; 150 karakter → lulus</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20187,7 +20187,7 @@
           <t>Register: email &gt; 255 karakter / format salah / sudah terdaftar → ditolak</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20212,7 +20212,7 @@
           <t>Register: password 7 karakter → ditolak; 8 karakter → lulus; konfirmasi berbeda → ditolak</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20237,7 +20237,7 @@
           <t>Register: tanpa centang privacy_accepted / terms_accepted → ditolak</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20262,7 +20262,7 @@
           <t>Spasi di awal/akhir email ditangani; email huruf besar/kecil diperlakukan konsisten</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20287,7 +20287,7 @@
           <t>Profil: nama kosong/&gt;150 → ditolak; telepon &gt;20 → ditolak; telepon kosong → lulus (opsional)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20312,7 +20312,7 @@
           <t>Alamat: label kosong/&gt;50 → ditolak; penerima kosong/&gt;150; telepon kosong/&gt;20</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20337,7 +20337,7 @@
           <t>Alamat: provinsi/kota/kecamatan kosong atau &gt;100 → ditolak</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20362,7 +20362,7 @@
           <t>Alamat: kode pos kosong/&gt;10 karakter → ditolak; alamat lengkap kosong → ditolak</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20387,7 +20387,7 @@
           <t>Alamat: is_default hanya boolean; menetapkan alamat baru sebagai default menurunkan default lama</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20412,7 +20412,7 @@
           <t>Pengajuan: brand &gt;150 / bio &gt;500 / portofolio bukan URL / &gt;255 → ditolak; tanpa terms → ditolak</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20437,7 +20437,7 @@
           <t>KYC: nama KYC kosong/&gt;150; nomor KTP kosong/&gt;100; alamat kosong/&gt;500</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20462,7 +20462,7 @@
           <t>KYC: tanggal lahir kosong / hari ini / masa depan → ditolak; kemarin → lulus</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20487,7 +20487,7 @@
           <t>KYC: foto KTP kosong; PDF/GIF ditolak; JPG &amp; PNG ≤5MB lulus; 5,1MB ditolak</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20512,7 +20512,7 @@
           <t>KYC: metode pencairan di luar {bank_transfer, gopay, ovo, dana, shopeepay} ditolak</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20537,7 +20537,7 @@
           <t>KYC: nomor rekening kosong/&gt;50; nama pemilik kosong/&gt;150</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20562,7 +20562,7 @@
           <t>KYC pengguna &lt;18 tahun tanpa data wali/persetujuan wali → ditolak</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20587,7 +20587,7 @@
           <t>Judul kosong/&gt;150 → ditolak; deskripsi opsional; kategori harus ada di database</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20612,7 +20612,7 @@
           <t>File: wajib saat buat; PNG &amp; SVG ≤20MB lulus; JPG/GIF/PDF ditolak; 20,1MB ditolak</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20637,7 +20637,7 @@
           <t>product_ids: kosong → ditolak; id tidak ada → ditolak; satu id valid → lulus</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20662,7 +20662,7 @@
           <t>Tag: 10 tag lulus, 11 ditolak; satu tag 31 karakter ditolak</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20687,7 +20687,7 @@
           <t>Edit: file opsional; judul &amp; product_ids tetap wajib</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20712,7 +20712,7 @@
           <t>Produk: nama ID/EN kosong/&gt;150 ditolak; harga kosong/negatif/bukan angka ditolak; harga 0 lulus</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20737,7 +20737,7 @@
           <t>Produk: segmen di luar {pria, wanita, unisex, anak} ditolak; kategori tidak ada ditolak</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20762,7 +20762,7 @@
           <t>Varian: warna &gt;50, ukuran &gt;20, potongan &gt;50, material &gt;100 ditolak; area cetak di luar {depan, belakang, lengan} ditolak</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20787,7 +20787,7 @@
           <t>Varian: tambahan harga bukan angka ditolak; negatif lulus; mockup kosong ditolak</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20812,7 +20812,7 @@
           <t>Mockup: PNG/SVG ≤20MB lulus; format lain ditolak</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20837,7 +20837,7 @@
           <t>Tier Bulk: min_qty &lt;1 / bukan bilangan bulat ditolak; max_qty &lt; min_qty ditolak; harga negatif ditolak</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20862,7 +20862,7 @@
           <t>Keranjang: product_variant_id tidak ada → ditolak; quantity 0/negatif/desimal → ditolak; qty 1 lulus (BR-009)</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20887,7 +20887,7 @@
           <t>Checkout: cart_item_ids kosong → ditolak; id milik user lain → ditolak; address_id milik user lain/ tak ada → ditolak</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20912,7 +20912,7 @@
           <t>Checkout: courier_company/courier_type kosong atau &gt;50 → ditolak; kurir yang tidak tersedia untuk alamat → ditolak (bukan ongkir 0)</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20937,7 +20937,7 @@
           <t>Bulk: items kosong ditolak; item qty &lt;1 ditolak; varian tak ada ditolak; design_id tak ada ditolak</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20962,7 +20962,7 @@
           <t>Ongkir (shipping-rates): wajib address_id + salah satu dari cart_item_ids / items</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -20987,7 +20987,7 @@
           <t>Catatan (notes) panjang &amp; karakter khusus tersimpan aman</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21012,7 +21012,7 @@
           <t>Ulasan: rating 0/6/kosong ditolak; 1–5 lulus; order_item bukan milik user ditolak; komentar opsional</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21037,7 +21037,7 @@
           <t>Chat: pesan kosong / 2001 karakter ditolak; 2000 lulus</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21062,7 +21062,7 @@
           <t>Wishlist: harus salah satu dari product_id atau design_id; keduanya kosong ditolak; id tak ada ditolak</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21087,7 +21087,7 @@
           <t>Alasan tolak/ban: kurang dari 10 karakter ditolak (UI menonaktifkan tombol); 10 karakter lulus</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21112,7 +21112,7 @@
           <t>Ban: copyright_violation hanya boolean</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21137,7 +21137,7 @@
           <t>Booking: courier_company/courier_type opsional (≤50); override format salah ditolak/ditangani</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21162,7 +21162,7 @@
           <t>Status pesanan: hanya nilai diproses_produksi diterima; nilai lain ditolak</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21187,7 +21187,7 @@
           <t>Pengaturan notifikasi: is_enabled wajib boolean; tipe tak dikenal → 404</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21212,7 +21212,7 @@
           <t>sort di luar daftar yang diizinkan → ditolak (422), bukan 500</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21237,7 +21237,7 @@
           <t>page &lt;1 / per_page &gt;100 / per_page 0 → ditolak</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21262,7 +21262,7 @@
           <t>price_min negatif ditolak; price_max &lt; price_min ditolak</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21287,7 +21287,7 @@
           <t>genders/print_areas di luar enum ditolak; array kosong diabaikan</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21312,7 +21312,7 @@
           <t>lang di luar {id,en} ditolak; search &gt;150 karakter ditolak</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21337,7 +21337,7 @@
           <t>Parameter berupa array terstruktur (categories[]=a&amp;categories[]=b) bekerja</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21410,7 +21410,7 @@
           <t>Customer biasa tidak bisa mengakses endpoint upload desain (403)</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21435,7 +21435,7 @@
           <t>Creator berstatus menunggu approval tidak bisa upload desain sampai disetujui</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21460,7 +21460,7 @@
           <t>Desain baru tidak tampil publik sebelum approval admin</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21485,14 +21485,14 @@
           <t>Creator tidak bisa diaktifkan tanpa data KYC lengkap (validasi KTP, tanggal lahir, rekening)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Sebagian</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>approve creator tanpa KYC: Verifikasi tambahan (kelompok hanya-API): tidak ada profil creator tanpa KYC di data uji | Sebelumnya (Sebagian): approve creator tanpa KYC: Verifikasi tambahan (kelompok hanya-API): tidak ada profil creator tanpa KYC di dat</t>
+          <t>approve tanpa KYC: Putaran 80 baris: status=200, status profil=aktif, {"data":{"id":12,"user":{"id":20,"name":"Herman Schiller PhD","email":"jamal.collier@example.com"}," | Sebelumnya (Sebagian): approve creator tanpa KYC: Verifikasi tambahan (kelompok hanya-API): tidak ada profil creator tanpa KYC di data uji | Sebelumnya (Sebagian): approve creator tanpa KYC: Verifikasi tambahan (kelompok hanya-API): tidak ada profil creator tanpa</t>
         </is>
       </c>
     </row>
@@ -21510,7 +21510,7 @@
           <t>Pesanan Belum Dibayar tidak muncul di Antrian Produksi &amp; tidak bisa di-"Mulai Produksi"</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21537,12 +21537,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Kode: MidtransWebhookController memverifikasi signature (403 bila salah) lalu mengambil status server-ke-server (getTransactionStatus). Webhook valid tidak disimulasikan: env QC tanpa kunci Midtrans; ada test PHPUnit. Pengujian signature palsu ada di sheet Keamanan.</t>
+          <t>Putaran 80 baris: MidtransWebhookController memverifikasi signature (403 bila salah) lalu mengambil status server-ke-server; tes PHPUnit memetakan settlement, capture+accept, pending, deny, cancel, expire ke status pembayaran/pesanan yang benar (hanya settlement/capture-accept memajukan pesanan ke Menunggu Approval). | Sebelumnya (Sebagian): Kode: MidtransWebhookController memverifikasi signature (403 bila salah) lalu mengambil status server-ke-server (getTransactionStatus). Webhook valid tidak disimulasikan: env QC tanpa kunci Midtrans; ada test PHPUnit. Pengujian signature pa</t>
         </is>
       </c>
     </row>
@@ -21560,7 +21560,7 @@
           <t>Form rating tidak muncul/ditolak API sebelum status Selesai</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21610,7 +21610,7 @@
           <t>Satu item hanya dapat diulas sekali; ulasan hanya oleh pemilik pesanan</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21635,7 +21635,7 @@
           <t>Tidak ada tombol/endpoint untuk mengunduh file asli desain creator oleh customer</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21660,7 +21660,7 @@
           <t>URL file asli desain tidak terekspos lewat respons API publik selain yang dibutuhkan (thumbnail)</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21735,7 +21735,7 @@
           <t>Komisi tercipta otomatis per item pesanan yang memakai desain creator saat pesanan dibayar (bukan untuk custom upload)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21760,7 +21760,7 @@
           <t>Nominal = persentase (CREATOR_COMMISSION_RATE) × subtotal item</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21785,7 +21785,7 @@
           <t>Payout mingguan hanya untuk total terhutang ≥ CREATOR_PAYOUT_MINIMUM &amp; rekening terisi</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21812,12 +21812,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kode: tanpa DISBURSEMENT api_key disburse() mengembalikan null -&gt; komisi tidak ditandai dibayar (benar). TEMUAN: bila api_key diisi, disburse() hanya mengembalikan UUID acak tanpa transfer nyata dan komisi langsung 'dibayar' (stub PayoutService.php:~79).</t>
+          <t>Putaran 80 baris: PERBAIKAN: PayoutService::disburse() dulu mengembalikan UUID acak bila api_key diisi sehingga komisi ditandai dibayar tanpa transfer; kini mengembalikan null (tidak menandai dibayar) sampai integrasi nyata ada. Dicakup test PayoutTest. | Sebelumnya (Sebagian): Kode: tanpa DISBURSEMENT api_key disburse() mengembalikan null -&gt; komisi tidak ditandai dibayar (benar). TEMUAN: bila api_key diisi, disburse() hanya mengembalikan UUID acak tanpa transfer nyata dan komisi langsung 'dibayar' (stub PayoutSer</t>
         </is>
       </c>
     </row>
@@ -21862,12 +21862,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>API: checkout 1 pcs berhasil (201, belum_dibayar, ongkir Biteship Sandbox); qty 0/negatif ditolak (Validasi #30). Catatan: produk uji berharga 0 menghasilkan subtotal 0 - admin dapat membuat produk harga 0 (sesuai Validasi #24).</t>
+          <t>Putaran 80 baris: checkout 1 pcs berhasil (201, belum_dibayar); qty 0/negatif ditolak 422 (Validasi #30). | Sebelumnya (Sebagian): API: checkout 1 pcs berhasil (201, belum_dibayar, ongkir Biteship Sandbox); qty 0/negatif ditolak (Validasi #30). Catatan: produk uji berharga 0 menghasilkan subtotal 0 - admin dapat membuat produk harga 0 (sesuai Validasi #24).</t>
         </is>
       </c>
     </row>
@@ -21885,7 +21885,7 @@
           <t>Batal diizinkan hanya status Menunggu Approval; status lain → 422</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -21912,12 +21912,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Rute: tidak ada endpoint batal per-item/parsial (route:list). Tidak ada DP. UI tidak diuji.</t>
+          <t>Putaran 80 baris: route:list tidak memiliki endpoint batal per-item/parsial maupun DP; UI detail pesanan hanya menyediakan satu tombol 'Batalkan Pesanan' untuk seluruh pesanan (BR-018/022). | Sebelumnya (Sebagian): Rute: tidak ada endpoint batal per-item/parsial (route:list). Tidak ada DP. UI tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -21962,12 +21962,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verifikasi ulang setelah perbaikan: tier tumpang tindih kini ditolak (422); nilai tepi di semua batas (qty = min, = maks, = maks+1) belum diuji penuh lewat checkout. | Sebelumnya (Sebagian): Tier seed: 1-49 Rp80rb, 50-99 Rp70rb, 100-249 Rp60rb, 250+ Rp50rb. Bulk qty 5 diproses (201) dengan harga 80rb</t>
+          <t>Putaran 80 baris: nilai tepi tier diuji otomatis (1, 49, 50, 99, 100, 249, 250, 100000 -&gt; tier benar); tier tumpang tindih ditolak 422; qty 0 ditolak; qty di atas tier tertinggi memakai tier tanpa batas. | Sebelumnya (Sebagian): Verifikasi ulang setelah perbaikan: tier tumpang tindih kini ditolak (422); nilai tepi di semua batas (qty = min, = maks, = maks+1) belum diuji penuh lewat checkout. | Sebelumnya (Sebagian): Tier seed: 1-49 Rp80rb, 50-99 Rp70rb, 100-249 Rp6</t>
         </is>
       </c>
     </row>
@@ -21985,7 +21985,7 @@
           <t>Harga tier sama persis di halaman Bulk Order, Checkout Bulk, &amp; tabel pesanan</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -22010,7 +22010,7 @@
           <t>Tidak ada registrasi creator terpisah; satu email = satu akun</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -22035,7 +22035,7 @@
           <t>User creator tetap bisa belanja sebagai customer tanpa logout</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -22062,12 +22062,12 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Kode/test BR-014 (webhook delivered -&gt; menunggu_konfirmasi, auto-complete 3 hari kerja via config business.auto_complete_business_days=3). Webhook Biteship asli tidak dijalankan.</t>
+          <t>Putaran 80 baris: webhook delivered -&gt; menunggu_konfirmasi (test ShippingTest), konfirmasi manual -&gt; selesai, auto-selesai 3 hari kerja dengan akhir pekan dilewati (test baru: terkirim Jumat 10:00 -&gt; belum selesai Selasa 23:59, selesai Rabu 10:00). | Sebelumnya (Sebagian): Kode/test BR-014 (webhook delivered -&gt; menunggu_konfirmasi, auto-complete 3 hari kerja via config business.auto_complete_business_days=3). Webhook Biteship asli tidak dijalankan.</t>
         </is>
       </c>
     </row>
@@ -22085,7 +22085,7 @@
           <t>Job cancel-unpaid membatalkan tepat &gt; 24 jam; nilai waktu dibaca dari config/business.php</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -22110,7 +22110,7 @@
           <t>Pesanan yang dibatalkan menyimpan cancelled_by=system &amp; riwayat status</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Lulus</t>
         </is>
@@ -22237,12 +22237,12 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>API: /checkout/bulk menerima items tanpa keranjang (201, harga tier); /checkout memakai cart_item_ids. Tercakup test BR-026.</t>
+          <t>Putaran 80 baris: /checkout/bulk menerima items langsung tanpa keranjang (harga tier); /checkout memakai cart_item_ids (harga produk); tercakup test BR-026. | Sebelumnya (Sebagian): API: /checkout/bulk menerima items tanpa keranjang (201, harga tier); /checkout memakai cart_item_ids. Tercakup test BR-026.</t>
         </is>
       </c>
     </row>
@@ -22262,12 +22262,12 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kode/test BR-026: bulk memakai items langsung, keranjang tak tersentuh. UI tidak diuji.</t>
+          <t>Putaran 80 baris: bulk memakai items langsung sehingga keranjang tidak tersentuh (kode + test BR-026); halaman bulk order tidak membaca keranjang. | Sebelumnya (Sebagian): Kode/test BR-026: bulk memakai items langsung, keranjang tak tersentuh. UI tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -22312,12 +22312,12 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Sebagian</t>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>API: PATCH notification-settings berfungsi (Validasi #43); efek mematikan notifikasi dibuktikan test BR-027. TEMUAN: tipe tak dikenal membuat baris baru.</t>
+          <t>Putaran 80 baris: PATCH notification-settings berfungsi; tipe tak dikenal kini 404 tanpa membuat baris (diperbaiki); efek mematikan jenis notifikasi dibuktikan test BR-027. | Sebelumnya (Sebagian): API: PATCH notification-settings berfungsi (Validasi #43); efek mematikan notifikasi dibuktikan test BR-027. TEMUAN: tipe tak dikenal membuat baris baru.</t>
         </is>
       </c>
     </row>

--- a/Required Document/QC_Claude_Hasil.xlsx
+++ b/Required Document/QC_Claude_Hasil.xlsx
@@ -513,13 +513,13 @@
         <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -541,13 +541,13 @@
         <v>135</v>
       </c>
       <c r="C3" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>4</v>
@@ -569,13 +569,13 @@
         <v>51</v>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -597,13 +597,13 @@
         <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1</v>
@@ -625,13 +625,13 @@
         <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
@@ -653,13 +653,13 @@
         <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -709,13 +709,13 @@
         <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -737,13 +737,13 @@
         <v>64</v>
       </c>
       <c r="C10" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
@@ -765,13 +765,13 @@
         <v>68</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
@@ -793,13 +793,13 @@
         <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -898,14 +898,14 @@
           <t>Registrasi akun baru (centang syarat &amp; privasi) → email verifikasi tiba → klik tautan → "Email berhasil diverifikasi"</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>API registrasi 201 + verifikasi bertanda tangan 403 bila diubah (sheet Keamanan/Validasi); email verifikasi nyata &amp; klik tautan tidak dapat diuji (mail=log).</t>
+          <t>registrasi dan verifikasi email: Putaran 28 baris: registrasi (201, syarat &amp; privasi dicentang) -&gt; email verifikasi di log -&gt; membuka tautan bertanda tangan di browser menampilkan 'Email berhasil diverifikasi' dan email_verified_at terisi (2026-10-16 16:26:19). Pengiriman ke inbox nyata tidak diuji. | Sebelumnya (Sebagian): API registrasi 201 + verifikasi bertanda tangan 403 bila diubah (sheet Keamanan/Validasi); email verifikasi nyata &amp; klik tautan tidak dapat diuji (mail=log).</t>
         </is>
       </c>
     </row>
@@ -2373,14 +2373,14 @@
           <t>Customer A tidak menerima pesan/notifikasi milik customer B</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Isolasi per user diuji via API (chat/notifikasi orang lain 403/404, sheet Keamanan #9); kanal WebSocket tidak diuji.</t>
+          <t>Putaran 28 baris: isolasi API (chat/notifikasi orang lain 403/404) dan otorisasi kanal privat realtime (test /broadcasting/auth: customer lain ditolak 403 untuk chat.{thread} dan App.Models.User.{id}); pengiriman WebSocket nyata butuh Pusher. | Sebelumnya (Sebagian): Isolasi per user diuji via API (chat/notifikasi orang lain 403/404, sheet Keamanan #9); kanal WebSocket tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
           <t>Jalankan alur belanja penuh dalam mode EN → semua teks UI, pesan error validasi, &amp; email berbahasa Inggris</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Accept-Language: en menghasilkan pesan validasi berbahasa Inggris; nama produk seed id=en sama sehingga tidak dapat dibedakan; UI/email EN tidak diuji.</t>
+          <t>Putaran 28 baris: alur belanja di mode EN: sapuan 21 halaman UI tanpa teks Indonesia, pesan validasi Inggris, email Inggris, notifikasi Inggris, nama/deskripsi produk Inggris (data QC punya satu produk dengan nama EN berbeda). Teks dari pengguna (nama desain, alamat) tentu tidak diterjemahkan. | Sebelumnya (Sebagian): Accept-Language: en menghasilkan pesan validasi berbahasa Inggris; nama produk seed id=en sama sehingga tidak dapat dibedakan; UI/email EN tidak diuji.</t>
         </is>
       </c>
     </row>
@@ -3171,14 +3171,14 @@
           <t>Validasi gagal → 422 dengan struktur errors per-field berbahasa sesuai (Accept-Language / ?lang)</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sheet Validasi Form: 422 dengan errors per-field (bahasa ID). Lokalisasi EN pesan error backend belum penuh (known gap).</t>
+          <t>Putaran 28 baris: 422 berstruktur errors per-field; bahasa mengikuti Accept-Language/?lang: terverifikasi untuk id dan en (validation.php en memakai teks bawaan Laravel; atribut kustom jatuh ke nama kolom). | Sebelumnya (Sebagian): Sheet Validasi Form: 422 dengan errors per-field (bahasa ID). Lokalisasi EN pesan error backend belum penuh (known gap).</t>
         </is>
       </c>
     </row>
@@ -3246,14 +3246,14 @@
           <t>Respons uang konsisten (string 2 desimal) di semua endpoint</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>format uang: Putaran 80 baris: 304 bidang; tidak konsisten: /orders.meta.total=8 ; /catalog/products?per_page=3.meta.total=11 ; /marketplace/designs?per_page=3.data.0.starting_price=58000 ; /marketplace/designs?per_page=3.data.1.starting_price=191000 ; /marketplace/designs?per_page=3.data.2.starting_price=174000 | Sebelumnya (Sebagian): Contoh respons uang berupa string 2 desimal ('120000.00'); tidak semua endpoint disapu.</t>
+          <t>Putaran 28 baris: sapuan 15 endpoint menemukan 1 bidang uang tidak konsisten (starting_price desain berupa angka); DIPERBAIKI menjadi string 2 desimal. meta.total/count memang bilangan bulat. | Sebelumnya (Sebagian): format uang: Putaran 80 baris: 304 bidang; tidak konsisten: /orders.meta.total=8 ; /catalog/products?per_page=3.meta.total=11 ; /marketplace/designs?per_page=3.data.0.starting_price=58000 ; /marketpla</t>
         </is>
       </c>
     </row>
@@ -3571,14 +3571,14 @@
           <t>Kanal privat chat.{thread} hanya bisa di-subscribe peserta thread; admin.chat hanya admin</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>routes/channels.php mendefinisikan chat.{threadId}; otorisasi kanal tidak disimulasikan dengan koneksi WebSocket.</t>
+          <t>Putaran 28 baris: test otomatis POST /broadcasting/auth dengan driver pusher (kunci uji): peserta thread 200, bukan peserta 403, admin 200 pada chat.{thread} dan admin.chat, bukan admin pada admin.chat 403, kanal user sendiri 200 dan milik orang lain 403. | Sebelumnya (Sebagian): routes/channels.php mendefinisikan chat.{threadId}; otorisasi kanal tidak disimulasikan dengan koneksi WebSocket.</t>
         </is>
       </c>
     </row>
@@ -3746,14 +3746,14 @@
           <t>Domain produksi ada di allowlist gambar Next.js; gambar tampil melalui optimizer (/_next/image)</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Allowlist domain ada; tampil via /_next/image di produksi diperiksa di sheet Public.</t>
+          <t>Putaran 28 baris: build produksi + next start: /_next/image untuk https://cdn.harmoniclothing.com/mockups/placeholder.png menjawab 200 (domain CDN ada di allowlist), host lain (evil.example.com) ditolak 400; header keamanan (X-Frame-Options, HSTS, nosniff) ikut terkirim. | Sebelumnya (Sebagian): Allowlist domain ada; tampil via /_next/image di produksi diperiksa di sheet Public.</t>
         </is>
       </c>
     </row>
@@ -5069,14 +5069,14 @@
           <t>Tidak ada rahasia (.env, kunci API, token) di repo Git, bundle frontend, atau respons error; hanya NEXT_PUBLIC_* publik di bundle</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tidak ada .env rahasia ter-track (hanya .env.example); frontend/.env.production ter-track tetapi hanya berisi nilai NEXT_PUBLIC publik. Tidak ada pola kunci API di file ter-track dan kunci Biteship tidak ada di riwayat git. Bundle frontend produksi belum diperiksa.</t>
+          <t>Putaran 28 baris: next build produksi (env produksi asli) lalu grep .next/static dan .next/server: 0 berkas memuat pola kunci (SB-Mid-server, biteship_test/live, APP_KEY base64, PRIVATE KEY, sk_live, DB_PASSWORD, PUSHER secret, R2 secret, AKIA); .env ter-track hanya .env.example dan frontend/.env.production (nilai publik); riwayat git tidak memuat kunci Biteship/Midtrans/APP_KEY. | Sebelumnya (Sebagian): Tidak ada .env rahasia ter-track (hanya .env.example); frontend/.env.production ter-track tetapi hanya berisi nilai NEXT_PUBLIC publik. Tidak ada pola kunci API di file ter-track dan kunci Biteship ti</t>
         </is>
       </c>
     </row>
@@ -5892,14 +5892,14 @@
           <t>Tautan PRODUK (T-Shirt, Hoodie, Jacket) mengarah ke katalog dengan filter yang benar</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Putaran 80 baris: footer memakai /catalog?kategori=t-shirt|hoodie|jacket (slug sesuai kategori produksi menurut catatan sebelumnya); verifikasi ulang ke API produksi tidak bisa dilakukan sekarang karena backend laptop (tunnel Cloudflare) sedang mati (HTTP 530). Data QC memakai kategori acak sehingga hasil filter tidak dapat dicocokkan. | Sebelumnya (Sebagian): Browser QC (localhost:3001 + backend QC): footer: /catalog?kategori=t-shirt|hoodie|jacket; kategori seed QC acak, jadi hasil filter tidak bisa diverifikasi.</t>
+          <t>tautan produk di footer: Putaran 28 baris: tiga tautan PRODUK footer (T-Shirt, Hoodie, Jacket) mengarah ke /catalog?kategori=&lt;slug&gt; dan menghasilkan filter yang benar (lihat #67); katalog produksi masih data demo acak sehingga kategori sungguhan perlu dibuat pemilik. | Sebelumnya (Sebagian): Putaran 80 baris: footer memakai /catalog?kategori=t-shirt|hoodie|jacket (slug sesuai kategori produksi menurut catatan sebelumnya); verifikasi ulang ke API produksi tidak bisa dilakukan sekarang kare</t>
         </is>
       </c>
     </row>
@@ -6967,14 +6967,14 @@
           <t>Filter via URL dari footer (mis. kategori T-Shirt) menghasilkan hasil benar</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Putaran 80 baris: tautan footer menghasilkan filter kategori lewat URL (diuji berfungsi di QC dengan kategori seed); hasil untuk kategori produksi T-Shirt/Hoodie/Jacket belum diverifikasi ulang karena backend produksi sedang mati (HTTP 530). | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): tautan footer 'T-Shirt' -&gt; /catalog?kategori=t-shirt menghasilkan 'Menampilkan 0 dari 10 produk': slug kategori di footer tidak cocok dengan kategori data QC (seed faker: Dolorum ipsam, dst.), jadi hasil </t>
+          <t>filter kategori dari footer: Putaran 28 baris: data QC diberi kategori T-Shirt/Hoodie/Jacket (2 produk tiap kategori); klik tautan footer -&gt; /catalog?kategori=&lt;slug&gt; dan menampilkan tepat 2 kartu per kategori (T-Shirt: Menampilkan 2 dari 13, Hoodie: Menampilkan 2 dari 13, Jacket: Menampilkan 2 dari 13). Katalog produksi saat ini masih data demo acak, jadi kategori sungguhan perlu dibuat pemilik. | Sebelumnya (Sebagian): Putaran 80 baris: tautan footer menghasilkan filter kategori lewat URL (diuji berfungsi di QC dengan kategori seed); hasil untuk kategori produksi T-Shirt/Hoodie/Jacket belum diverifikasi ulang karena</t>
         </is>
       </c>
     </row>
@@ -7117,14 +7117,14 @@
           <t>Galeri gambar berganti sesuai warna yang dipilih; thumbnail dapat diklik</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): galeri berganti sesuai warna: warna tersedia=; gambar utama berubah saat ganti warna=false; jumlah gambar=9; mockup seed memakai placeholder sama sehingga perubahan visual tidak dapat dibuktikan penuh</t>
+          <t>galeri sesuai warna: Putaran 28 baris: produk 'Sequi explicabo nisi' dengan dua warna (Hitam, Merah QC) berbeda berkas mockup: memilih Hitam menampilkan qc-warna-a.png, memilih Merah QC menampilkan qc-warna-b.png (gambar utama berganti); 4 thumbnail dapat diklik. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): galeri berganti sesuai warna: warna tersedia=; gambar utama berubah saat ganti warna=false; jumlah gambar=9; mockup seed memakai placeholder sama se</t>
         </is>
       </c>
     </row>
@@ -11346,14 +11346,14 @@
           <t>Upload desain sendiri (opsional) berfungsi; link pilih desain marketplace berfungsi; catatan opsional tersimpan</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): bulk order: upload desain, pilih marketplace, catatan: halaman bulk order: input upload desain=1, tautan pilih desain marketplace=1, kolom catatan=1; penyimpanan catatan sampai ke pesanan tidak diverifikasi (butuh checkout bulk + Midtrans)</t>
+          <t>Putaran 28 baris: UI bulk order memuat input upload, tautan pilih desain marketplace, dan kolom catatan; test otomatis checkout bulk menyimpan custom_design_file_path dan notes pada pesanan serta design_id untuk desain marketplace. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): bulk order: upload desain, pilih marketplace, catatan: halaman bulk order: input upload desain=1, tautan pilih desain marketplace=1, kolom catatan=1</t>
         </is>
       </c>
     </row>
@@ -12021,14 +12021,14 @@
           <t>Pratinjau desain per item (file yang dikirim customer / desain marketplace) tampil benar</t>
         </is>
       </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>pratinjau desain per item: Putaran 80 baris: pratinjau desain marketplace di detail pesanan tampil (thumbnail), dan API mengirim custom_design_url untuk unggahan customer sendiri; render berkas unggahan customer di UI butuh pesanan berisi unggahan (checkout Snap) - belum dibuat di data QC. | Sebelumnya (Sebagian): Browser QC (Playwright, putaran 2): detail pesanan HC-20261013-7551 (item dengan desain marketplace): pratinjau desain tampil sebagai thumbnail kecil 64px (placeholder seed 'designs/thumbnails/placeholder.png'); API mengirim design_file_url</t>
+          <t>pratinjau unggahan customer: Putaran 28 baris: item pesanan dengan unggahan customer sendiri: halaman detail kini menampilkan pratinjau berkas desain itu (label 'Desain kamu', naturalWidth 48px) di samping foto produk; sebelumnya hanya foto produk yang tampil. Desain marketplace tampil sebagai thumbnail desain. | Sebelumnya (Sebagian): pratinjau desain per item: Putaran 80 baris: pratinjau desain marketplace di detail pesanan tampil (thumbnail), dan API mengirim custom_design_url untuk unggahan customer sendiri; render berkas unggah</t>
         </is>
       </c>
     </row>
@@ -13719,14 +13719,14 @@
           <t>Submit berhasil → status "Menunggu Review" tampil; form terkunci/ditampilkan baca-saja</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>KYC terkirim: tampilan baca-saja: Verifikasi tambahan (kelompok hanya-API): teks='Verifikasi Data Diri / Verifikasi Data Diri', input file=1, tombol kirim=1 | Sebelumnya (Sebagian): KYC terkirim: tampilan baca-saja: Verifikasi tambahan (kelompok hanya-API): teks='Verifikasi Data Diri / Verif</t>
+          <t>KYC terkirim: Putaran 28 baris: submit KYC lewat UI -&gt; status 'Menunggu Review' tampil dan formulir tidak lagi ditampilkan (terkunci); setelah reload status dibaca dari server (GET /creator/verification) dan tetap terkunci dengan catatan 'sedang ditinjau admin'. Sebelumnya status hanya di memori halaman sehingga formulir bisa diisi ulang. | Sebelumnya (Sebagian): KYC terkirim: tampilan baca-saja: Verifikasi tambahan (kelompok hanya-API): teks='Verifikasi Data Diri / Verifikasi Data Diri', input file=1, tombol kirim=1 | Sebelumnya (Sebagian): KYC terkirim: tamp</t>
         </is>
       </c>
     </row>
@@ -13744,14 +13744,14 @@
           <t>Status Disetujui/Ditolak/Diblokir tampil benar; Ditolak menampilkan alasan &amp; bisa mengajukan ulang (BR-028 versi creator bila ada)</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): status verifikasi tampil: halaman verifikasi creator aktif menampilkan: ; status Ditolak/Diblokir dengan alasan &amp; ajukan ulang (BR-028) diuji di sheet Validasi/BR via API</t>
+          <t>status ditolak dan diblokir: Putaran 28 baris: Ditolak: badge + alasan 'Foto KTP buram, unggah ulang' + formulir kembali terbuka untuk kirim ulang (BR-028); Diblokir: badge + catatan hubungi admin, formulir terkunci; Disetujui: badge + catatan akun aktif, formulir terkunci. Server menolak kirim ulang selain status ditolak (test otomatis). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): status verifikasi tampil: halaman verifikasi creator aktif menampilkan: ; status Ditolak/Diblokir dengan alasan &amp; ajukan ulang (BR-028) diuji di she</t>
         </is>
       </c>
     </row>
@@ -13994,14 +13994,14 @@
           <t>Preview desain pada tiap produk/apparel yang dipilih tampil benar</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): preview desain per produk (detail creator): detail desain aktif #13: 2 gambar, 0 gagal dimuat (naturalWidth=0); teks: Produk #9 / Produk #10</t>
+          <t>preview per produk: Putaran 28 baris: detail desain #13: 2 gambar pratinjau termuat semua (naturalWidth &gt; 0) dan nama produk apparel tampil. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): preview desain per produk (detail creator): detail desain aktif #13: 2 gambar, 0 gagal dimuat (naturalWidth=0); teks: Produk #9 / Produk #10</t>
         </is>
       </c>
     </row>
@@ -14369,14 +14369,14 @@
           <t>Preview file yang diunggah tampil (bukan broken image)</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>preview file unggahan tampil: Verifikasi tambahan (kelompok hanya-API): gambar=4, rusak=1 | Sebelumnya (Sebagian): preview file unggahan tampil: Verifikasi tambahan (kelompok hanya-API): gambar=4, rusak=1 | Sebelumnya (Sebagi</t>
+          <t>preview unggahan: Putaran 28 baris: memilih berkas PNG di halaman upload kini menampilkan pratinjau gambar (blob, naturalWidth &gt; 0, tanpa gambar rusak); sebelumnya halaman hanya menampilkan nama berkas. | Sebelumnya (Sebagian): preview file unggahan tampil: Verifikasi tambahan (kelompok hanya-API): gambar=4, rusak=1 | Sebelumnya (Sebagian): preview file unggahan tampil: Verifikasi tambahan (kelompok hanya-API): gambar=4, rus</t>
         </is>
       </c>
     </row>
@@ -15517,14 +15517,14 @@
           <t>Ubah data lalu "Simpan Perubahan" → toast sukses &amp; tabel ter-update; refresh tetap tersimpan</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): tambah produk via UI + 42 slug: produk baru tidak ditemukan (10 -&gt; 10); field input=8 | Bukti lain: API: update produk berhasil (E2E-09); toast/tabel UI tidak diuji.</t>
+          <t>edit produk lewat UI: Putaran 28 baris: ubah nama produk lewat form 'Simpan Perubahan': toast sukses tampil; tabel memuat nama baru 'Harum iure perferendis (QC)' dan nilai tetap setelah reload (API: Harum iure perferendis (QC)). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): tambah produk via UI + 42 slug: produk baru tidak ditemukan (10 -&gt; 10); field input=8 | Bukti lain: API: update produk berhasil (E2E-09); toast/tabe</t>
         </is>
       </c>
     </row>
@@ -15792,14 +15792,14 @@
           <t>Edit varian inline (baris varian) tersimpan; ganti foto mockup berfungsi</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Verifikasi ulang setelah perbaikan: tombol aksi baris varian kini punya nama aksesibel ('Edit'); edit inline dan ganti foto mockup belum diotomasi penuh. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): edit varian inline: tombol aksi baris varian berupa ikon t</t>
+          <t xml:space="preserve">edit varian dan ganti mockup: Putaran 28 baris: edit inline varian #33: price_modifier 0.00 -&gt; 12345.00 dan mockup diganti (40b-4be6-8bfa-7ea491c2183f.png) tersimpan di API setelah Simpan. | Sebelumnya (Sebagian): Verifikasi ulang setelah perbaikan: tombol aksi baris varian kini punya nama aksesibel ('Edit'); edit inline dan ganti foto mockup belum diotomasi penuh. | Sebelumnya (Sebagian): UI (Playwright, Edge </t>
         </is>
       </c>
     </row>
@@ -16467,14 +16467,14 @@
           <t>"Ganti Kurir": modal format perusahaan:tipe (mis. jne:reg); override berhasil membooking kurir lain</t>
         </is>
       </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Ganti Kurir: tombol 'Ganti Kurir' ada (2); modal: 'HC-20261013-6233	jne reg	jne	WB123	Sudah Dibooking / HC-20261013-9139	jne reg	-	-	Belum Dibooking / HC-20261013-7645	jne reg	-	-	Belum Dibooking'; booking ke kurir lain tidak dijalankan agar tidak membuat order Biteship sandbox baru</t>
+          <t>Putaran 28 baris: test otomatis dengan Http::fake Biteship: override gojek/instant (default pesanan jne/reg) -&gt; permintaan ke api.biteship.com/v1/orders memuat courier_company=gojek dan courier_type=instant, shipment tersimpan dengan kurir baru dan biteship_order_id. Booking ke order sandbox baru tidak dibuat. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): Ganti Kurir: tombol 'Ganti Kurir' ada (2); modal: 'HC-20261013-6233	jne reg	jne	WB123	Sudah Dibooking / HC-20261013-9139	jne reg	-	-	Belum Dibooking</t>
         </is>
       </c>
     </row>
@@ -16517,14 +16517,14 @@
           <t>Biteship down/kredensial salah → pesan error jelas, tidak membuat shipment setengah jadi</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Biteship down / kredensial salah: kegagalan Biteship tidak disimulasikan (mematikan key QC butuh restart backend); tinjau kode OrderService::bookShipment: catch/throw ada=true</t>
+          <t>Putaran 28 baris: PERBAIKAN + test: Biteship menjawab 401 -&gt; admin menerima 422 dengan pesan jelas ('Layanan kurir (Biteship) tidak dapat dihubungi atau menolak permintaan. Pengiriman belum dibuat'), tidak ada baris shipment, status pesanan tetap diproses_produksi, dan booking ulang berhasil. Sebelumnya respons 500 generik. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): Biteship down / kredensial salah: kegagalan Biteship tidak disimulasikan (mematikan key QC butuh restart backend); tinjau kode OrderService::bookShi</t>
         </is>
       </c>
     </row>
@@ -17365,14 +17365,14 @@
           <t>Mode EN: telusuri satu halaman tiap role — TIDAK boleh ada teks Indonesia tersisa pada UI (catat setiap temuan)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): mode EN: sisa teks Indonesia: 20 halaman (4 role) dalam EN; sisa teks Indonesia pada 2 halaman: /account/addresses: Hapus UI || /notifications: Pesanan selesai / Pesanan sampai / Pesanan HC-20261013-6457 telah sampai. Konfirmasi penerimaan sekarang.</t>
+          <t>Putaran 28 baris: sapuan mode EN pada 21 halaman 4 peran: satu-satunya kata Indonesia yang terdeteksi adalah 'Produk' pada nama data uji ('Produk QC Audit') di tabel admin, bukan teks antarmuka. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): mode EN: sisa teks Indonesia: 20 halaman (4 role) dalam EN; sisa teks Indonesia pada 2 halaman: /account/addresses: Hapus UI || /notifications: Pesa</t>
         </is>
       </c>
     </row>
@@ -17415,14 +17415,14 @@
           <t>Pesan error validasi dari backend mengikuti bahasa; email verifikasi/reset mengikuti bahasa</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>API: Accept-Language: en menghasilkan pesan validasi berbahasa Inggris; email dan pesan backend lain tetap Indonesia (known gap).</t>
+          <t>Putaran 28 baris: Accept-Language en: pesan validasi berbahasa Inggris; email verifikasi dan reset memakai subjek/isi Inggris (test render locale en vs id); teks notifikasi in-app kini mengikuti bahasa pembaca; seluruh berkas lang id/en memiliki jumlah kunci sama kecuali nama atribut validasi kustom (jatuh ke nama kolom bawaan). | Sebelumnya (Sebagian): API: Accept-Language: en menghasilkan pesan validasi berbahasa Inggris; email dan pesan backend lain tetap Indonesia (known gap).</t>
         </is>
       </c>
     </row>
@@ -17865,14 +17865,14 @@
           <t>Koneksi lambat (Fast 3G): halaman tetap dapat dipakai, skeleton tampil, tidak ada timeout diam-diam</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): Fast 3G: Fast 3G (latensi 562ms, 1.6Mbps): daftar produk muncul setelah 25 dtk (10 kartu); skeleton terdeteksi saat awal=9; dev server tanpa optimasi produksi sehingga angka bukan acuan produksi</t>
+          <t>Putaran 28 baris: situs produksi dengan throttle Fast 3G (latensi 562ms, 1.6Mbps, CDP): /catalog menampilkan judul dan kartu produk pada ~1.0 dtk (halaman pertama dirender di server); beranda menampilkan judul pada 0.9 dtk dengan skeleton lalu kartu populer pada 5.9 dtk; tidak ada timeout diam-diam. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): Fast 3G: Fast 3G (latensi 562ms, 1.6Mbps): daftar produk muncul setelah 25 dtk (10 kartu); skeleton terdeteksi saat awal=9; dev server tanpa optimas</t>
         </is>
       </c>
     </row>
@@ -17890,15 +17890,15 @@
           <t>JavaScript nonaktif: halaman publik utama tetap menampilkan konten dasar (SSR) atau pesan yang sesuai</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): JavaScript nonaktif: tanpa JS: /: 3016 karakter, h1='Wujudkan Ide.
-Ciptakan Produk.', produk=0 ; /catalog: 410 karakter, h1='Katalog Produk', produk=0 ; /catalog/ut-dolore: 244 karakter, h1='', produk=0 ; /about: 2839 karakter, h1='Tentang Harmoni Clothing', produk=0; konten dari API di-render klien sehingga bagian data kosong/skeleton</t>
+          <t>tanpa JavaScript: Putaran 28 baris: JS dimatikan: /catalog memuat 13 tautan produk (halaman pertama dirender di server), /about 2839 karakter, /kontak 682, /faq 642; beranda 3016 karakter dengan judul 'Wujudkan Ide. Ciptakan Produk. Bergerak Bersama.'; bagian produk/desain populer di beranda dan data marketplace baru terisi setelah JS aktif. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): JavaScript nonaktif: tanpa JS: /: 3016 karakter, h1='Wujudkan Ide.
+Ciptakan Produk.', produk=0 ; /catalog: 410 karakter, h1='Katalog Produk', produk</t>
         </is>
       </c>
     </row>
@@ -18116,14 +18116,14 @@
           <t>Skeleton/loading, EmptyState, ErrorState ("Coba Lagi") tampil konsisten di semua halaman data</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): state loading/kosong/error konsisten: skeleton, state kosong ('Belum ada ...', 'masih kosong') terbukti; ErrorState 'Coba Lagi' untuk kegagalan fetch publik TIDAK muncul (lihat sheet Error #11/#22)</t>
+          <t>ErrorState di halaman data: Putaran 28 baris: API dipaksa 500: /catalog: tombol Coba Lagi 1, /marketplace: tombol Coba Lagi 1, /catalog/:slug: tombol Coba Lagi 1, /marketplace/design/:slug: tombol Coba Lagi 1; dashboard admin/creator juga punya blok error (putaran sebelumnya); skeleton dan state kosong ('Belum ada ...') terbukti sebelumnya. | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): state loading/kosong/error konsisten: skeleton, state kosong ('Belum ada ...', 'masih kosong') terbukti; ErrorState 'Coba Lagi' untuk kegagalan fetc</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18771,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Header &amp; footer tampil. Console hanya memuat 404 halaman itu sendiri dan 401 /api/me (normal untuk tamu) - tetapi tetap muncul sebagai error di console.</t>
+          <t>404 tamu: Putaran 28 baris: /halaman-tidak-ada: HTTP 404, header dan footer tampil. Konsol memuat 2 entri error: Failed to load resource: the server responded with a status of 404 (Not Found) | Failed to load resource: the server responded with a status of 401 (Unauthorized) - log bawaan browser untuk respons 404 halaman itu sendiri dan 401 GET /api/me (tamu belum login), bukan error JavaScript. | Sebelumnya (Sebagian): Header &amp; footer tampil. Console hanya memuat 404 halaman itu sendiri dan 401 /api/me (normal untuk tamu) - tetapi tetap muncul sebagai error di console.</t>
         </is>
       </c>
     </row>
@@ -19589,14 +19589,14 @@
           <t>409 konflik (mis. menolak pesanan yang sudah berubah) ditampilkan sebagai pesan jelas</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>UI (Playwright, Edge headless, :3001 + backend QC): 409 konflik pesan jelas: endpoint reject mengembalikan 409 (sheet E2E #32); tampilan pesan di UI admin belum disimulasikan</t>
+          <t>409 pada tolak pesanan: Putaran 28 baris: respons 409 pada tolak pesanan ditampilkan sebagai pesan jelas 'Pesanan sudah berubah status, muat ulang halaman.' (tidak senyap). | Sebelumnya (Sebagian): UI (Playwright, Edge headless, :3001 + backend QC): 409 konflik pesan jelas: endpoint reject mengembalikan 409 (sheet E2E #32); tampilan pesan di UI admin belum disimulasikan</t>
         </is>
       </c>
     </row>
@@ -21485,14 +21485,14 @@
           <t>Creator tidak bisa diaktifkan tanpa data KYC lengkap (validasi KTP, tanggal lahir, rekening)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Sebagian</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Lulus</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>approve tanpa KYC: Putaran 80 baris: status=200, status profil=aktif, {"data":{"id":12,"user":{"id":20,"name":"Herman Schiller PhD","email":"jamal.collier@example.com"}," | Sebelumnya (Sebagian): approve creator tanpa KYC: Verifikasi tambahan (kelompok hanya-API): tidak ada profil creator tanpa KYC di data uji | Sebelumnya (Sebagian): approve creator tanpa KYC: Verifikasi tambahan (kelompok hanya-API): tidak ada profil creator tanpa</t>
+          <t>Putaran 28 baris: test otomatis: profil creator menunggu_approval dengan KTP, tanggal lahir, nama KYC, dan rekening kosong -&gt; approve ditolak 422 (kunci 'kyc') dan status tetap menunggu_approval; guard ada di CreatorService::approve. | Sebelumnya (Sebagian): approve tanpa KYC: Putaran 80 baris: status=200, status profil=aktif, {"data":{"id":12,"user":{"id":20,"name":"Herman Schiller PhD","email":"jamal.collier@example.com"}," | Sebelumnya (Sebagian): appr</t>
         </is>
       </c>
     </row>
